--- a/templates/LRC_Watchlist_master.xlsx
+++ b/templates/LRC_Watchlist_master.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="596">
   <si>
     <t xml:space="preserve">LRC Watchlist Builder — Swing &amp; Investment</t>
   </si>
@@ -707,6 +707,96 @@
     <t xml:space="preserve">Trigger: Sell stop below the 15-day low (49.11) — only AFTER the 14 Oct results are digested. Short entry 49.00, stop 50.96 (2×ATR 0.98), target 43.12 (3R). LRC Work-sheet 14 Oct: SELL (6-m target ~$38.37, -25%; score 3.5/5; technical: CLEARED — STAGED ENTRY). SELL (−25%) + technical clearance. Results 14 Oct (today) — wait for the reaction. 5th short: house limit is 4 open shorts, so only if one of the others has not triggered. Data 13 Oct close: stockanalysis statistics + daily history to 13 Oct (SMA20/ATR14 computed); Perf Half vs ~13 Apr close; EPS growth this yr = consensus current FY (adjusted). Perf Quarter n/f (history page holds 50 sessions). Finviz itself blocked for us — same filters applied manually. — P. Nkuna</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating BUY (6-m value 262.56); CLEARED. Entry 222.63, stop 210.83 (2×ATR), target 258.03 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating BUY (6-m value 426.0); NOT CLEARED. Entry 342.47, stop 318.21 (2×ATR), target 415.25 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deckers Outdoor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating BUY (6-m value 103.0); NOT CLEARED — results within 14 days. Entry 88.16, stop 83.18 (2×ATR), target 103.1 (3R). Results 2026-10-22 — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOOGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alphabet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 319.72); CLEARED — results within 14 days. Entry 329.72, stop 346.98 (2×ATR), target 277.94 (3R). Results 2026-10-28 — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dell Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 404.7); CLEARED. Entry 438.62, stop 501.96 (2×ATR), target 248.6 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEYS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keysight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 319.77); CLEARED. Entry 322.42, stop 347.22 (2×ATR), target 248.02 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amphenol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 75.63); CLEARED — results within 14 days. Entry 77.72, stop 83.08 (2×ATR), target 61.64 (3R). Results 2026-10-28 — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 29.75); CLEARED. Entry 31.91, stop 34.03 (2×ATR), target 25.55 (3R). house limit: max 4 shorts — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">META</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 677.14); CLEARED — results within 14 days. Entry 679.69, stop 728.69 (2×ATR), target 532.69 (3R). Results 2026-10-21; house limit: max 4 shorts — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arista Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 144.61); CLEARED — results within 14 days. Entry 176.42, stop 192.82 (2×ATR), target 127.22 (3R). Results 2026-11-03; house limit: max 4 shorts — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fastenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 38.37); CLEARED. Entry 47.21, stop 49.85 (2×ATR), target 39.29 (3R). house limit: max 4 shorts — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Micro Devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 402.73); CLEARED — results within 14 days. Entry 523.55, stop 576.65 (2×ATR), target 364.25 (3R). Results 2026-11-03; house limit: max 4 shorts — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wabtec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 248.07); CLEARED — results within 14 days. Entry 274.58, stop 288.58 (2×ATR), target 232.58 (3R). Results 2026-10-21; house limit: max 4 shorts — LRC Watchlist Agent</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weekly Review — swing (every weekend)</t>
   </si>
   <si>
@@ -788,6 +878,9 @@
     <t xml:space="preserve">Finviz is blocked for our tools, so the Swing Long / Swing Short presets were applied manually on stockanalysis.com data (13 Oct closes). LRC RULE: only BUY/SELL-rated names with technical clearance are tradeable. LONGS: only NVDA qualifies; INTU and DECK are BUY-rated but in downtrends (watch only). 2 long slots unfilled — the momentum names the long preset finds (DELL, HPE, KEYS, APH, AMD) all rate SELL on valuation. SHORTS: NKE, ANET, AMD, DELL, FAST (max 4 open; FAST only after its 14 Oct results). Event risk inside 14 days: WAB 21 Oct, DECK 22 Oct, META 21 Oct, APH/GOOGL 28 Oct. S&amp;P 500 above its 200-day; JSE All Share below (−7.4% in 6 months). Lesson: an un-entered trigger cost us the PCTY move (+9%) — set conditional orders when a setup is approved. — P. Nkuna</t>
   </si>
   <si>
+    <t xml:space="preserve">Built by the LRC Watchlist Agent 2026-10-23T03:09+02:00: 3 long / 10 short candidates under house rules. Analyst to review before any trade.</t>
+  </si>
+  <si>
     <t xml:space="preserve">How to pick long-term investments (hold 5 to 10+ years) — every month</t>
   </si>
   <si>
@@ -1038,9 +1131,6 @@
   </si>
   <si>
     <t xml:space="preserve">LRC Work-sheet 14 Oct: HOLD, 6-m target $157.05 (-1%), score 3.8/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">META</t>
   </si>
   <si>
     <t xml:space="preserve">Meta Platforms, Inc.</t>
@@ -2540,13 +2630,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865800</xdr:colOff>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2556,11 +2646,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2582,13 +2673,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>513360</xdr:colOff>
+      <xdr:colOff>420840</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2598,11 +2689,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2624,13 +2716,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865800</xdr:colOff>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2640,11 +2732,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2665,14 +2758,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>90360</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2682,11 +2775,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2707,14 +2801,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19800</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2724,11 +2818,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2750,13 +2845,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865800</xdr:colOff>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="6" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2766,11 +2861,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2791,14 +2887,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>90360</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="7" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2808,11 +2904,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2833,14 +2930,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19800</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="8" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2850,11 +2947,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2876,13 +2974,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865800</xdr:colOff>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="9" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2892,11 +2990,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2915,34 +3014,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -3089,7 +3188,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="22"/>
@@ -3325,40 +3424,40 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="56" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="57" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>144</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="H3" s="57" t="s">
-        <v>545</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3366,7 +3465,7 @@
         <v>179</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>192</v>
@@ -3375,13 +3474,13 @@
         <v>183</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="H4" s="58" t="s">
         <v>182</v>
@@ -3389,7 +3488,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="B5" s="58" t="s">
         <v>184</v>
@@ -3404,38 +3503,38 @@
         <v>192</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="58" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="58" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>41</v>
@@ -3452,10 +3551,10 @@
         <v>185</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>559</v>
+        <v>589</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3463,7 +3562,7 @@
         <v>191</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="H9" s="58" t="s">
         <v>189</v>
@@ -3471,10 +3570,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="58" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3482,15 +3581,15 @@
         <v>211</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="58" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3498,12 +3597,12 @@
         <v>213</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="58" t="s">
-        <v>565</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -3524,7 +3623,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
@@ -3601,7 +3700,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="8" t="n">
         <f aca="false">IF('Swing Watchlist'!$C$4="","",'Swing Watchlist'!$C$4)</f>
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -3626,7 +3725,7 @@
       <c r="C6" s="7"/>
       <c r="D6" s="10" t="n">
         <f aca="false">'Swing Watchlist'!U4</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -3676,7 +3775,7 @@
       <c r="C8" s="7"/>
       <c r="D8" s="11" t="str">
         <f aca="false">'Swing Watchlist'!U5&amp;"  ·  "&amp;'Swing Watchlist'!U6</f>
-        <v>8 / 0  ·  3 / 5</v>
+        <v>13 / 0  ·  3 / 10</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -3701,7 +3800,7 @@
       <c r="C9" s="7"/>
       <c r="D9" s="11" t="str">
         <f aca="false">COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"A")&amp;" / "&amp;COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"B")&amp;" / "&amp;COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"C")</f>
-        <v>2 / 0 / 6</v>
+        <v>0 / 9 / 4</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -3857,23 +3956,23 @@
       </c>
       <c r="B16" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>NVDA</v>
+        <v>NKE</v>
       </c>
       <c r="C16" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
-        <v>Long</v>
+        <v>Short</v>
       </c>
       <c r="D16" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="F16" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Run Technical Review — LONG entry</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>1</v>
@@ -3906,7 +4005,7 @@
       </c>
       <c r="B17" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>NKE</v>
+        <v>KEYS</v>
       </c>
       <c r="C17" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -3914,15 +4013,15 @@
       </c>
       <c r="D17" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="F17" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Run Technical Review — SHORT entry</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>2</v>
@@ -3955,23 +4054,23 @@
       </c>
       <c r="B18" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>ANET</v>
+        <v>NVDA</v>
       </c>
       <c r="C18" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
-        <v>Short</v>
+        <v>Long</v>
       </c>
       <c r="D18" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F18" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Drop or re-check next week</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H18" s="13" t="n">
         <v>3</v>
@@ -4004,7 +4103,7 @@
       </c>
       <c r="B19" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>FAST</v>
+        <v>GOOGL</v>
       </c>
       <c r="C19" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -4012,15 +4111,15 @@
       </c>
       <c r="D19" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F19" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Drop or re-check next week</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H19" s="13" t="n">
         <v>4</v>
@@ -4053,7 +4152,7 @@
       </c>
       <c r="B20" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>AMD</v>
+        <v>ANET</v>
       </c>
       <c r="C20" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -4061,15 +4160,15 @@
       </c>
       <c r="D20" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F20" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Drop or re-check next week</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H20" s="13" t="n">
         <v>5</v>
@@ -4199,7 +4298,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="16"/>
@@ -4720,7 +4819,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AX210"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
@@ -4871,7 +4970,7 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="19" t="n">
-        <v>46312</v>
+        <v>46316</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>118</v>
@@ -4900,7 +4999,7 @@
       <c r="T4" s="22"/>
       <c r="U4" s="23" t="n">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$C$11:$C$210,"?*")</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V4" s="24" t="str">
         <f aca="false">IF(U4&gt;=$C$5,"✔ minimum met","⚠ need "&amp;($C$5-U4)&amp;" more")</f>
@@ -4944,7 +5043,7 @@
       <c r="T5" s="22"/>
       <c r="U5" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$B$11:$B$210,"US")&amp;" / "&amp;COUNTIFS($A$11:$A$210,$C$4,$B$11:$B$210,"JSE")</f>
-        <v>8 / 0</v>
+        <v>13 / 0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4982,7 +5081,7 @@
       <c r="T6" s="22"/>
       <c r="U6" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$C$11:$C$210,"?*",$F$11:$F$210,"&lt;&gt;Short")&amp;" / "&amp;COUNTIFS($A$11:$A$210,$C$4,$F$11:$F$210,"Short")</f>
-        <v>3 / 5</v>
+        <v>3 / 10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5020,7 +5119,7 @@
       <c r="T7" s="22"/>
       <c r="U7" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$AK$11:$AK$210,"A")&amp;" / "&amp;COUNTIF($AP$11:$AP$210,"Open position")</f>
-        <v>2 / 0</v>
+        <v>0 / 0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5876,9 +5975,9 @@
       <c r="AV14" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="AX14" s="43" t="n">
+      <c r="AX14" s="43" t="str">
         <f aca="false">IF(AND(C14&lt;&gt;"",A14=$C$4,ISNUMBER(AJ14)),AJ14+ROW()/100000,"")</f>
-        <v>17.00014</v>
+        <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6038,9 +6137,9 @@
       <c r="AV15" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="AX15" s="43" t="n">
+      <c r="AX15" s="43" t="str">
         <f aca="false">IF(AND(C15&lt;&gt;"",A15=$C$4,ISNUMBER(AJ15)),AJ15+ROW()/100000,"")</f>
-        <v>8.00015</v>
+        <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6200,9 +6299,9 @@
       <c r="AV16" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="AX16" s="43" t="n">
+      <c r="AX16" s="43" t="str">
         <f aca="false">IF(AND(C16&lt;&gt;"",A16=$C$4,ISNUMBER(AJ16)),AJ16+ROW()/100000,"")</f>
-        <v>8.00016</v>
+        <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6360,9 +6459,9 @@
       <c r="AV17" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="AX17" s="43" t="n">
+      <c r="AX17" s="43" t="str">
         <f aca="false">IF(AND(C17&lt;&gt;"",A17=$C$4,ISNUMBER(AJ17)),AJ17+ROW()/100000,"")</f>
-        <v>16.00017</v>
+        <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6522,9 +6621,9 @@
       <c r="AV18" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="AX18" s="43" t="n">
+      <c r="AX18" s="43" t="str">
         <f aca="false">IF(AND(C18&lt;&gt;"",A18=$C$4,ISNUMBER(AJ18)),AJ18+ROW()/100000,"")</f>
-        <v>9.00018</v>
+        <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6686,9 +6785,9 @@
       <c r="AV19" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="AX19" s="43" t="n">
+      <c r="AX19" s="43" t="str">
         <f aca="false">IF(AND(C19&lt;&gt;"",A19=$C$4,ISNUMBER(AJ19)),AJ19+ROW()/100000,"")</f>
-        <v>8.00019</v>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6850,9 +6949,9 @@
       <c r="AV20" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="AX20" s="43" t="n">
+      <c r="AX20" s="43" t="str">
         <f aca="false">IF(AND(C20&lt;&gt;"",A20=$C$4,ISNUMBER(AJ20)),AJ20+ROW()/100000,"")</f>
-        <v>7.0002</v>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7012,99 +7111,149 @@
       <c r="AV21" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="AX21" s="43" t="n">
+      <c r="AX21" s="43" t="str">
         <f aca="false">IF(AND(C21&lt;&gt;"",A21=$C$4,ISNUMBER(AJ21)),AJ21+ROW()/100000,"")</f>
-        <v>8.00021</v>
+        <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="26"/>
+      <c r="A22" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G22" s="26" t="n">
+        <v>221.97</v>
+      </c>
       <c r="H22" s="26"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="37" t="str">
+      <c r="I22" s="36" t="n">
+        <v>117533575</v>
+      </c>
+      <c r="J22" s="37" t="n">
         <f aca="false">IF(OR(G22="",I22=""),"",G22*I22/1000000)</f>
-        <v/>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="38"/>
+        <v>26088.92764275</v>
+      </c>
+      <c r="K22" s="21" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="L22" s="21" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="M22" s="21" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="O22" s="21" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="P22" s="21" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>-0.0879</v>
+      </c>
+      <c r="R22" s="21" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="S22" s="38" t="n">
+        <v>0.74</v>
+      </c>
       <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="26"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="26"/>
-      <c r="Z22" s="26"/>
-      <c r="AA22" s="26"/>
-      <c r="AB22" s="16" t="str">
+      <c r="U22" s="21" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="V22" s="19" t="n">
+        <v>46344</v>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="X22" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y22" s="26" t="n">
+        <v>222.63</v>
+      </c>
+      <c r="Z22" s="26" t="n">
+        <v>210.83</v>
+      </c>
+      <c r="AA22" s="26" t="n">
+        <v>258.03</v>
+      </c>
+      <c r="AB22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",(AND(M22&lt;&gt;"",N(M22)&lt;0))+(AND(L22&lt;&gt;"",N(L22)&lt;0))+(AND(K22&lt;&gt;"",N(K22)&lt;0))+AND(L22&lt;&gt;"",M22&lt;&gt;"",N(M22)&lt;N(L22)),(N(M22)&gt;0)+(N(L22)&gt;0)+(N(K22)&gt;0)+AND(L22&lt;&gt;"",M22&lt;&gt;"",N(M22)&gt;N(L22))))</f>
-        <v/>
-      </c>
-      <c r="AC22" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",IF(N22="",0,IF(AND(N22&gt;=30,N22&lt;=50),2,IF(OR(AND(N22&gt;=25,N22&lt;30),AND(N22&gt;50,N22&lt;=60)),1,0)))+IF(P22="",0,IF(AND(IF(B22="JSE",$L$5,$L$4)&lt;&gt;"",P22&lt;IF(B22="JSE",$L$5,$L$4)),2,IF(P22&lt;0,1,0))),IF(N22="",0,IF(AND(N22&gt;=50,N22&lt;=70),2,IF(OR(AND(N22&gt;=40,N22&lt;50),AND(N22&gt;70,N22&lt;=75)),1,0)))+IF(P22="",0,IF(AND(IF(B22="JSE",$L$5,$L$4)&lt;&gt;"",P22&gt;IF(B22="JSE",$L$5,$L$4)),2,IF(P22&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD22" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AD22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",IF(R22="",0,IF(R22&lt;=0.1,2,IF(R22&lt;=0.25,1,0))),IF(Q22="",0,IF(Q22&gt;=-0.1,2,IF(Q22&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE22" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AE22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(J22="",0,IF(J22&gt;=IF(B22="JSE",$L$7,$L$6),2,IF(J22&gt;=IF(B22="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF22" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",AND(T22&lt;&gt;"",N(T22)&lt;0),N(T22)&gt;0)+(N(S22)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG22" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(AL22="",0,IF(AL22&gt;=3,4,IF(AL22&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH22" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(AND(ISNUMBER(V22),ISNUMBER(A22),V22&gt;=A22,V22-A22&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI22" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(AND(F22="Short",N(U22)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="23" t="n">
         <f aca="false">IF(C22="","",SUM(AB22:AI22))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="AK22" s="24" t="str">
         <f aca="false">IF(C22="","",IF(AJ22&gt;=14,"A",IF(AJ22&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL22" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL22" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y22="",Z22="",AA22=""),"",IF(F22="Short",IF(Z22&lt;=Y22,"",(Y22-AA22)/(Z22-Y22)),IF(Y22&lt;=Z22,"",(AA22-Y22)/(Y22-Z22)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM22" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="37" t="n">
         <f aca="false">IF(OR(Y22="",Z22="",N(Y22)=N(Z22)),"",IF(OR(AND(F22="Short",Z22&lt;Y22),AND(NOT(F22="Short"),Z22&gt;Y22)),"stop on wrong side",ABS(Y22-Z22)))</f>
-        <v/>
-      </c>
-      <c r="AN22" s="40" t="str">
+        <v>11.8</v>
+      </c>
+      <c r="AN22" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM22)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM22,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO22" s="37" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="AO22" s="37" t="n">
         <f aca="false">IFERROR(IF(AN22="","",AN22*Y22),"")</f>
-        <v/>
-      </c>
-      <c r="AP22" s="35"/>
+        <v>6.6789</v>
+      </c>
+      <c r="AP22" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ22" s="19"/>
       <c r="AR22" s="26"/>
       <c r="AS22" s="41" t="str">
@@ -7117,102 +7266,156 @@
       </c>
       <c r="AU22" s="14" t="str">
         <f aca="false">IF(C22="","",IF(AP22="Open position",IF(IF(F22="Short",AND(ISNUMBER(AR22),ISNUMBER(Z22),AR22&gt;=Z22),AND(ISNUMBER(AR22),ISNUMBER(Z22),AR22&lt;=Z22)),IF(F22="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F22="Short",AND(ISNUMBER(AR22),ISNUMBER(AA22),AR22&lt;=AA22),AND(ISNUMBER(AR22),ISNUMBER(AA22),AR22&gt;=AA22)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT22),AT22&gt;182),IF(F22="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT22),AT22&gt;42,ISNUMBER(AS22),AS22&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F22="Short",AND(L22&lt;&gt;"",N(L22)&gt;0),AND(L22&lt;&gt;"",N(L22)&lt;0)),IF(F22="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP22="Closed",AP22="Dropped"),"Closed",IF(AK22="A",IF(F22="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK22="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV22" s="35"/>
-      <c r="AX22" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV22" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="AX22" s="43" t="n">
         <f aca="false">IF(AND(C22&lt;&gt;"",A22=$C$4,ISNUMBER(AJ22)),AJ22+ROW()/100000,"")</f>
-        <v/>
+        <v>12.00022</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="26"/>
+      <c r="A23" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="26" t="n">
+        <v>335.61</v>
+      </c>
       <c r="H23" s="26"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="37" t="str">
+      <c r="I23" s="36" t="n">
+        <v>3793417</v>
+      </c>
+      <c r="J23" s="37" t="n">
         <f aca="false">IF(OR(G23="",I23=""),"",G23*I23/1000000)</f>
-        <v/>
-      </c>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="26"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="26"/>
-      <c r="Z23" s="26"/>
-      <c r="AA23" s="26"/>
-      <c r="AB23" s="16" t="str">
+        <v>1273.10867937</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="L23" s="21" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="M23" s="21" t="n">
+        <v>-0.0948</v>
+      </c>
+      <c r="N23" s="25" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="O23" s="21" t="n">
+        <v>0.1921</v>
+      </c>
+      <c r="P23" s="21" t="n">
+        <v>-0.1788</v>
+      </c>
+      <c r="Q23" s="21" t="n">
+        <v>-0.513</v>
+      </c>
+      <c r="R23" s="21" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="S23" s="38" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T23" s="21" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="U23" s="21" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="V23" s="19" t="n">
+        <v>46345</v>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="X23" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y23" s="26" t="n">
+        <v>342.47</v>
+      </c>
+      <c r="Z23" s="26" t="n">
+        <v>318.21</v>
+      </c>
+      <c r="AA23" s="26" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AB23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",(AND(M23&lt;&gt;"",N(M23)&lt;0))+(AND(L23&lt;&gt;"",N(L23)&lt;0))+(AND(K23&lt;&gt;"",N(K23)&lt;0))+AND(L23&lt;&gt;"",M23&lt;&gt;"",N(M23)&lt;N(L23)),(N(M23)&gt;0)+(N(L23)&gt;0)+(N(K23)&gt;0)+AND(L23&lt;&gt;"",M23&lt;&gt;"",N(M23)&gt;N(L23))))</f>
-        <v/>
-      </c>
-      <c r="AC23" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",IF(N23="",0,IF(AND(N23&gt;=30,N23&lt;=50),2,IF(OR(AND(N23&gt;=25,N23&lt;30),AND(N23&gt;50,N23&lt;=60)),1,0)))+IF(P23="",0,IF(AND(IF(B23="JSE",$L$5,$L$4)&lt;&gt;"",P23&lt;IF(B23="JSE",$L$5,$L$4)),2,IF(P23&lt;0,1,0))),IF(N23="",0,IF(AND(N23&gt;=50,N23&lt;=70),2,IF(OR(AND(N23&gt;=40,N23&lt;50),AND(N23&gt;70,N23&lt;=75)),1,0)))+IF(P23="",0,IF(AND(IF(B23="JSE",$L$5,$L$4)&lt;&gt;"",P23&gt;IF(B23="JSE",$L$5,$L$4)),2,IF(P23&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD23" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AD23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",IF(R23="",0,IF(R23&lt;=0.1,2,IF(R23&lt;=0.25,1,0))),IF(Q23="",0,IF(Q23&gt;=-0.1,2,IF(Q23&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE23" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(J23="",0,IF(J23&gt;=IF(B23="JSE",$L$7,$L$6),2,IF(J23&gt;=IF(B23="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF23" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",AND(T23&lt;&gt;"",N(T23)&lt;0),N(T23)&gt;0)+(N(S23)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG23" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(AL23="",0,IF(AL23&gt;=3,4,IF(AL23&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH23" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(AND(ISNUMBER(V23),ISNUMBER(A23),V23&gt;=A23,V23-A23&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI23" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(AND(F23="Short",N(U23)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="23" t="n">
         <f aca="false">IF(C23="","",SUM(AB23:AI23))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK23" s="24" t="str">
         <f aca="false">IF(C23="","",IF(AJ23&gt;=14,"A",IF(AJ23&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL23" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL23" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y23="",Z23="",AA23=""),"",IF(F23="Short",IF(Z23&lt;=Y23,"",(Y23-AA23)/(Z23-Y23)),IF(Y23&lt;=Z23,"",(AA23-Y23)/(Y23-Z23)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM23" s="37" t="str">
+        <v>2.99999999999999</v>
+      </c>
+      <c r="AM23" s="37" t="n">
         <f aca="false">IF(OR(Y23="",Z23="",N(Y23)=N(Z23)),"",IF(OR(AND(F23="Short",Z23&lt;Y23),AND(NOT(F23="Short"),Z23&gt;Y23)),"stop on wrong side",ABS(Y23-Z23)))</f>
-        <v/>
-      </c>
-      <c r="AN23" s="40" t="str">
+        <v>24.26</v>
+      </c>
+      <c r="AN23" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM23)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM23,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO23" s="37" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="AO23" s="37" t="n">
         <f aca="false">IFERROR(IF(AN23="","",AN23*Y23),"")</f>
-        <v/>
-      </c>
-      <c r="AP23" s="35"/>
+        <v>3.4247</v>
+      </c>
+      <c r="AP23" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ23" s="19"/>
       <c r="AR23" s="26"/>
       <c r="AS23" s="41" t="str">
@@ -7225,102 +7428,154 @@
       </c>
       <c r="AU23" s="14" t="str">
         <f aca="false">IF(C23="","",IF(AP23="Open position",IF(IF(F23="Short",AND(ISNUMBER(AR23),ISNUMBER(Z23),AR23&gt;=Z23),AND(ISNUMBER(AR23),ISNUMBER(Z23),AR23&lt;=Z23)),IF(F23="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F23="Short",AND(ISNUMBER(AR23),ISNUMBER(AA23),AR23&lt;=AA23),AND(ISNUMBER(AR23),ISNUMBER(AA23),AR23&gt;=AA23)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT23),AT23&gt;182),IF(F23="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT23),AT23&gt;42,ISNUMBER(AS23),AS23&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F23="Short",AND(L23&lt;&gt;"",N(L23)&gt;0),AND(L23&lt;&gt;"",N(L23)&lt;0)),IF(F23="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP23="Closed",AP23="Dropped"),"Closed",IF(AK23="A",IF(F23="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK23="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV23" s="35"/>
-      <c r="AX23" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV23" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="AX23" s="43" t="n">
         <f aca="false">IF(AND(C23&lt;&gt;"",A23=$C$4,ISNUMBER(AJ23)),AJ23+ROW()/100000,"")</f>
-        <v/>
+        <v>10.00023</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="26"/>
+      <c r="A24" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>85.49</v>
+      </c>
       <c r="H24" s="26"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="37" t="str">
+      <c r="I24" s="36" t="n">
+        <v>2911073</v>
+      </c>
+      <c r="J24" s="37" t="n">
         <f aca="false">IF(OR(G24="",I24=""),"",G24*I24/1000000)</f>
-        <v/>
-      </c>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="38"/>
+        <v>248.86763077</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="M24" s="21" t="n">
+        <v>-0.1454</v>
+      </c>
+      <c r="N24" s="25" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="O24" s="21" t="n">
+        <v>-0.1116</v>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>-0.2061</v>
+      </c>
+      <c r="Q24" s="21" t="n">
+        <v>-0.3009</v>
+      </c>
+      <c r="R24" s="21" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="S24" s="38" t="n">
+        <v>1.01</v>
+      </c>
       <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="26"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="26"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="26"/>
-      <c r="AB24" s="16" t="str">
+      <c r="U24" s="21" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="V24" s="19" t="n">
+        <v>46317</v>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="X24" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y24" s="26" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="Z24" s="26" t="n">
+        <v>83.18</v>
+      </c>
+      <c r="AA24" s="26" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AB24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",(AND(M24&lt;&gt;"",N(M24)&lt;0))+(AND(L24&lt;&gt;"",N(L24)&lt;0))+(AND(K24&lt;&gt;"",N(K24)&lt;0))+AND(L24&lt;&gt;"",M24&lt;&gt;"",N(M24)&lt;N(L24)),(N(M24)&gt;0)+(N(L24)&gt;0)+(N(K24)&gt;0)+AND(L24&lt;&gt;"",M24&lt;&gt;"",N(M24)&gt;N(L24))))</f>
-        <v/>
-      </c>
-      <c r="AC24" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",IF(N24="",0,IF(AND(N24&gt;=30,N24&lt;=50),2,IF(OR(AND(N24&gt;=25,N24&lt;30),AND(N24&gt;50,N24&lt;=60)),1,0)))+IF(P24="",0,IF(AND(IF(B24="JSE",$L$5,$L$4)&lt;&gt;"",P24&lt;IF(B24="JSE",$L$5,$L$4)),2,IF(P24&lt;0,1,0))),IF(N24="",0,IF(AND(N24&gt;=50,N24&lt;=70),2,IF(OR(AND(N24&gt;=40,N24&lt;50),AND(N24&gt;70,N24&lt;=75)),1,0)))+IF(P24="",0,IF(AND(IF(B24="JSE",$L$5,$L$4)&lt;&gt;"",P24&gt;IF(B24="JSE",$L$5,$L$4)),2,IF(P24&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD24" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AD24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",IF(R24="",0,IF(R24&lt;=0.1,2,IF(R24&lt;=0.25,1,0))),IF(Q24="",0,IF(Q24&gt;=-0.1,2,IF(Q24&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE24" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(J24="",0,IF(J24&gt;=IF(B24="JSE",$L$7,$L$6),2,IF(J24&gt;=IF(B24="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF24" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",AND(T24&lt;&gt;"",N(T24)&lt;0),N(T24)&gt;0)+(N(S24)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG24" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(AL24="",0,IF(AL24&gt;=3,4,IF(AL24&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH24" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(AND(ISNUMBER(V24),ISNUMBER(A24),V24&gt;=A24,V24-A24&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI24" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(AND(F24="Short",N(U24)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ24" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="23" t="n">
         <f aca="false">IF(C24="","",SUM(AB24:AI24))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AK24" s="24" t="str">
         <f aca="false">IF(C24="","",IF(AJ24&gt;=14,"A",IF(AJ24&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL24" s="39" t="str">
+        <v>C</v>
+      </c>
+      <c r="AL24" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y24="",Z24="",AA24=""),"",IF(F24="Short",IF(Z24&lt;=Y24,"",(Y24-AA24)/(Z24-Y24)),IF(Y24&lt;=Z24,"",(AA24-Y24)/(Y24-Z24)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM24" s="37" t="str">
+        <v>3.00000000000001</v>
+      </c>
+      <c r="AM24" s="37" t="n">
         <f aca="false">IF(OR(Y24="",Z24="",N(Y24)=N(Z24)),"",IF(OR(AND(F24="Short",Z24&lt;Y24),AND(NOT(F24="Short"),Z24&gt;Y24)),"stop on wrong side",ABS(Y24-Z24)))</f>
-        <v/>
-      </c>
-      <c r="AN24" s="40" t="str">
+        <v>4.97999999999999</v>
+      </c>
+      <c r="AN24" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM24)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM24,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO24" s="37" t="str">
+        <v>0.09</v>
+      </c>
+      <c r="AO24" s="37" t="n">
         <f aca="false">IFERROR(IF(AN24="","",AN24*Y24),"")</f>
-        <v/>
-      </c>
-      <c r="AP24" s="35"/>
+        <v>7.9344</v>
+      </c>
+      <c r="AP24" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ24" s="19"/>
       <c r="AR24" s="26"/>
       <c r="AS24" s="41" t="str">
@@ -7333,102 +7588,154 @@
       </c>
       <c r="AU24" s="14" t="str">
         <f aca="false">IF(C24="","",IF(AP24="Open position",IF(IF(F24="Short",AND(ISNUMBER(AR24),ISNUMBER(Z24),AR24&gt;=Z24),AND(ISNUMBER(AR24),ISNUMBER(Z24),AR24&lt;=Z24)),IF(F24="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F24="Short",AND(ISNUMBER(AR24),ISNUMBER(AA24),AR24&lt;=AA24),AND(ISNUMBER(AR24),ISNUMBER(AA24),AR24&gt;=AA24)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT24),AT24&gt;182),IF(F24="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT24),AT24&gt;42,ISNUMBER(AS24),AS24&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F24="Short",AND(L24&lt;&gt;"",N(L24)&gt;0),AND(L24&lt;&gt;"",N(L24)&lt;0)),IF(F24="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP24="Closed",AP24="Dropped"),"Closed",IF(AK24="A",IF(F24="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK24="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV24" s="35"/>
-      <c r="AX24" s="43" t="str">
+        <v>Drop or re-check next week</v>
+      </c>
+      <c r="AV24" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="AX24" s="43" t="n">
         <f aca="false">IF(AND(C24&lt;&gt;"",A24=$C$4,ISNUMBER(AJ24)),AJ24+ROW()/100000,"")</f>
-        <v/>
+        <v>8.00024</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="26"/>
+      <c r="A25" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="26" t="n">
+        <v>334.76</v>
+      </c>
       <c r="H25" s="26"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="37" t="str">
+      <c r="I25" s="36" t="n">
+        <v>25764278</v>
+      </c>
+      <c r="J25" s="37" t="n">
         <f aca="false">IF(OR(G25="",I25=""),"",G25*I25/1000000)</f>
-        <v/>
-      </c>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="38"/>
+        <v>8624.84970328</v>
+      </c>
+      <c r="K25" s="21" t="n">
+        <v>-0.0302</v>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>-0.0264</v>
+      </c>
+      <c r="M25" s="21" t="n">
+        <v>-0.0191</v>
+      </c>
+      <c r="N25" s="25" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="O25" s="21" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="P25" s="21" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="Q25" s="21" t="n">
+        <v>-0.1807</v>
+      </c>
+      <c r="R25" s="21" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="S25" s="38" t="n">
+        <v>1.13</v>
+      </c>
       <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="26"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="26"/>
-      <c r="Z25" s="26"/>
-      <c r="AA25" s="26"/>
-      <c r="AB25" s="16" t="str">
+      <c r="U25" s="21" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="V25" s="19" t="n">
+        <v>46323</v>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>8.63</v>
+      </c>
+      <c r="X25" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y25" s="26" t="n">
+        <v>329.72</v>
+      </c>
+      <c r="Z25" s="26" t="n">
+        <v>346.98</v>
+      </c>
+      <c r="AA25" s="26" t="n">
+        <v>277.94</v>
+      </c>
+      <c r="AB25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(F25="Short",(AND(M25&lt;&gt;"",N(M25)&lt;0))+(AND(L25&lt;&gt;"",N(L25)&lt;0))+(AND(K25&lt;&gt;"",N(K25)&lt;0))+AND(L25&lt;&gt;"",M25&lt;&gt;"",N(M25)&lt;N(L25)),(N(M25)&gt;0)+(N(L25)&gt;0)+(N(K25)&gt;0)+AND(L25&lt;&gt;"",M25&lt;&gt;"",N(M25)&gt;N(L25))))</f>
-        <v/>
-      </c>
-      <c r="AC25" s="16" t="str">
+        <v>3</v>
+      </c>
+      <c r="AC25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(F25="Short",IF(N25="",0,IF(AND(N25&gt;=30,N25&lt;=50),2,IF(OR(AND(N25&gt;=25,N25&lt;30),AND(N25&gt;50,N25&lt;=60)),1,0)))+IF(P25="",0,IF(AND(IF(B25="JSE",$L$5,$L$4)&lt;&gt;"",P25&lt;IF(B25="JSE",$L$5,$L$4)),2,IF(P25&lt;0,1,0))),IF(N25="",0,IF(AND(N25&gt;=50,N25&lt;=70),2,IF(OR(AND(N25&gt;=40,N25&lt;50),AND(N25&gt;70,N25&lt;=75)),1,0)))+IF(P25="",0,IF(AND(IF(B25="JSE",$L$5,$L$4)&lt;&gt;"",P25&gt;IF(B25="JSE",$L$5,$L$4)),2,IF(P25&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD25" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AD25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(F25="Short",IF(R25="",0,IF(R25&lt;=0.1,2,IF(R25&lt;=0.25,1,0))),IF(Q25="",0,IF(Q25&gt;=-0.1,2,IF(Q25&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE25" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(J25="",0,IF(J25&gt;=IF(B25="JSE",$L$7,$L$6),2,IF(J25&gt;=IF(B25="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF25" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(F25="Short",AND(T25&lt;&gt;"",N(T25)&lt;0),N(T25)&gt;0)+(N(S25)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG25" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(AL25="",0,IF(AL25&gt;=3,4,IF(AL25&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH25" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(AND(ISNUMBER(V25),ISNUMBER(A25),V25&gt;=A25,V25-A25&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI25" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(AND(F25="Short",N(U25)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ25" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="23" t="n">
         <f aca="false">IF(C25="","",SUM(AB25:AI25))</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="AK25" s="24" t="str">
         <f aca="false">IF(C25="","",IF(AJ25&gt;=14,"A",IF(AJ25&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL25" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL25" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y25="",Z25="",AA25=""),"",IF(F25="Short",IF(Z25&lt;=Y25,"",(Y25-AA25)/(Z25-Y25)),IF(Y25&lt;=Z25,"",(AA25-Y25)/(Y25-Z25)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM25" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="37" t="n">
         <f aca="false">IF(OR(Y25="",Z25="",N(Y25)=N(Z25)),"",IF(OR(AND(F25="Short",Z25&lt;Y25),AND(NOT(F25="Short"),Z25&gt;Y25)),"stop on wrong side",ABS(Y25-Z25)))</f>
-        <v/>
-      </c>
-      <c r="AN25" s="40" t="str">
+        <v>17.26</v>
+      </c>
+      <c r="AN25" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM25)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM25,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO25" s="37" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="AO25" s="37" t="n">
         <f aca="false">IFERROR(IF(AN25="","",AN25*Y25),"")</f>
-        <v/>
-      </c>
-      <c r="AP25" s="35"/>
+        <v>6.5944</v>
+      </c>
+      <c r="AP25" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ25" s="19"/>
       <c r="AR25" s="26"/>
       <c r="AS25" s="41" t="str">
@@ -7441,102 +7748,156 @@
       </c>
       <c r="AU25" s="14" t="str">
         <f aca="false">IF(C25="","",IF(AP25="Open position",IF(IF(F25="Short",AND(ISNUMBER(AR25),ISNUMBER(Z25),AR25&gt;=Z25),AND(ISNUMBER(AR25),ISNUMBER(Z25),AR25&lt;=Z25)),IF(F25="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F25="Short",AND(ISNUMBER(AR25),ISNUMBER(AA25),AR25&lt;=AA25),AND(ISNUMBER(AR25),ISNUMBER(AA25),AR25&gt;=AA25)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT25),AT25&gt;182),IF(F25="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT25),AT25&gt;42,ISNUMBER(AS25),AS25&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F25="Short",AND(L25&lt;&gt;"",N(L25)&gt;0),AND(L25&lt;&gt;"",N(L25)&lt;0)),IF(F25="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP25="Closed",AP25="Dropped"),"Closed",IF(AK25="A",IF(F25="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK25="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV25" s="35"/>
-      <c r="AX25" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV25" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX25" s="43" t="n">
         <f aca="false">IF(AND(C25&lt;&gt;"",A25=$C$4,ISNUMBER(AJ25)),AJ25+ROW()/100000,"")</f>
-        <v/>
+        <v>11.00025</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="26"/>
+      <c r="A26" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>485.88</v>
+      </c>
       <c r="H26" s="26"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="37" t="str">
+      <c r="I26" s="36" t="n">
+        <v>7680617</v>
+      </c>
+      <c r="J26" s="37" t="n">
         <f aca="false">IF(OR(G26="",I26=""),"",G26*I26/1000000)</f>
-        <v/>
-      </c>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="38"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="26"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="26"/>
-      <c r="Z26" s="26"/>
-      <c r="AA26" s="26"/>
-      <c r="AB26" s="16" t="str">
+        <v>3731.85818796</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="L26" s="21" t="n">
+        <v>-0.0552</v>
+      </c>
+      <c r="M26" s="21" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="N26" s="25" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="O26" s="21" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="P26" s="21" t="n">
+        <v>1.2636</v>
+      </c>
+      <c r="Q26" s="21" t="n">
+        <v>-0.1841</v>
+      </c>
+      <c r="R26" s="21" t="n">
+        <v>3.4083</v>
+      </c>
+      <c r="S26" s="38" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="T26" s="21" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="U26" s="21" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="V26" s="19" t="n">
+        <v>46350</v>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="X26" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y26" s="26" t="n">
+        <v>438.62</v>
+      </c>
+      <c r="Z26" s="26" t="n">
+        <v>501.96</v>
+      </c>
+      <c r="AA26" s="26" t="n">
+        <v>248.6</v>
+      </c>
+      <c r="AB26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(F26="Short",(AND(M26&lt;&gt;"",N(M26)&lt;0))+(AND(L26&lt;&gt;"",N(L26)&lt;0))+(AND(K26&lt;&gt;"",N(K26)&lt;0))+AND(L26&lt;&gt;"",M26&lt;&gt;"",N(M26)&lt;N(L26)),(N(M26)&gt;0)+(N(L26)&gt;0)+(N(K26)&gt;0)+AND(L26&lt;&gt;"",M26&lt;&gt;"",N(M26)&gt;N(L26))))</f>
-        <v/>
-      </c>
-      <c r="AC26" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(F26="Short",IF(N26="",0,IF(AND(N26&gt;=30,N26&lt;=50),2,IF(OR(AND(N26&gt;=25,N26&lt;30),AND(N26&gt;50,N26&lt;=60)),1,0)))+IF(P26="",0,IF(AND(IF(B26="JSE",$L$5,$L$4)&lt;&gt;"",P26&lt;IF(B26="JSE",$L$5,$L$4)),2,IF(P26&lt;0,1,0))),IF(N26="",0,IF(AND(N26&gt;=50,N26&lt;=70),2,IF(OR(AND(N26&gt;=40,N26&lt;50),AND(N26&gt;70,N26&lt;=75)),1,0)))+IF(P26="",0,IF(AND(IF(B26="JSE",$L$5,$L$4)&lt;&gt;"",P26&gt;IF(B26="JSE",$L$5,$L$4)),2,IF(P26&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD26" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AD26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(F26="Short",IF(R26="",0,IF(R26&lt;=0.1,2,IF(R26&lt;=0.25,1,0))),IF(Q26="",0,IF(Q26&gt;=-0.1,2,IF(Q26&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE26" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(J26="",0,IF(J26&gt;=IF(B26="JSE",$L$7,$L$6),2,IF(J26&gt;=IF(B26="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF26" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(F26="Short",AND(T26&lt;&gt;"",N(T26)&lt;0),N(T26)&gt;0)+(N(S26)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG26" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(AL26="",0,IF(AL26&gt;=3,4,IF(AL26&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH26" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(AND(ISNUMBER(V26),ISNUMBER(A26),V26&gt;=A26,V26-A26&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI26" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(AND(F26="Short",N(U26)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ26" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="23" t="n">
         <f aca="false">IF(C26="","",SUM(AB26:AI26))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK26" s="24" t="str">
         <f aca="false">IF(C26="","",IF(AJ26&gt;=14,"A",IF(AJ26&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL26" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL26" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y26="",Z26="",AA26=""),"",IF(F26="Short",IF(Z26&lt;=Y26,"",(Y26-AA26)/(Z26-Y26)),IF(Y26&lt;=Z26,"",(AA26-Y26)/(Y26-Z26)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM26" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="37" t="n">
         <f aca="false">IF(OR(Y26="",Z26="",N(Y26)=N(Z26)),"",IF(OR(AND(F26="Short",Z26&lt;Y26),AND(NOT(F26="Short"),Z26&gt;Y26)),"stop on wrong side",ABS(Y26-Z26)))</f>
-        <v/>
-      </c>
-      <c r="AN26" s="40" t="str">
+        <v>63.34</v>
+      </c>
+      <c r="AN26" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM26)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM26,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO26" s="37" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="37" t="n">
         <f aca="false">IFERROR(IF(AN26="","",AN26*Y26),"")</f>
-        <v/>
-      </c>
-      <c r="AP26" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP26" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ26" s="19"/>
       <c r="AR26" s="26"/>
       <c r="AS26" s="41" t="str">
@@ -7549,102 +7910,156 @@
       </c>
       <c r="AU26" s="14" t="str">
         <f aca="false">IF(C26="","",IF(AP26="Open position",IF(IF(F26="Short",AND(ISNUMBER(AR26),ISNUMBER(Z26),AR26&gt;=Z26),AND(ISNUMBER(AR26),ISNUMBER(Z26),AR26&lt;=Z26)),IF(F26="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F26="Short",AND(ISNUMBER(AR26),ISNUMBER(AA26),AR26&lt;=AA26),AND(ISNUMBER(AR26),ISNUMBER(AA26),AR26&gt;=AA26)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT26),AT26&gt;182),IF(F26="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT26),AT26&gt;42,ISNUMBER(AS26),AS26&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F26="Short",AND(L26&lt;&gt;"",N(L26)&gt;0),AND(L26&lt;&gt;"",N(L26)&lt;0)),IF(F26="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP26="Closed",AP26="Dropped"),"Closed",IF(AK26="A",IF(F26="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK26="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV26" s="35"/>
-      <c r="AX26" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV26" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="AX26" s="43" t="n">
         <f aca="false">IF(AND(C26&lt;&gt;"",A26=$C$4,ISNUMBER(AJ26)),AJ26+ROW()/100000,"")</f>
-        <v/>
+        <v>10.00026</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="26"/>
+      <c r="A27" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>341.35</v>
+      </c>
       <c r="H27" s="26"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="37" t="str">
+      <c r="I27" s="36" t="n">
+        <v>1226576</v>
+      </c>
+      <c r="J27" s="37" t="n">
         <f aca="false">IF(OR(G27="",I27=""),"",G27*I27/1000000)</f>
-        <v/>
-      </c>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="38"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="16" t="str">
+        <v>418.6917176</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>-0.0601</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="N27" s="25" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="O27" s="21" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Q27" s="21" t="n">
+        <v>-0.1246</v>
+      </c>
+      <c r="R27" s="21" t="n">
+        <v>1.0901</v>
+      </c>
+      <c r="S27" s="38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="T27" s="21" t="n">
+        <v>0.6025</v>
+      </c>
+      <c r="U27" s="21" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="V27" s="19" t="n">
+        <v>46349</v>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="X27" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y27" s="26" t="n">
+        <v>322.42</v>
+      </c>
+      <c r="Z27" s="26" t="n">
+        <v>347.22</v>
+      </c>
+      <c r="AA27" s="26" t="n">
+        <v>248.02</v>
+      </c>
+      <c r="AB27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(F27="Short",(AND(M27&lt;&gt;"",N(M27)&lt;0))+(AND(L27&lt;&gt;"",N(L27)&lt;0))+(AND(K27&lt;&gt;"",N(K27)&lt;0))+AND(L27&lt;&gt;"",M27&lt;&gt;"",N(M27)&lt;N(L27)),(N(M27)&gt;0)+(N(L27)&gt;0)+(N(K27)&gt;0)+AND(L27&lt;&gt;"",M27&lt;&gt;"",N(M27)&gt;N(L27))))</f>
-        <v/>
-      </c>
-      <c r="AC27" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(F27="Short",IF(N27="",0,IF(AND(N27&gt;=30,N27&lt;=50),2,IF(OR(AND(N27&gt;=25,N27&lt;30),AND(N27&gt;50,N27&lt;=60)),1,0)))+IF(P27="",0,IF(AND(IF(B27="JSE",$L$5,$L$4)&lt;&gt;"",P27&lt;IF(B27="JSE",$L$5,$L$4)),2,IF(P27&lt;0,1,0))),IF(N27="",0,IF(AND(N27&gt;=50,N27&lt;=70),2,IF(OR(AND(N27&gt;=40,N27&lt;50),AND(N27&gt;70,N27&lt;=75)),1,0)))+IF(P27="",0,IF(AND(IF(B27="JSE",$L$5,$L$4)&lt;&gt;"",P27&gt;IF(B27="JSE",$L$5,$L$4)),2,IF(P27&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD27" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AD27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(F27="Short",IF(R27="",0,IF(R27&lt;=0.1,2,IF(R27&lt;=0.25,1,0))),IF(Q27="",0,IF(Q27&gt;=-0.1,2,IF(Q27&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE27" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(J27="",0,IF(J27&gt;=IF(B27="JSE",$L$7,$L$6),2,IF(J27&gt;=IF(B27="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF27" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(F27="Short",AND(T27&lt;&gt;"",N(T27)&lt;0),N(T27)&gt;0)+(N(S27)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG27" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(AL27="",0,IF(AL27&gt;=3,4,IF(AL27&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH27" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(AND(ISNUMBER(V27),ISNUMBER(A27),V27&gt;=A27,V27-A27&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI27" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(AND(F27="Short",N(U27)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ27" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="23" t="n">
         <f aca="false">IF(C27="","",SUM(AB27:AI27))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="AK27" s="24" t="str">
         <f aca="false">IF(C27="","",IF(AJ27&gt;=14,"A",IF(AJ27&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL27" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL27" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y27="",Z27="",AA27=""),"",IF(F27="Short",IF(Z27&lt;=Y27,"",(Y27-AA27)/(Z27-Y27)),IF(Y27&lt;=Z27,"",(AA27-Y27)/(Y27-Z27)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM27" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="37" t="n">
         <f aca="false">IF(OR(Y27="",Z27="",N(Y27)=N(Z27)),"",IF(OR(AND(F27="Short",Z27&lt;Y27),AND(NOT(F27="Short"),Z27&gt;Y27)),"stop on wrong side",ABS(Y27-Z27)))</f>
-        <v/>
-      </c>
-      <c r="AN27" s="40" t="str">
+        <v>24.8</v>
+      </c>
+      <c r="AN27" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM27)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM27,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO27" s="37" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="AO27" s="37" t="n">
         <f aca="false">IFERROR(IF(AN27="","",AN27*Y27),"")</f>
-        <v/>
-      </c>
-      <c r="AP27" s="35"/>
+        <v>3.2242</v>
+      </c>
+      <c r="AP27" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ27" s="19"/>
       <c r="AR27" s="26"/>
       <c r="AS27" s="41" t="str">
@@ -7657,102 +8072,156 @@
       </c>
       <c r="AU27" s="14" t="str">
         <f aca="false">IF(C27="","",IF(AP27="Open position",IF(IF(F27="Short",AND(ISNUMBER(AR27),ISNUMBER(Z27),AR27&gt;=Z27),AND(ISNUMBER(AR27),ISNUMBER(Z27),AR27&lt;=Z27)),IF(F27="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F27="Short",AND(ISNUMBER(AR27),ISNUMBER(AA27),AR27&lt;=AA27),AND(ISNUMBER(AR27),ISNUMBER(AA27),AR27&gt;=AA27)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT27),AT27&gt;182),IF(F27="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT27),AT27&gt;42,ISNUMBER(AS27),AS27&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F27="Short",AND(L27&lt;&gt;"",N(L27)&gt;0),AND(L27&lt;&gt;"",N(L27)&lt;0)),IF(F27="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP27="Closed",AP27="Dropped"),"Closed",IF(AK27="A",IF(F27="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK27="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV27" s="35"/>
-      <c r="AX27" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV27" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="AX27" s="43" t="n">
         <f aca="false">IF(AND(C27&lt;&gt;"",A27=$C$4,ISNUMBER(AJ27)),AJ27+ROW()/100000,"")</f>
-        <v/>
+        <v>12.00027</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="26"/>
+      <c r="A28" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>79.2</v>
+      </c>
       <c r="H28" s="26"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="37" t="str">
+      <c r="I28" s="36" t="n">
+        <v>12129273</v>
+      </c>
+      <c r="J28" s="37" t="n">
         <f aca="false">IF(OR(G28="",I28=""),"",G28*I28/1000000)</f>
-        <v/>
-      </c>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="38"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="26"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="16" t="str">
+        <v>960.6384216</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="L28" s="21" t="n">
+        <v>-0.0338</v>
+      </c>
+      <c r="M28" s="21" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="N28" s="25" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="Q28" s="21" t="n">
+        <v>-0.1193</v>
+      </c>
+      <c r="R28" s="21" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="S28" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" s="21" t="n">
+        <v>0.6088</v>
+      </c>
+      <c r="U28" s="21" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="V28" s="19" t="n">
+        <v>46323</v>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X28" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y28" s="26" t="n">
+        <v>77.72</v>
+      </c>
+      <c r="Z28" s="26" t="n">
+        <v>83.08</v>
+      </c>
+      <c r="AA28" s="26" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="AB28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(F28="Short",(AND(M28&lt;&gt;"",N(M28)&lt;0))+(AND(L28&lt;&gt;"",N(L28)&lt;0))+(AND(K28&lt;&gt;"",N(K28)&lt;0))+AND(L28&lt;&gt;"",M28&lt;&gt;"",N(M28)&lt;N(L28)),(N(M28)&gt;0)+(N(L28)&gt;0)+(N(K28)&gt;0)+AND(L28&lt;&gt;"",M28&lt;&gt;"",N(M28)&gt;N(L28))))</f>
-        <v/>
-      </c>
-      <c r="AC28" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(F28="Short",IF(N28="",0,IF(AND(N28&gt;=30,N28&lt;=50),2,IF(OR(AND(N28&gt;=25,N28&lt;30),AND(N28&gt;50,N28&lt;=60)),1,0)))+IF(P28="",0,IF(AND(IF(B28="JSE",$L$5,$L$4)&lt;&gt;"",P28&lt;IF(B28="JSE",$L$5,$L$4)),2,IF(P28&lt;0,1,0))),IF(N28="",0,IF(AND(N28&gt;=50,N28&lt;=70),2,IF(OR(AND(N28&gt;=40,N28&lt;50),AND(N28&gt;70,N28&lt;=75)),1,0)))+IF(P28="",0,IF(AND(IF(B28="JSE",$L$5,$L$4)&lt;&gt;"",P28&gt;IF(B28="JSE",$L$5,$L$4)),2,IF(P28&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD28" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AD28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(F28="Short",IF(R28="",0,IF(R28&lt;=0.1,2,IF(R28&lt;=0.25,1,0))),IF(Q28="",0,IF(Q28&gt;=-0.1,2,IF(Q28&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE28" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(J28="",0,IF(J28&gt;=IF(B28="JSE",$L$7,$L$6),2,IF(J28&gt;=IF(B28="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF28" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(F28="Short",AND(T28&lt;&gt;"",N(T28)&lt;0),N(T28)&gt;0)+(N(S28)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG28" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(AL28="",0,IF(AL28&gt;=3,4,IF(AL28&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH28" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(AND(ISNUMBER(V28),ISNUMBER(A28),V28&gt;=A28,V28-A28&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI28" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(AND(F28="Short",N(U28)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ28" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="23" t="n">
         <f aca="false">IF(C28="","",SUM(AB28:AI28))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK28" s="24" t="str">
         <f aca="false">IF(C28="","",IF(AJ28&gt;=14,"A",IF(AJ28&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL28" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL28" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y28="",Z28="",AA28=""),"",IF(F28="Short",IF(Z28&lt;=Y28,"",(Y28-AA28)/(Z28-Y28)),IF(Y28&lt;=Z28,"",(AA28-Y28)/(Y28-Z28)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM28" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="37" t="n">
         <f aca="false">IF(OR(Y28="",Z28="",N(Y28)=N(Z28)),"",IF(OR(AND(F28="Short",Z28&lt;Y28),AND(NOT(F28="Short"),Z28&gt;Y28)),"stop on wrong side",ABS(Y28-Z28)))</f>
-        <v/>
-      </c>
-      <c r="AN28" s="40" t="str">
+        <v>5.36</v>
+      </c>
+      <c r="AN28" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM28)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM28,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO28" s="37" t="str">
+        <v>0.08</v>
+      </c>
+      <c r="AO28" s="37" t="n">
         <f aca="false">IFERROR(IF(AN28="","",AN28*Y28),"")</f>
-        <v/>
-      </c>
-      <c r="AP28" s="35"/>
+        <v>6.2176</v>
+      </c>
+      <c r="AP28" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ28" s="19"/>
       <c r="AR28" s="26"/>
       <c r="AS28" s="41" t="str">
@@ -7765,102 +8234,154 @@
       </c>
       <c r="AU28" s="14" t="str">
         <f aca="false">IF(C28="","",IF(AP28="Open position",IF(IF(F28="Short",AND(ISNUMBER(AR28),ISNUMBER(Z28),AR28&gt;=Z28),AND(ISNUMBER(AR28),ISNUMBER(Z28),AR28&lt;=Z28)),IF(F28="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F28="Short",AND(ISNUMBER(AR28),ISNUMBER(AA28),AR28&lt;=AA28),AND(ISNUMBER(AR28),ISNUMBER(AA28),AR28&gt;=AA28)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT28),AT28&gt;182),IF(F28="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT28),AT28&gt;42,ISNUMBER(AS28),AS28&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F28="Short",AND(L28&lt;&gt;"",N(L28)&gt;0),AND(L28&lt;&gt;"",N(L28)&lt;0)),IF(F28="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP28="Closed",AP28="Dropped"),"Closed",IF(AK28="A",IF(F28="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK28="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV28" s="35"/>
-      <c r="AX28" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV28" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="AX28" s="43" t="n">
         <f aca="false">IF(AND(C28&lt;&gt;"",A28=$C$4,ISNUMBER(AJ28)),AJ28+ROW()/100000,"")</f>
-        <v/>
+        <v>10.00028</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="26"/>
+      <c r="A29" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="26" t="n">
+        <v>37.53</v>
+      </c>
       <c r="H29" s="26"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="37" t="str">
+      <c r="I29" s="36" t="n">
+        <v>33149133</v>
+      </c>
+      <c r="J29" s="37" t="n">
         <f aca="false">IF(OR(G29="",I29=""),"",G29*I29/1000000)</f>
-        <v/>
-      </c>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
+        <v>1244.08696149</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <v>0.0518</v>
+      </c>
+      <c r="L29" s="21" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <v>-0.2017</v>
+      </c>
+      <c r="N29" s="25" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="O29" s="21" t="n">
+        <v>-0.0844</v>
+      </c>
+      <c r="P29" s="21" t="n">
+        <v>-0.1784</v>
+      </c>
+      <c r="Q29" s="21" t="n">
+        <v>-0.4672</v>
+      </c>
+      <c r="R29" s="21" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="S29" s="38" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="T29" s="21" t="n">
+        <v>-0.1642</v>
+      </c>
+      <c r="U29" s="21" t="n">
+        <v>0.0842</v>
+      </c>
       <c r="V29" s="19"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="16" t="str">
+      <c r="W29" s="26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X29" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y29" s="26" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="Z29" s="26" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="AA29" s="26" t="n">
+        <v>25.55</v>
+      </c>
+      <c r="AB29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(F29="Short",(AND(M29&lt;&gt;"",N(M29)&lt;0))+(AND(L29&lt;&gt;"",N(L29)&lt;0))+(AND(K29&lt;&gt;"",N(K29)&lt;0))+AND(L29&lt;&gt;"",M29&lt;&gt;"",N(M29)&lt;N(L29)),(N(M29)&gt;0)+(N(L29)&gt;0)+(N(K29)&gt;0)+AND(L29&lt;&gt;"",M29&lt;&gt;"",N(M29)&gt;N(L29))))</f>
-        <v/>
-      </c>
-      <c r="AC29" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(F29="Short",IF(N29="",0,IF(AND(N29&gt;=30,N29&lt;=50),2,IF(OR(AND(N29&gt;=25,N29&lt;30),AND(N29&gt;50,N29&lt;=60)),1,0)))+IF(P29="",0,IF(AND(IF(B29="JSE",$L$5,$L$4)&lt;&gt;"",P29&lt;IF(B29="JSE",$L$5,$L$4)),2,IF(P29&lt;0,1,0))),IF(N29="",0,IF(AND(N29&gt;=50,N29&lt;=70),2,IF(OR(AND(N29&gt;=40,N29&lt;50),AND(N29&gt;70,N29&lt;=75)),1,0)))+IF(P29="",0,IF(AND(IF(B29="JSE",$L$5,$L$4)&lt;&gt;"",P29&gt;IF(B29="JSE",$L$5,$L$4)),2,IF(P29&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD29" s="16" t="str">
+        <v>3</v>
+      </c>
+      <c r="AD29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(F29="Short",IF(R29="",0,IF(R29&lt;=0.1,2,IF(R29&lt;=0.25,1,0))),IF(Q29="",0,IF(Q29&gt;=-0.1,2,IF(Q29&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE29" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(J29="",0,IF(J29&gt;=IF(B29="JSE",$L$7,$L$6),2,IF(J29&gt;=IF(B29="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF29" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(F29="Short",AND(T29&lt;&gt;"",N(T29)&lt;0),N(T29)&gt;0)+(N(S29)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG29" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(AL29="",0,IF(AL29&gt;=3,4,IF(AL29&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH29" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(AND(ISNUMBER(V29),ISNUMBER(A29),V29&gt;=A29,V29-A29&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI29" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(AND(F29="Short",N(U29)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ29" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="23" t="n">
         <f aca="false">IF(C29="","",SUM(AB29:AI29))</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="AK29" s="24" t="str">
         <f aca="false">IF(C29="","",IF(AJ29&gt;=14,"A",IF(AJ29&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL29" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL29" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y29="",Z29="",AA29=""),"",IF(F29="Short",IF(Z29&lt;=Y29,"",(Y29-AA29)/(Z29-Y29)),IF(Y29&lt;=Z29,"",(AA29-Y29)/(Y29-Z29)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM29" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="37" t="n">
         <f aca="false">IF(OR(Y29="",Z29="",N(Y29)=N(Z29)),"",IF(OR(AND(F29="Short",Z29&lt;Y29),AND(NOT(F29="Short"),Z29&gt;Y29)),"stop on wrong side",ABS(Y29-Z29)))</f>
-        <v/>
-      </c>
-      <c r="AN29" s="40" t="str">
+        <v>2.12</v>
+      </c>
+      <c r="AN29" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM29)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM29,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO29" s="37" t="str">
+        <v>0.21</v>
+      </c>
+      <c r="AO29" s="37" t="n">
         <f aca="false">IFERROR(IF(AN29="","",AN29*Y29),"")</f>
-        <v/>
-      </c>
-      <c r="AP29" s="35"/>
+        <v>6.7011</v>
+      </c>
+      <c r="AP29" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ29" s="19"/>
       <c r="AR29" s="26"/>
       <c r="AS29" s="41" t="str">
@@ -7873,102 +8394,154 @@
       </c>
       <c r="AU29" s="14" t="str">
         <f aca="false">IF(C29="","",IF(AP29="Open position",IF(IF(F29="Short",AND(ISNUMBER(AR29),ISNUMBER(Z29),AR29&gt;=Z29),AND(ISNUMBER(AR29),ISNUMBER(Z29),AR29&lt;=Z29)),IF(F29="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F29="Short",AND(ISNUMBER(AR29),ISNUMBER(AA29),AR29&lt;=AA29),AND(ISNUMBER(AR29),ISNUMBER(AA29),AR29&gt;=AA29)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT29),AT29&gt;182),IF(F29="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT29),AT29&gt;42,ISNUMBER(AS29),AS29&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F29="Short",AND(L29&lt;&gt;"",N(L29)&gt;0),AND(L29&lt;&gt;"",N(L29)&lt;0)),IF(F29="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP29="Closed",AP29="Dropped"),"Closed",IF(AK29="A",IF(F29="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK29="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV29" s="35"/>
-      <c r="AX29" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV29" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="AX29" s="43" t="n">
         <f aca="false">IF(AND(C29&lt;&gt;"",A29=$C$4,ISNUMBER(AJ29)),AJ29+ROW()/100000,"")</f>
-        <v/>
+        <v>13.00029</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="26"/>
+      <c r="A30" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G30" s="26" t="n">
+        <v>697.52</v>
+      </c>
       <c r="H30" s="26"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="37" t="str">
+      <c r="I30" s="36" t="n">
+        <v>19309160</v>
+      </c>
+      <c r="J30" s="37" t="n">
         <f aca="false">IF(OR(G30="",I30=""),"",G30*I30/1000000)</f>
-        <v/>
-      </c>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="38"/>
+        <v>13468.5252832</v>
+      </c>
+      <c r="K30" s="21" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="L30" s="21" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="M30" s="21" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="N30" s="25" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="O30" s="21" t="n">
+        <v>0.1508</v>
+      </c>
+      <c r="P30" s="21" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="Q30" s="21" t="n">
+        <v>-0.1055</v>
+      </c>
+      <c r="R30" s="21" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="S30" s="38" t="n">
+        <v>1.51</v>
+      </c>
       <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="26"/>
-      <c r="Z30" s="26"/>
-      <c r="AA30" s="26"/>
-      <c r="AB30" s="16" t="str">
+      <c r="U30" s="21" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="V30" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X30" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y30" s="26" t="n">
+        <v>679.69</v>
+      </c>
+      <c r="Z30" s="26" t="n">
+        <v>728.69</v>
+      </c>
+      <c r="AA30" s="26" t="n">
+        <v>532.69</v>
+      </c>
+      <c r="AB30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(F30="Short",(AND(M30&lt;&gt;"",N(M30)&lt;0))+(AND(L30&lt;&gt;"",N(L30)&lt;0))+(AND(K30&lt;&gt;"",N(K30)&lt;0))+AND(L30&lt;&gt;"",M30&lt;&gt;"",N(M30)&lt;N(L30)),(N(M30)&gt;0)+(N(L30)&gt;0)+(N(K30)&gt;0)+AND(L30&lt;&gt;"",M30&lt;&gt;"",N(M30)&gt;N(L30))))</f>
-        <v/>
-      </c>
-      <c r="AC30" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(F30="Short",IF(N30="",0,IF(AND(N30&gt;=30,N30&lt;=50),2,IF(OR(AND(N30&gt;=25,N30&lt;30),AND(N30&gt;50,N30&lt;=60)),1,0)))+IF(P30="",0,IF(AND(IF(B30="JSE",$L$5,$L$4)&lt;&gt;"",P30&lt;IF(B30="JSE",$L$5,$L$4)),2,IF(P30&lt;0,1,0))),IF(N30="",0,IF(AND(N30&gt;=50,N30&lt;=70),2,IF(OR(AND(N30&gt;=40,N30&lt;50),AND(N30&gt;70,N30&lt;=75)),1,0)))+IF(P30="",0,IF(AND(IF(B30="JSE",$L$5,$L$4)&lt;&gt;"",P30&gt;IF(B30="JSE",$L$5,$L$4)),2,IF(P30&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD30" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AD30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(F30="Short",IF(R30="",0,IF(R30&lt;=0.1,2,IF(R30&lt;=0.25,1,0))),IF(Q30="",0,IF(Q30&gt;=-0.1,2,IF(Q30&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE30" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(J30="",0,IF(J30&gt;=IF(B30="JSE",$L$7,$L$6),2,IF(J30&gt;=IF(B30="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF30" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(F30="Short",AND(T30&lt;&gt;"",N(T30)&lt;0),N(T30)&gt;0)+(N(S30)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG30" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(AL30="",0,IF(AL30&gt;=3,4,IF(AL30&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH30" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(AND(ISNUMBER(V30),ISNUMBER(A30),V30&gt;=A30,V30-A30&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI30" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(AND(F30="Short",N(U30)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ30" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="23" t="n">
         <f aca="false">IF(C30="","",SUM(AB30:AI30))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK30" s="24" t="str">
         <f aca="false">IF(C30="","",IF(AJ30&gt;=14,"A",IF(AJ30&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL30" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL30" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y30="",Z30="",AA30=""),"",IF(F30="Short",IF(Z30&lt;=Y30,"",(Y30-AA30)/(Z30-Y30)),IF(Y30&lt;=Z30,"",(AA30-Y30)/(Y30-Z30)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM30" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="37" t="n">
         <f aca="false">IF(OR(Y30="",Z30="",N(Y30)=N(Z30)),"",IF(OR(AND(F30="Short",Z30&lt;Y30),AND(NOT(F30="Short"),Z30&gt;Y30)),"stop on wrong side",ABS(Y30-Z30)))</f>
-        <v/>
-      </c>
-      <c r="AN30" s="40" t="str">
+        <v>49</v>
+      </c>
+      <c r="AN30" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM30)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM30,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO30" s="37" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="37" t="n">
         <f aca="false">IFERROR(IF(AN30="","",AN30*Y30),"")</f>
-        <v/>
-      </c>
-      <c r="AP30" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP30" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ30" s="19"/>
       <c r="AR30" s="26"/>
       <c r="AS30" s="41" t="str">
@@ -7981,102 +8554,154 @@
       </c>
       <c r="AU30" s="14" t="str">
         <f aca="false">IF(C30="","",IF(AP30="Open position",IF(IF(F30="Short",AND(ISNUMBER(AR30),ISNUMBER(Z30),AR30&gt;=Z30),AND(ISNUMBER(AR30),ISNUMBER(Z30),AR30&lt;=Z30)),IF(F30="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F30="Short",AND(ISNUMBER(AR30),ISNUMBER(AA30),AR30&lt;=AA30),AND(ISNUMBER(AR30),ISNUMBER(AA30),AR30&gt;=AA30)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT30),AT30&gt;182),IF(F30="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT30),AT30&gt;42,ISNUMBER(AS30),AS30&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F30="Short",AND(L30&lt;&gt;"",N(L30)&gt;0),AND(L30&lt;&gt;"",N(L30)&lt;0)),IF(F30="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP30="Closed",AP30="Dropped"),"Closed",IF(AK30="A",IF(F30="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK30="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV30" s="35"/>
-      <c r="AX30" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV30" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="AX30" s="43" t="n">
         <f aca="false">IF(AND(C30&lt;&gt;"",A30=$C$4,ISNUMBER(AJ30)),AJ30+ROW()/100000,"")</f>
-        <v/>
+        <v>10.0003</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="26"/>
+      <c r="A31" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" s="26" t="n">
+        <v>184.33</v>
+      </c>
       <c r="H31" s="26"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="37" t="str">
+      <c r="I31" s="36" t="n">
+        <v>6108406</v>
+      </c>
+      <c r="J31" s="37" t="n">
         <f aca="false">IF(OR(G31="",I31=""),"",G31*I31/1000000)</f>
-        <v/>
-      </c>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="21"/>
-      <c r="S31" s="38"/>
+        <v>1125.96247798</v>
+      </c>
+      <c r="K31" s="21" t="n">
+        <v>-0.0837</v>
+      </c>
+      <c r="L31" s="21" t="n">
+        <v>-0.0682</v>
+      </c>
+      <c r="M31" s="21" t="n">
+        <v>0.1283</v>
+      </c>
+      <c r="N31" s="25" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="O31" s="21" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="P31" s="21" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="Q31" s="21" t="n">
+        <v>-0.1522</v>
+      </c>
+      <c r="R31" s="21" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="S31" s="38" t="n">
+        <v>1.08</v>
+      </c>
       <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="16" t="str">
+      <c r="U31" s="21" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="V31" s="19" t="n">
+        <v>46329</v>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="X31" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y31" s="26" t="n">
+        <v>176.42</v>
+      </c>
+      <c r="Z31" s="26" t="n">
+        <v>192.82</v>
+      </c>
+      <c r="AA31" s="26" t="n">
+        <v>127.22</v>
+      </c>
+      <c r="AB31" s="16" t="n">
         <f aca="false">IF(C31="","",IF(F31="Short",(AND(M31&lt;&gt;"",N(M31)&lt;0))+(AND(L31&lt;&gt;"",N(L31)&lt;0))+(AND(K31&lt;&gt;"",N(K31)&lt;0))+AND(L31&lt;&gt;"",M31&lt;&gt;"",N(M31)&lt;N(L31)),(N(M31)&gt;0)+(N(L31)&gt;0)+(N(K31)&gt;0)+AND(L31&lt;&gt;"",M31&lt;&gt;"",N(M31)&gt;N(L31))))</f>
-        <v/>
-      </c>
-      <c r="AC31" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC31" s="16" t="n">
         <f aca="false">IF(C31="","",IF(F31="Short",IF(N31="",0,IF(AND(N31&gt;=30,N31&lt;=50),2,IF(OR(AND(N31&gt;=25,N31&lt;30),AND(N31&gt;50,N31&lt;=60)),1,0)))+IF(P31="",0,IF(AND(IF(B31="JSE",$L$5,$L$4)&lt;&gt;"",P31&lt;IF(B31="JSE",$L$5,$L$4)),2,IF(P31&lt;0,1,0))),IF(N31="",0,IF(AND(N31&gt;=50,N31&lt;=70),2,IF(OR(AND(N31&gt;=40,N31&lt;50),AND(N31&gt;70,N31&lt;=75)),1,0)))+IF(P31="",0,IF(AND(IF(B31="JSE",$L$5,$L$4)&lt;&gt;"",P31&gt;IF(B31="JSE",$L$5,$L$4)),2,IF(P31&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD31" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AD31" s="16" t="n">
         <f aca="false">IF(C31="","",IF(F31="Short",IF(R31="",0,IF(R31&lt;=0.1,2,IF(R31&lt;=0.25,1,0))),IF(Q31="",0,IF(Q31&gt;=-0.1,2,IF(Q31&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE31" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="16" t="n">
         <f aca="false">IF(C31="","",IF(J31="",0,IF(J31&gt;=IF(B31="JSE",$L$7,$L$6),2,IF(J31&gt;=IF(B31="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF31" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF31" s="16" t="n">
         <f aca="false">IF(C31="","",IF(F31="Short",AND(T31&lt;&gt;"",N(T31)&lt;0),N(T31)&gt;0)+(N(S31)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG31" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="16" t="n">
         <f aca="false">IF(C31="","",IF(AL31="",0,IF(AL31&gt;=3,4,IF(AL31&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH31" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH31" s="16" t="n">
         <f aca="false">IF(C31="","",IF(AND(ISNUMBER(V31),ISNUMBER(A31),V31&gt;=A31,V31-A31&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI31" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI31" s="16" t="n">
         <f aca="false">IF(C31="","",IF(AND(F31="Short",N(U31)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ31" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="23" t="n">
         <f aca="false">IF(C31="","",SUM(AB31:AI31))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK31" s="24" t="str">
         <f aca="false">IF(C31="","",IF(AJ31&gt;=14,"A",IF(AJ31&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL31" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL31" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y31="",Z31="",AA31=""),"",IF(F31="Short",IF(Z31&lt;=Y31,"",(Y31-AA31)/(Z31-Y31)),IF(Y31&lt;=Z31,"",(AA31-Y31)/(Y31-Z31)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM31" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="37" t="n">
         <f aca="false">IF(OR(Y31="",Z31="",N(Y31)=N(Z31)),"",IF(OR(AND(F31="Short",Z31&lt;Y31),AND(NOT(F31="Short"),Z31&gt;Y31)),"stop on wrong side",ABS(Y31-Z31)))</f>
-        <v/>
-      </c>
-      <c r="AN31" s="40" t="str">
+        <v>16.4</v>
+      </c>
+      <c r="AN31" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM31)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM31,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO31" s="37" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="AO31" s="37" t="n">
         <f aca="false">IFERROR(IF(AN31="","",AN31*Y31),"")</f>
-        <v/>
-      </c>
-      <c r="AP31" s="35"/>
+        <v>3.5284</v>
+      </c>
+      <c r="AP31" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ31" s="19"/>
       <c r="AR31" s="26"/>
       <c r="AS31" s="41" t="str">
@@ -8089,102 +8714,154 @@
       </c>
       <c r="AU31" s="14" t="str">
         <f aca="false">IF(C31="","",IF(AP31="Open position",IF(IF(F31="Short",AND(ISNUMBER(AR31),ISNUMBER(Z31),AR31&gt;=Z31),AND(ISNUMBER(AR31),ISNUMBER(Z31),AR31&lt;=Z31)),IF(F31="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F31="Short",AND(ISNUMBER(AR31),ISNUMBER(AA31),AR31&lt;=AA31),AND(ISNUMBER(AR31),ISNUMBER(AA31),AR31&gt;=AA31)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT31),AT31&gt;182),IF(F31="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT31),AT31&gt;42,ISNUMBER(AS31),AS31&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F31="Short",AND(L31&lt;&gt;"",N(L31)&gt;0),AND(L31&lt;&gt;"",N(L31)&lt;0)),IF(F31="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP31="Closed",AP31="Dropped"),"Closed",IF(AK31="A",IF(F31="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK31="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV31" s="35"/>
-      <c r="AX31" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV31" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="AX31" s="43" t="n">
         <f aca="false">IF(AND(C31&lt;&gt;"",A31=$C$4,ISNUMBER(AJ31)),AJ31+ROW()/100000,"")</f>
-        <v/>
+        <v>10.00031</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="26"/>
+      <c r="A32" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="E32" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F32" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G32" s="26" t="n">
+        <v>52.49</v>
+      </c>
       <c r="H32" s="26"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="37" t="str">
+      <c r="I32" s="36" t="n">
+        <v>7468324</v>
+      </c>
+      <c r="J32" s="37" t="n">
         <f aca="false">IF(OR(G32="",I32=""),"",G32*I32/1000000)</f>
-        <v/>
-      </c>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="21"/>
-      <c r="S32" s="38"/>
+        <v>392.01232676</v>
+      </c>
+      <c r="K32" s="21" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="L32" s="21" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="M32" s="21" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="N32" s="25" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="O32" s="21" t="n">
+        <v>0.1374</v>
+      </c>
+      <c r="P32" s="21" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="Q32" s="21" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="R32" s="21" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="S32" s="38" t="n">
+        <v>0.85</v>
+      </c>
       <c r="T32" s="21"/>
-      <c r="U32" s="21"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="35"/>
-      <c r="Y32" s="26"/>
-      <c r="Z32" s="26"/>
-      <c r="AA32" s="26"/>
-      <c r="AB32" s="16" t="str">
+      <c r="U32" s="21" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="V32" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X32" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y32" s="26" t="n">
+        <v>47.21</v>
+      </c>
+      <c r="Z32" s="26" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="AA32" s="26" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="AB32" s="16" t="n">
         <f aca="false">IF(C32="","",IF(F32="Short",(AND(M32&lt;&gt;"",N(M32)&lt;0))+(AND(L32&lt;&gt;"",N(L32)&lt;0))+(AND(K32&lt;&gt;"",N(K32)&lt;0))+AND(L32&lt;&gt;"",M32&lt;&gt;"",N(M32)&lt;N(L32)),(N(M32)&gt;0)+(N(L32)&gt;0)+(N(K32)&gt;0)+AND(L32&lt;&gt;"",M32&lt;&gt;"",N(M32)&gt;N(L32))))</f>
-        <v/>
-      </c>
-      <c r="AC32" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="16" t="n">
         <f aca="false">IF(C32="","",IF(F32="Short",IF(N32="",0,IF(AND(N32&gt;=30,N32&lt;=50),2,IF(OR(AND(N32&gt;=25,N32&lt;30),AND(N32&gt;50,N32&lt;=60)),1,0)))+IF(P32="",0,IF(AND(IF(B32="JSE",$L$5,$L$4)&lt;&gt;"",P32&lt;IF(B32="JSE",$L$5,$L$4)),2,IF(P32&lt;0,1,0))),IF(N32="",0,IF(AND(N32&gt;=50,N32&lt;=70),2,IF(OR(AND(N32&gt;=40,N32&lt;50),AND(N32&gt;70,N32&lt;=75)),1,0)))+IF(P32="",0,IF(AND(IF(B32="JSE",$L$5,$L$4)&lt;&gt;"",P32&gt;IF(B32="JSE",$L$5,$L$4)),2,IF(P32&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD32" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="16" t="n">
         <f aca="false">IF(C32="","",IF(F32="Short",IF(R32="",0,IF(R32&lt;=0.1,2,IF(R32&lt;=0.25,1,0))),IF(Q32="",0,IF(Q32&gt;=-0.1,2,IF(Q32&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE32" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="16" t="n">
         <f aca="false">IF(C32="","",IF(J32="",0,IF(J32&gt;=IF(B32="JSE",$L$7,$L$6),2,IF(J32&gt;=IF(B32="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF32" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF32" s="16" t="n">
         <f aca="false">IF(C32="","",IF(F32="Short",AND(T32&lt;&gt;"",N(T32)&lt;0),N(T32)&gt;0)+(N(S32)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG32" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="16" t="n">
         <f aca="false">IF(C32="","",IF(AL32="",0,IF(AL32&gt;=3,4,IF(AL32&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH32" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="16" t="n">
         <f aca="false">IF(C32="","",IF(AND(ISNUMBER(V32),ISNUMBER(A32),V32&gt;=A32,V32-A32&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI32" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="16" t="n">
         <f aca="false">IF(C32="","",IF(AND(F32="Short",N(U32)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ32" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="23" t="n">
         <f aca="false">IF(C32="","",SUM(AB32:AI32))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="AK32" s="24" t="str">
         <f aca="false">IF(C32="","",IF(AJ32&gt;=14,"A",IF(AJ32&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL32" s="39" t="str">
+        <v>C</v>
+      </c>
+      <c r="AL32" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y32="",Z32="",AA32=""),"",IF(F32="Short",IF(Z32&lt;=Y32,"",(Y32-AA32)/(Z32-Y32)),IF(Y32&lt;=Z32,"",(AA32-Y32)/(Y32-Z32)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM32" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="37" t="n">
         <f aca="false">IF(OR(Y32="",Z32="",N(Y32)=N(Z32)),"",IF(OR(AND(F32="Short",Z32&lt;Y32),AND(NOT(F32="Short"),Z32&gt;Y32)),"stop on wrong side",ABS(Y32-Z32)))</f>
-        <v/>
-      </c>
-      <c r="AN32" s="40" t="str">
+        <v>2.64</v>
+      </c>
+      <c r="AN32" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM32)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM32,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO32" s="37" t="str">
+        <v>0.17</v>
+      </c>
+      <c r="AO32" s="37" t="n">
         <f aca="false">IFERROR(IF(AN32="","",AN32*Y32),"")</f>
-        <v/>
-      </c>
-      <c r="AP32" s="35"/>
+        <v>8.0257</v>
+      </c>
+      <c r="AP32" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ32" s="19"/>
       <c r="AR32" s="26"/>
       <c r="AS32" s="41" t="str">
@@ -8197,102 +8874,156 @@
       </c>
       <c r="AU32" s="14" t="str">
         <f aca="false">IF(C32="","",IF(AP32="Open position",IF(IF(F32="Short",AND(ISNUMBER(AR32),ISNUMBER(Z32),AR32&gt;=Z32),AND(ISNUMBER(AR32),ISNUMBER(Z32),AR32&lt;=Z32)),IF(F32="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F32="Short",AND(ISNUMBER(AR32),ISNUMBER(AA32),AR32&lt;=AA32),AND(ISNUMBER(AR32),ISNUMBER(AA32),AR32&gt;=AA32)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT32),AT32&gt;182),IF(F32="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT32),AT32&gt;42,ISNUMBER(AS32),AS32&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F32="Short",AND(L32&lt;&gt;"",N(L32)&gt;0),AND(L32&lt;&gt;"",N(L32)&lt;0)),IF(F32="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP32="Closed",AP32="Dropped"),"Closed",IF(AK32="A",IF(F32="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK32="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV32" s="35"/>
-      <c r="AX32" s="43" t="str">
+        <v>Drop or re-check next week</v>
+      </c>
+      <c r="AV32" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="AX32" s="43" t="n">
         <f aca="false">IF(AND(C32&lt;&gt;"",A32=$C$4,ISNUMBER(AJ32)),AJ32+ROW()/100000,"")</f>
-        <v/>
+        <v>6.00032</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="26"/>
+      <c r="A33" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G33" s="26" t="n">
+        <v>552.72</v>
+      </c>
       <c r="H33" s="26"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="37" t="str">
+      <c r="I33" s="36" t="n">
+        <v>22280195</v>
+      </c>
+      <c r="J33" s="37" t="n">
         <f aca="false">IF(OR(G33="",I33=""),"",G33*I33/1000000)</f>
-        <v/>
-      </c>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="25"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="38"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="21"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="35"/>
-      <c r="Y33" s="26"/>
-      <c r="Z33" s="26"/>
-      <c r="AA33" s="26"/>
-      <c r="AB33" s="16" t="str">
+        <v>12314.7093804</v>
+      </c>
+      <c r="K33" s="21" t="n">
+        <v>-0.0772</v>
+      </c>
+      <c r="L33" s="21" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="M33" s="21" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="N33" s="25" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="O33" s="21" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="P33" s="21" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="Q33" s="21" t="n">
+        <v>-0.1607</v>
+      </c>
+      <c r="R33" s="21" t="n">
+        <v>1.9366</v>
+      </c>
+      <c r="S33" s="38" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="T33" s="21" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="U33" s="21" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="V33" s="19" t="n">
+        <v>46329</v>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="X33" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y33" s="26" t="n">
+        <v>523.55</v>
+      </c>
+      <c r="Z33" s="26" t="n">
+        <v>576.65</v>
+      </c>
+      <c r="AA33" s="26" t="n">
+        <v>364.25</v>
+      </c>
+      <c r="AB33" s="16" t="n">
         <f aca="false">IF(C33="","",IF(F33="Short",(AND(M33&lt;&gt;"",N(M33)&lt;0))+(AND(L33&lt;&gt;"",N(L33)&lt;0))+(AND(K33&lt;&gt;"",N(K33)&lt;0))+AND(L33&lt;&gt;"",M33&lt;&gt;"",N(M33)&lt;N(L33)),(N(M33)&gt;0)+(N(L33)&gt;0)+(N(K33)&gt;0)+AND(L33&lt;&gt;"",M33&lt;&gt;"",N(M33)&gt;N(L33))))</f>
-        <v/>
-      </c>
-      <c r="AC33" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="16" t="n">
         <f aca="false">IF(C33="","",IF(F33="Short",IF(N33="",0,IF(AND(N33&gt;=30,N33&lt;=50),2,IF(OR(AND(N33&gt;=25,N33&lt;30),AND(N33&gt;50,N33&lt;=60)),1,0)))+IF(P33="",0,IF(AND(IF(B33="JSE",$L$5,$L$4)&lt;&gt;"",P33&lt;IF(B33="JSE",$L$5,$L$4)),2,IF(P33&lt;0,1,0))),IF(N33="",0,IF(AND(N33&gt;=50,N33&lt;=70),2,IF(OR(AND(N33&gt;=40,N33&lt;50),AND(N33&gt;70,N33&lt;=75)),1,0)))+IF(P33="",0,IF(AND(IF(B33="JSE",$L$5,$L$4)&lt;&gt;"",P33&gt;IF(B33="JSE",$L$5,$L$4)),2,IF(P33&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD33" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AD33" s="16" t="n">
         <f aca="false">IF(C33="","",IF(F33="Short",IF(R33="",0,IF(R33&lt;=0.1,2,IF(R33&lt;=0.25,1,0))),IF(Q33="",0,IF(Q33&gt;=-0.1,2,IF(Q33&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE33" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="16" t="n">
         <f aca="false">IF(C33="","",IF(J33="",0,IF(J33&gt;=IF(B33="JSE",$L$7,$L$6),2,IF(J33&gt;=IF(B33="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF33" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF33" s="16" t="n">
         <f aca="false">IF(C33="","",IF(F33="Short",AND(T33&lt;&gt;"",N(T33)&lt;0),N(T33)&gt;0)+(N(S33)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG33" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="16" t="n">
         <f aca="false">IF(C33="","",IF(AL33="",0,IF(AL33&gt;=3,4,IF(AL33&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH33" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH33" s="16" t="n">
         <f aca="false">IF(C33="","",IF(AND(ISNUMBER(V33),ISNUMBER(A33),V33&gt;=A33,V33-A33&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI33" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI33" s="16" t="n">
         <f aca="false">IF(C33="","",IF(AND(F33="Short",N(U33)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ33" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="23" t="n">
         <f aca="false">IF(C33="","",SUM(AB33:AI33))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK33" s="24" t="str">
         <f aca="false">IF(C33="","",IF(AJ33&gt;=14,"A",IF(AJ33&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL33" s="39" t="str">
+        <v>C</v>
+      </c>
+      <c r="AL33" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y33="",Z33="",AA33=""),"",IF(F33="Short",IF(Z33&lt;=Y33,"",(Y33-AA33)/(Z33-Y33)),IF(Y33&lt;=Z33,"",(AA33-Y33)/(Y33-Z33)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM33" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="37" t="n">
         <f aca="false">IF(OR(Y33="",Z33="",N(Y33)=N(Z33)),"",IF(OR(AND(F33="Short",Z33&lt;Y33),AND(NOT(F33="Short"),Z33&gt;Y33)),"stop on wrong side",ABS(Y33-Z33)))</f>
-        <v/>
-      </c>
-      <c r="AN33" s="40" t="str">
+        <v>53.1</v>
+      </c>
+      <c r="AN33" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM33)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM33,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO33" s="37" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="37" t="n">
         <f aca="false">IFERROR(IF(AN33="","",AN33*Y33),"")</f>
-        <v/>
-      </c>
-      <c r="AP33" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP33" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ33" s="19"/>
       <c r="AR33" s="26"/>
       <c r="AS33" s="41" t="str">
@@ -8305,102 +9036,154 @@
       </c>
       <c r="AU33" s="14" t="str">
         <f aca="false">IF(C33="","",IF(AP33="Open position",IF(IF(F33="Short",AND(ISNUMBER(AR33),ISNUMBER(Z33),AR33&gt;=Z33),AND(ISNUMBER(AR33),ISNUMBER(Z33),AR33&lt;=Z33)),IF(F33="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F33="Short",AND(ISNUMBER(AR33),ISNUMBER(AA33),AR33&lt;=AA33),AND(ISNUMBER(AR33),ISNUMBER(AA33),AR33&gt;=AA33)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT33),AT33&gt;182),IF(F33="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT33),AT33&gt;42,ISNUMBER(AS33),AS33&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F33="Short",AND(L33&lt;&gt;"",N(L33)&gt;0),AND(L33&lt;&gt;"",N(L33)&lt;0)),IF(F33="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP33="Closed",AP33="Dropped"),"Closed",IF(AK33="A",IF(F33="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK33="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV33" s="35"/>
-      <c r="AX33" s="43" t="str">
+        <v>Drop or re-check next week</v>
+      </c>
+      <c r="AV33" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="AX33" s="43" t="n">
         <f aca="false">IF(AND(C33&lt;&gt;"",A33=$C$4,ISNUMBER(AJ33)),AJ33+ROW()/100000,"")</f>
-        <v/>
+        <v>7.00033</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="26"/>
+      <c r="A34" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G34" s="26" t="n">
+        <v>288.96</v>
+      </c>
       <c r="H34" s="26"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="37" t="str">
+      <c r="I34" s="36" t="n">
+        <v>891537</v>
+      </c>
+      <c r="J34" s="37" t="n">
         <f aca="false">IF(OR(G34="",I34=""),"",G34*I34/1000000)</f>
-        <v/>
-      </c>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
-      <c r="R34" s="21"/>
-      <c r="S34" s="38"/>
+        <v>257.61853152</v>
+      </c>
+      <c r="K34" s="21" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="L34" s="21" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="M34" s="21" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="N34" s="25" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="O34" s="21" t="n">
+        <v>-0.0303</v>
+      </c>
+      <c r="P34" s="21" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="Q34" s="21" t="n">
+        <v>-0.0577</v>
+      </c>
+      <c r="R34" s="21" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="S34" s="38" t="n">
+        <v>2.87</v>
+      </c>
       <c r="T34" s="21"/>
-      <c r="U34" s="21"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="35"/>
-      <c r="Y34" s="26"/>
-      <c r="Z34" s="26"/>
-      <c r="AA34" s="26"/>
-      <c r="AB34" s="16" t="str">
+      <c r="U34" s="21" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="V34" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X34" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y34" s="26" t="n">
+        <v>274.58</v>
+      </c>
+      <c r="Z34" s="26" t="n">
+        <v>288.58</v>
+      </c>
+      <c r="AA34" s="26" t="n">
+        <v>232.58</v>
+      </c>
+      <c r="AB34" s="16" t="n">
         <f aca="false">IF(C34="","",IF(F34="Short",(AND(M34&lt;&gt;"",N(M34)&lt;0))+(AND(L34&lt;&gt;"",N(L34)&lt;0))+(AND(K34&lt;&gt;"",N(K34)&lt;0))+AND(L34&lt;&gt;"",M34&lt;&gt;"",N(M34)&lt;N(L34)),(N(M34)&gt;0)+(N(L34)&gt;0)+(N(K34)&gt;0)+AND(L34&lt;&gt;"",M34&lt;&gt;"",N(M34)&gt;N(L34))))</f>
-        <v/>
-      </c>
-      <c r="AC34" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="16" t="n">
         <f aca="false">IF(C34="","",IF(F34="Short",IF(N34="",0,IF(AND(N34&gt;=30,N34&lt;=50),2,IF(OR(AND(N34&gt;=25,N34&lt;30),AND(N34&gt;50,N34&lt;=60)),1,0)))+IF(P34="",0,IF(AND(IF(B34="JSE",$L$5,$L$4)&lt;&gt;"",P34&lt;IF(B34="JSE",$L$5,$L$4)),2,IF(P34&lt;0,1,0))),IF(N34="",0,IF(AND(N34&gt;=50,N34&lt;=70),2,IF(OR(AND(N34&gt;=40,N34&lt;50),AND(N34&gt;70,N34&lt;=75)),1,0)))+IF(P34="",0,IF(AND(IF(B34="JSE",$L$5,$L$4)&lt;&gt;"",P34&gt;IF(B34="JSE",$L$5,$L$4)),2,IF(P34&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD34" s="16" t="str">
+        <v>3</v>
+      </c>
+      <c r="AD34" s="16" t="n">
         <f aca="false">IF(C34="","",IF(F34="Short",IF(R34="",0,IF(R34&lt;=0.1,2,IF(R34&lt;=0.25,1,0))),IF(Q34="",0,IF(Q34&gt;=-0.1,2,IF(Q34&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE34" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="16" t="n">
         <f aca="false">IF(C34="","",IF(J34="",0,IF(J34&gt;=IF(B34="JSE",$L$7,$L$6),2,IF(J34&gt;=IF(B34="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF34" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF34" s="16" t="n">
         <f aca="false">IF(C34="","",IF(F34="Short",AND(T34&lt;&gt;"",N(T34)&lt;0),N(T34)&gt;0)+(N(S34)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG34" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="16" t="n">
         <f aca="false">IF(C34="","",IF(AL34="",0,IF(AL34&gt;=3,4,IF(AL34&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH34" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH34" s="16" t="n">
         <f aca="false">IF(C34="","",IF(AND(ISNUMBER(V34),ISNUMBER(A34),V34&gt;=A34,V34-A34&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI34" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI34" s="16" t="n">
         <f aca="false">IF(C34="","",IF(AND(F34="Short",N(U34)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ34" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="23" t="n">
         <f aca="false">IF(C34="","",SUM(AB34:AI34))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AK34" s="24" t="str">
         <f aca="false">IF(C34="","",IF(AJ34&gt;=14,"A",IF(AJ34&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL34" s="39" t="str">
+        <v>C</v>
+      </c>
+      <c r="AL34" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y34="",Z34="",AA34=""),"",IF(F34="Short",IF(Z34&lt;=Y34,"",(Y34-AA34)/(Z34-Y34)),IF(Y34&lt;=Z34,"",(AA34-Y34)/(Y34-Z34)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM34" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="37" t="n">
         <f aca="false">IF(OR(Y34="",Z34="",N(Y34)=N(Z34)),"",IF(OR(AND(F34="Short",Z34&lt;Y34),AND(NOT(F34="Short"),Z34&gt;Y34)),"stop on wrong side",ABS(Y34-Z34)))</f>
-        <v/>
-      </c>
-      <c r="AN34" s="40" t="str">
+        <v>14</v>
+      </c>
+      <c r="AN34" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM34)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM34,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO34" s="37" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="AO34" s="37" t="n">
         <f aca="false">IFERROR(IF(AN34="","",AN34*Y34),"")</f>
-        <v/>
-      </c>
-      <c r="AP34" s="35"/>
+        <v>8.2374</v>
+      </c>
+      <c r="AP34" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ34" s="19"/>
       <c r="AR34" s="26"/>
       <c r="AS34" s="41" t="str">
@@ -8413,12 +9196,14 @@
       </c>
       <c r="AU34" s="14" t="str">
         <f aca="false">IF(C34="","",IF(AP34="Open position",IF(IF(F34="Short",AND(ISNUMBER(AR34),ISNUMBER(Z34),AR34&gt;=Z34),AND(ISNUMBER(AR34),ISNUMBER(Z34),AR34&lt;=Z34)),IF(F34="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F34="Short",AND(ISNUMBER(AR34),ISNUMBER(AA34),AR34&lt;=AA34),AND(ISNUMBER(AR34),ISNUMBER(AA34),AR34&gt;=AA34)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT34),AT34&gt;182),IF(F34="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT34),AT34&gt;42,ISNUMBER(AS34),AS34&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F34="Short",AND(L34&lt;&gt;"",N(L34)&gt;0),AND(L34&lt;&gt;"",N(L34)&lt;0)),IF(F34="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP34="Closed",AP34="Dropped"),"Closed",IF(AK34="A",IF(F34="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK34="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV34" s="35"/>
-      <c r="AX34" s="43" t="str">
+        <v>Drop or re-check next week</v>
+      </c>
+      <c r="AV34" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="AX34" s="43" t="n">
         <f aca="false">IF(AND(C34&lt;&gt;"",A34=$C$4,ISNUMBER(AJ34)),AJ34+ROW()/100000,"")</f>
-        <v/>
+        <v>8.00034</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27577,7 +28362,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I68"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
@@ -27591,7 +28376,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -27602,7 +28387,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -27615,7 +28400,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -27628,7 +28413,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -27638,12 +28423,12 @@
       <c r="G5" s="44"/>
       <c r="H5" s="44"/>
       <c r="I5" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44"/>
@@ -27653,12 +28438,12 @@
       <c r="G6" s="44"/>
       <c r="H6" s="44"/>
       <c r="I6" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B7" s="44"/>
       <c r="C7" s="44"/>
@@ -27668,12 +28453,12 @@
       <c r="G7" s="44"/>
       <c r="H7" s="44"/>
       <c r="I7" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="B8" s="44"/>
       <c r="C8" s="44"/>
@@ -27683,12 +28468,12 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="B9" s="44"/>
       <c r="C9" s="44"/>
@@ -27698,12 +28483,12 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -27713,12 +28498,12 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="B11" s="44"/>
       <c r="C11" s="44"/>
@@ -27728,12 +28513,12 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
@@ -27743,12 +28528,12 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -27758,12 +28543,12 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -27779,39 +28564,39 @@
         <v>33</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>35</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="n">
         <v>46298</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D17" s="15" t="str">
         <f aca="false">IF(OR(B17="",C17=""),"",IF(AND(B17="Y",C17="Y"),"RISK-ON → favour longs",IF(AND(B17="N",C17="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
@@ -27829,21 +28614,21 @@
         <v>0</v>
       </c>
       <c r="H17" s="47" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="I17" s="47" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="n">
         <v>46312</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D18" s="15" t="str">
         <f aca="false">IF(OR(B18="",C18=""),"",IF(AND(B18="Y",C18="Y"),"RISK-ON → favour longs",IF(AND(B18="N",C18="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
@@ -27861,31 +28646,37 @@
         <v>0</v>
       </c>
       <c r="H18" s="47" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="I18" s="47" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="n">
+        <v>46316</v>
+      </c>
       <c r="B19" s="46"/>
       <c r="C19" s="46"/>
       <c r="D19" s="15" t="str">
         <f aca="false">IF(OR(B19="",C19=""),"",IF(AND(B19="Y",C19="Y"),"RISK-ON → favour longs",IF(AND(B19="N",C19="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
         <v/>
       </c>
-      <c r="E19" s="15" t="str">
+      <c r="E19" s="15" t="n">
         <f aca="false">IF(A19="","",COUNTIFS('Swing Watchlist'!$A$11:$A$210,A19,'Swing Watchlist'!$C$11:$C$210,"?*"))</f>
-        <v/>
-      </c>
-      <c r="F19" s="15" t="str">
+        <v>13</v>
+      </c>
+      <c r="F19" s="15" t="n">
         <f aca="false">IF(A19="","",COUNTIFS('Swing Watchlist'!$A$11:$A$210,A19,'Swing Watchlist'!$AK$11:$AK$210,"A"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="47"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="47" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
+      <c r="I19" s="47" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19"/>
@@ -28927,7 +29718,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="16"/>
@@ -28935,7 +29726,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -28945,7 +29736,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -28957,7 +29748,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -28969,10 +29760,10 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -28983,10 +29774,10 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -28997,10 +29788,10 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -29011,10 +29802,10 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -29025,10 +29816,10 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -29039,10 +29830,10 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -29053,10 +29844,10 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -29067,7 +29858,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -29079,10 +29870,10 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -29093,10 +29884,10 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -29107,10 +29898,10 @@
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -29121,10 +29912,10 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -29135,10 +29926,10 @@
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -29149,10 +29940,10 @@
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -29163,10 +29954,10 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -29180,7 +29971,7 @@
         <v>88</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -29191,7 +29982,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -29203,10 +29994,10 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -29217,10 +30008,10 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -29231,10 +30022,10 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -29287,7 +30078,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AP158"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
@@ -29318,7 +30109,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -29360,7 +30151,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -29404,20 +30195,20 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="19" t="n">
         <v>46296</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
       <c r="J4" s="22" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="K4" s="22"/>
       <c r="L4" s="23" t="n">
@@ -29433,20 +30224,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="25" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="E5" s="20"/>
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
       <c r="J5" s="22" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="K5" s="22"/>
       <c r="L5" s="24" t="str">
@@ -29456,7 +30247,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="27"/>
@@ -29481,7 +30272,7 @@
       <c r="V7" s="27"/>
       <c r="W7" s="27"/>
       <c r="X7" s="28" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="Y7" s="28"/>
       <c r="Z7" s="28"/>
@@ -29493,10 +30284,10 @@
       <c r="AF7" s="28"/>
       <c r="AG7" s="28"/>
       <c r="AH7" s="48" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="AI7" s="30" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="AJ7" s="30"/>
       <c r="AK7" s="30"/>
@@ -29527,79 +30318,79 @@
         <v>146</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="I8" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>336</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>338</v>
+      </c>
+      <c r="M8" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="O8" s="31" t="s">
+        <v>341</v>
+      </c>
+      <c r="P8" s="31" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q8" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="R8" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="S8" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="T8" s="31" t="s">
+        <v>346</v>
+      </c>
+      <c r="U8" s="31" t="s">
+        <v>347</v>
+      </c>
+      <c r="V8" s="31" t="s">
+        <v>348</v>
+      </c>
+      <c r="W8" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="X8" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y8" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="Z8" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="J8" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="K8" s="31" t="s">
+      <c r="AA8" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="L8" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="M8" s="31" t="s">
+      <c r="AB8" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="N8" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="O8" s="31" t="s">
+      <c r="AC8" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="P8" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q8" s="31" t="s">
-        <v>312</v>
-      </c>
-      <c r="R8" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="S8" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="T8" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="U8" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="V8" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="W8" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="X8" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="Y8" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="Z8" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="AA8" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="AB8" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC8" s="32" t="s">
-        <v>279</v>
-      </c>
       <c r="AD8" s="32" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="AE8" s="32" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="AF8" s="32" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="AG8" s="32" t="s">
         <v>51</v>
@@ -29611,19 +30402,19 @@
         <v>172</v>
       </c>
       <c r="AJ8" s="34" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="AK8" s="34" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="AL8" s="34" t="s">
         <v>174</v>
       </c>
       <c r="AM8" s="34" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="AN8" s="34" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29741,10 +30532,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI9" s="35" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="AJ9" s="35" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="AK9" s="19" t="n">
         <v>46309</v>
@@ -29757,7 +30548,7 @@
         <v>0</v>
       </c>
       <c r="AN9" s="35" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="AP9" s="43" t="n">
         <f aca="false">IF(AND(C9&lt;&gt;"",A9=$C$4,ISNUMBER(AF9)),AF9+ROW()/100000,"")</f>
@@ -29879,10 +30670,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI10" s="35" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="AJ10" s="35" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="AK10" s="19" t="n">
         <v>46309</v>
@@ -29895,7 +30686,7 @@
         <v>0</v>
       </c>
       <c r="AN10" s="35" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="AP10" s="43" t="n">
         <f aca="false">IF(AND(C10&lt;&gt;"",A10=$C$4,ISNUMBER(AF10)),AF10+ROW()/100000,"")</f>
@@ -30015,10 +30806,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI11" s="35" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="AJ11" s="35" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="AK11" s="19" t="n">
         <v>46309</v>
@@ -30031,7 +30822,7 @@
         <v>0</v>
       </c>
       <c r="AN11" s="35" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="AP11" s="43" t="n">
         <f aca="false">IF(AND(C11&lt;&gt;"",A11=$C$4,ISNUMBER(AF11)),AF11+ROW()/100000,"")</f>
@@ -30154,7 +30945,7 @@
         <v>192</v>
       </c>
       <c r="AJ12" s="35" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="AK12" s="19" t="n">
         <v>46309</v>
@@ -30167,7 +30958,7 @@
         <v>0</v>
       </c>
       <c r="AN12" s="35" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="AP12" s="43" t="n">
         <f aca="false">IF(AND(C12&lt;&gt;"",A12=$C$4,ISNUMBER(AF12)),AF12+ROW()/100000,"")</f>
@@ -30182,13 +30973,13 @@
         <v>179</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>335</v>
+        <v>243</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>762.5</v>
@@ -30292,7 +31083,7 @@
         <v>192</v>
       </c>
       <c r="AJ13" s="35" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="AK13" s="19" t="n">
         <v>46309</v>
@@ -30305,7 +31096,7 @@
         <v>0</v>
       </c>
       <c r="AN13" s="35" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="AP13" s="43" t="n">
         <f aca="false">IF(AND(C13&lt;&gt;"",A13=$C$4,ISNUMBER(AF13)),AF13+ROW()/100000,"")</f>
@@ -30423,10 +31214,10 @@
         <v>Closed</v>
       </c>
       <c r="AI14" s="35" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="AJ14" s="35" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="AK14" s="19" t="n">
         <v>46309</v>
@@ -30439,7 +31230,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="35" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="AP14" s="43" t="n">
         <f aca="false">IF(AND(C14&lt;&gt;"",A14=$C$4,ISNUMBER(AF14)),AF14+ROW()/100000,"")</f>
@@ -30555,10 +31346,10 @@
         <v>Closed</v>
       </c>
       <c r="AI15" s="35" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="AJ15" s="35" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="AK15" s="19" t="n">
         <v>46309</v>
@@ -30571,7 +31362,7 @@
         <v>0</v>
       </c>
       <c r="AN15" s="35" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="AP15" s="43" t="n">
         <f aca="false">IF(AND(C15&lt;&gt;"",A15=$C$4,ISNUMBER(AF15)),AF15+ROW()/100000,"")</f>
@@ -30687,10 +31478,10 @@
         <v>Closed</v>
       </c>
       <c r="AI16" s="35" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="AJ16" s="35" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="AK16" s="19" t="n">
         <v>46309</v>
@@ -30703,7 +31494,7 @@
         <v>0</v>
       </c>
       <c r="AN16" s="35" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="AP16" s="43" t="n">
         <f aca="false">IF(AND(C16&lt;&gt;"",A16=$C$4,ISNUMBER(AF16)),AF16+ROW()/100000,"")</f>
@@ -30823,10 +31614,10 @@
         <v>Closed</v>
       </c>
       <c r="AI17" s="35" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="AJ17" s="35" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="AK17" s="19" t="n">
         <v>46309</v>
@@ -30839,7 +31630,7 @@
         <v>0</v>
       </c>
       <c r="AN17" s="35" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="AP17" s="43" t="n">
         <f aca="false">IF(AND(C17&lt;&gt;"",A17=$C$4,ISNUMBER(AF17)),AF17+ROW()/100000,"")</f>
@@ -30959,10 +31750,10 @@
         <v>Closed</v>
       </c>
       <c r="AI18" s="35" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="AJ18" s="35" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="AK18" s="19" t="n">
         <v>46309</v>
@@ -30975,7 +31766,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="35" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AP18" s="43" t="n">
         <f aca="false">IF(AND(C18&lt;&gt;"",A18=$C$4,ISNUMBER(AF18)),AF18+ROW()/100000,"")</f>
@@ -42552,7 +43343,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
@@ -42564,7 +43355,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -42573,7 +43364,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -42584,7 +43375,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -42595,7 +43386,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -42603,12 +43394,12 @@
       <c r="E5" s="44"/>
       <c r="F5" s="44"/>
       <c r="G5" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44"/>
@@ -42616,12 +43407,12 @@
       <c r="E6" s="44"/>
       <c r="F6" s="44"/>
       <c r="G6" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="B7" s="44"/>
       <c r="C7" s="44"/>
@@ -42629,12 +43420,12 @@
       <c r="E7" s="44"/>
       <c r="F7" s="44"/>
       <c r="G7" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="B8" s="44"/>
       <c r="C8" s="44"/>
@@ -42642,12 +43433,12 @@
       <c r="E8" s="44"/>
       <c r="F8" s="44"/>
       <c r="G8" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="B9" s="44"/>
       <c r="C9" s="44"/>
@@ -42655,12 +43446,12 @@
       <c r="E9" s="44"/>
       <c r="F9" s="44"/>
       <c r="G9" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -42668,12 +43459,12 @@
       <c r="E10" s="44"/>
       <c r="F10" s="44"/>
       <c r="G10" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="B11" s="44"/>
       <c r="C11" s="44"/>
@@ -42681,12 +43472,12 @@
       <c r="E11" s="44"/>
       <c r="F11" s="44"/>
       <c r="G11" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
@@ -42694,12 +43485,12 @@
       <c r="E12" s="44"/>
       <c r="F12" s="44"/>
       <c r="G12" s="45" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -42707,12 +43498,12 @@
       <c r="E13" s="44"/>
       <c r="F13" s="44"/>
       <c r="G13" s="45" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -42729,22 +43520,22 @@
         <v>35</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>43</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="n">
         <v>46296</v>
       </c>
@@ -42757,16 +43548,16 @@
         <v>5</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="G17" s="47" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43159,7 +43950,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -43168,7 +43959,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -43176,7 +43967,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -43186,7 +43977,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -43196,587 +43987,587 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="52" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="52" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="52" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="52" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="52" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>403</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F15" s="52" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="52" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>419</v>
+        <v>449</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E18" s="52" t="s">
+        <v>456</v>
+      </c>
+      <c r="F18" s="52" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="52" t="s">
+        <v>429</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C19" s="52" t="s">
         <v>426</v>
       </c>
-      <c r="F18" s="52" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="52" t="s">
-        <v>399</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>396</v>
-      </c>
       <c r="D19" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="F19" s="52" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="D21" s="52" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="E22" s="52" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="F22" s="52" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D24" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E24" s="52" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F24" s="52" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="52" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E25" s="52" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="52" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="E26" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="52" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="C27" s="52" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="D27" s="52" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="E27" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="52" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="E28" s="52" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="F28" s="52" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="52" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="52" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="C30" s="52" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="E30" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F30" s="52" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="52" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>152</v>
       </c>
       <c r="C31" s="52" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="D31" s="52" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="52" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="C32" s="52" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="D32" s="52" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="E32" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F32" s="52" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="52" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="D33" s="52" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="53" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="B34" s="53"/>
       <c r="C34" s="53"/>
@@ -43786,7 +44577,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -43796,10 +44587,10 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="54" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -43808,10 +44599,10 @@
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="54" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -43820,7 +44611,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -43830,92 +44621,92 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="55" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="B42" s="55"/>
       <c r="C42" s="52" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="D42" s="52" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="E42" s="52" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="F42" s="52" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="55" t="s">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="B43" s="55"/>
       <c r="C43" s="52" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="D43" s="52" t="s">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="E43" s="52" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="F43" s="52" t="s">
-        <v>499</v>
+        <v>529</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="55" t="s">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="B44" s="55"/>
       <c r="C44" s="52" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="D44" s="52" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="E44" s="52" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="F44" s="52" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="55" t="s">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="B45" s="55"/>
       <c r="C45" s="52" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="D45" s="52" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="E45" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F45" s="52" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -43924,139 +44715,139 @@
       </c>
       <c r="B46" s="55"/>
       <c r="C46" s="52" t="s">
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="D46" s="52" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="E46" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F46" s="52" t="s">
-        <v>511</v>
+        <v>541</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="55" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="B47" s="55"/>
       <c r="C47" s="52" t="s">
-        <v>513</v>
+        <v>543</v>
       </c>
       <c r="D47" s="52" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="E47" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="55" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="B48" s="55"/>
       <c r="C48" s="52" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
       <c r="D48" s="52" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="E48" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="F48" s="52" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="55" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="B49" s="55"/>
       <c r="C49" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D49" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E49" s="52" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="F49" s="52" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="55" t="s">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="B50" s="55"/>
       <c r="C50" s="52" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="D50" s="52" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="E50" s="52" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="F50" s="52" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="55" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="B51" s="55"/>
       <c r="C51" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="D51" s="52" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E51" s="52" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="F51" s="52" t="s">
-        <v>529</v>
+        <v>559</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="55" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="B52" s="55"/>
       <c r="C52" s="52" t="s">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="D52" s="52" t="s">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="E52" s="52" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="F52" s="52" t="s">
-        <v>534</v>
+        <v>564</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="55" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="B53" s="55"/>
       <c r="C53" s="52" t="s">
-        <v>535</v>
+        <v>565</v>
       </c>
       <c r="D53" s="52" t="s">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="E53" s="52" t="s">
-        <v>537</v>
+        <v>567</v>
       </c>
       <c r="F53" s="52"/>
     </row>

--- a/templates/LRC_Watchlist_master.xlsx
+++ b/templates/LRC_Watchlist_master.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="566">
   <si>
     <t xml:space="preserve">LRC Watchlist Builder — Swing &amp; Investment</t>
   </si>
@@ -707,430 +707,340 @@
     <t xml:space="preserve">Trigger: Sell stop below the 15-day low (49.11) — only AFTER the 14 Oct results are digested. Short entry 49.00, stop 50.96 (2×ATR 0.98), target 43.12 (3R). LRC Work-sheet 14 Oct: SELL (6-m target ~$38.37, -25%; score 3.5/5; technical: CLEARED — STAGED ENTRY). SELL (−25%) + technical clearance. Results 14 Oct (today) — wait for the reaction. 5th short: house limit is 4 open shorts, so only if one of the others has not triggered. Data 13 Oct close: stockanalysis statistics + daily history to 13 Oct (SMA20/ATR14 computed); Perf Half vs ~13 Apr close; EPS growth this yr = consensus current FY (adjusted). Perf Quarter n/f (history page holds 50 sessions). Finviz itself blocked for us — same filters applied manually. — P. Nkuna</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating BUY (6-m value 262.56); CLEARED. Entry 222.63, stop 210.83 (2×ATR), target 258.03 (3R).  — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intuit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating BUY (6-m value 426.0); NOT CLEARED. Entry 342.47, stop 318.21 (2×ATR), target 415.25 (3R).  — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deckers Outdoor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating BUY (6-m value 103.0); NOT CLEARED — results within 14 days. Entry 88.16, stop 83.18 (2×ATR), target 103.1 (3R). Results 2026-10-22 — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOOGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alphabet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 319.72); CLEARED — results within 14 days. Entry 329.72, stop 346.98 (2×ATR), target 277.94 (3R). Results 2026-10-28 — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dell Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 404.7); CLEARED. Entry 438.62, stop 501.96 (2×ATR), target 248.6 (3R).  — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEYS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keysight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 319.77); CLEARED. Entry 322.42, stop 347.22 (2×ATR), target 248.02 (3R).  — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amphenol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 75.63); CLEARED — results within 14 days. Entry 77.72, stop 83.08 (2×ATR), target 61.64 (3R). Results 2026-10-28 — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 29.75); CLEARED. Entry 31.91, stop 34.03 (2×ATR), target 25.55 (3R). house limit: max 4 shorts — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Weekly Review — swing (every weekend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do this every Saturday or Sunday, in order. Log the result so you can see your process improve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist — tick each step (✔)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Market regime: S&amp;P 500 and JSE All Share vs their 200-day averages (log below)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Run the Finviz (US) and TradingView (JSE) swing presets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Shortlist 20–30 by 6-month performance; check charts for clean uptrends and setups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Add at least 5 candidates to the Swing Watchlist with this week's date (check the minimum counter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Plan entry, stop and target for every A/B candidate (reward:risk 2x+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Run the LRC Technical Review for A-grades you want to buy; trade only with clearance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Update 'Price now' on every open trade and act on each Review signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Check results dates for the next 2 weeks (event risk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Log the week below: trades opened/closed and one lesson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review log — one row per review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S&amp;P 500 above 200-day? (Y/N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSE All Share above 200-day? (Y/N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market regime → bias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-grades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trades opened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trades closed (why)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lessons / actions for next week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None (no swing positions open)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRC RULE: only Work-sheet names with a BUY/SELL rating AND technical clearance go on the watchlist (BUY = Long, SELL = Short). This week: PCTY (Long), WAB and ANET (Short). FAST (SELL) not added — technical clearance failed (score &lt;70%). 7 HOLDs not added. House minimum of 5 not met — run more Work-sheets to feed the list. S&amp;P 500 above 200-day; JSE All Share below (MA as of 26 Aug, stale). Shorts WAB/ANET are still in uptrends — act only on the breakdown triggers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None. PCTY long trigger (149) was hit ~8 Oct but no trade was entered; no swing positions open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finviz is blocked for our tools, so the Swing Long / Swing Short presets were applied manually on stockanalysis.com data (13 Oct closes). LRC RULE: only BUY/SELL-rated names with technical clearance are tradeable. LONGS: only NVDA qualifies; INTU and DECK are BUY-rated but in downtrends (watch only). 2 long slots unfilled — the momentum names the long preset finds (DELL, HPE, KEYS, APH, AMD) all rate SELL on valuation. SHORTS: NKE, ANET, AMD, DELL, FAST (max 4 open; FAST only after its 14 Oct results). Event risk inside 14 days: WAB 21 Oct, DECK 22 Oct, META 21 Oct, APH/GOOGL 28 Oct. S&amp;P 500 above its 200-day; JSE All Share below (−7.4% in 6 months). Lesson: an un-entered trigger cost us the PCTY move (+9%) — set conditional orders when a setup is approved. — P. Nkuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to pick long-term investments (hold 5 to 10+ years) — every month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal: own excellent businesses bought at sensible prices, and hold them while the business keeps compounding. Target: at least 5 new candidates a month, US and JSE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step-by-step (about 2–3 hours a month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Run the quality screen (15 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US: the Finviz 'Investment' preset on the Screener Settings tab. JSE: the TradingView preset, then check the annual report — JSE data on screeners is patchier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Shortlist on quality first (30 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefer businesses with high returns on capital (ROE 15%+, ROIC 12%+), strong margins, low debt and steady growth for 5+ years. Price comes second: a great business at a fair price beats a fair business at a great price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Understand the business (60 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each shortlisted name, answer in one line: what it sells, who pays, why customers stay (the moat), and what could break it. Read the latest annual report summary and results presentation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Judge moat and management (0–2 each)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moat: 2 = clear lasting advantage (brand, network, switching costs, scale, licence); 1 = some; 0 = none. Management: 2 = proven, honest, owner-like, sensible capital allocation; 1 = average or changing; 0 = concerns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Estimate fair value (optional, 30 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use the Valuation tab of the LRC Stock Analysis Template, or a simple check: FCF yield vs bond yield, P/E vs history and peers. The sheet then shows the margin of safety.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Enter in the sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add at least 5 candidates on 'Investment Watchlist' with this month's date. A = start the full LRC Stock Analysis Template; B = watch and re-check next month; C = reject.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Review what you own (monthly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update 'Price now'. Hold while the thesis is intact. Review if the price runs 20%+ above fair value, the quality score drops below 13, or a thesis-breaker appears (moat eroding, bad acquisition, management change).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the scores mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality /6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROE 15%+ = 2 (10%+ = 1); ROIC 12%+ = 2 (8%+ = 1); operating margin 15%+ = 1; gross margin 40%+ = 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth /4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS growth past 5 years 10%+ = 2 (5%+ = 1); sales growth past 5 years 8%+ = 2 (4%+ = 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance sheet /3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt/equity 0.5 or less = 2 (1.0 or less = 1); current ratio 1.2+ = 1. Banks and insurers: use your judgement instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valuation /4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward P/E 20 or less = 2 (30 or less = 1); price/free cash flow 20 or less = 2 (30 or less = 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner /1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insiders own 1%+ or dividend yield 2%+.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Judgement /4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your moat + management scores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin of safety /2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fair value 25%+ above price = 2; 10%+ = 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A = 18+ out of 24 · B = 13–17 · C = under 13.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long-term means years. Don't sell a great business because of one bad quarter; do sell if the thesis breaks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diversify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aim for 10–20 holdings across sectors and both markets over time; no single holding above 10% at purchase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoid traps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A very low P/E with falling sales is usually a value trap. High debt + cyclical earnings = danger in a downturn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investment Watchlist — monthly (hold 5 to 10+ years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every month add at least 5 quality candidates (US from Finviz, JSE from TradingView / annual reports). A-grades go into the full LRC Stock Analysis Template. Type percentages with the % sign. 'Price' = price when screened; update 'Price now' at each monthly review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current review month (1st of month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counts and the Top 5 use this month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This month's candidates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum new candidates per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House rule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US / JSE this month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INPUTS FROM FINVIZ / TRADINGVIEW + YOUR JUDGEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCORE (automatic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS &amp; THESIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward P/E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/FCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROIC / ROI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oper. margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt / Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS growth 5y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales growth 5y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dividend yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insider own</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moat 0-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management 0-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fair value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin of safety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoS pts /2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCORE /24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-line thesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change since added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-disruption fear has priced a 40%-FCF-margin software franchise at ~12.6x forward EPS; we think QuickBooks and TurboTax are stickier than the market believes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRC Work-sheet 14 Oct: BUY, 6-m target $426.00 (+41%), score 4.0/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-compute leader growing 70-90% a year at ~19x forward EPS — cheaper than its chip peers despite better margins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRC Work-sheet 14 Oct: BUY, 6-m target $262.56 (+15%), score 3.8/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two strong brands (HOKA, UGG), net cash and 23% margins at ~11x forward EPS; growth slowing but positive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRC Work-sheet 14 Oct: BUY, 6-m target $103.00 (+23%), score 3.8/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality payroll/HR software at 18x; our 6-month target is reached — accumulate below ~$146.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRC Work-sheet 14 Oct: HOLD, 6-m target $157.05 (-1%), score 3.8/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
   </si>
   <si>
     <t xml:space="preserve">META</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 677.14); CLEARED — results within 14 days. Entry 679.69, stop 728.69 (2×ATR), target 532.69 (3R). Results 2026-10-21; house limit: max 4 shorts — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arista Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 144.61); CLEARED — results within 14 days. Entry 176.42, stop 192.82 (2×ATR), target 127.22 (3R). Results 2026-11-03; house limit: max 4 shorts — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fastenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 38.37); CLEARED. Entry 47.21, stop 49.85 (2×ATR), target 39.29 (3R). house limit: max 4 shorts — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced Micro Devices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 402.73); CLEARED — results within 14 days. Entry 523.55, stop 576.65 (2×ATR), target 364.25 (3R). Results 2026-11-03; house limit: max 4 shorts — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wabtec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-23T03:09+02:00: LRC rating SELL (6-m value 248.07); CLEARED — results within 14 days. Entry 274.58, stop 288.58 (2×ATR), target 232.58 (3R). Results 2026-10-21; house limit: max 4 shorts — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly Review — swing (every weekend)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do this every Saturday or Sunday, in order. Log the result so you can see your process improve.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checklist — tick each step (✔)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Market regime: S&amp;P 500 and JSE All Share vs their 200-day averages (log below)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✔</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Run the Finviz (US) and TradingView (JSE) swing presets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Shortlist 20–30 by 6-month performance; check charts for clean uptrends and setups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Add at least 5 candidates to the Swing Watchlist with this week's date (check the minimum counter)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Plan entry, stop and target for every A/B candidate (reward:risk 2x+)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Run the LRC Technical Review for A-grades you want to buy; trade only with clearance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Update 'Price now' on every open trade and act on each Review signal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Check results dates for the next 2 weeks (event risk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Log the week below: trades opened/closed and one lesson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review log — one row per review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S&amp;P 500 above 200-day? (Y/N)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JSE All Share above 200-day? (Y/N)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market regime → bias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-grades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trades opened</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trades closed (why)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lessons / actions for next week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None (no swing positions open)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRC RULE: only Work-sheet names with a BUY/SELL rating AND technical clearance go on the watchlist (BUY = Long, SELL = Short). This week: PCTY (Long), WAB and ANET (Short). FAST (SELL) not added — technical clearance failed (score &lt;70%). 7 HOLDs not added. House minimum of 5 not met — run more Work-sheets to feed the list. S&amp;P 500 above 200-day; JSE All Share below (MA as of 26 Aug, stale). Shorts WAB/ANET are still in uptrends — act only on the breakdown triggers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None. PCTY long trigger (149) was hit ~8 Oct but no trade was entered; no swing positions open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finviz is blocked for our tools, so the Swing Long / Swing Short presets were applied manually on stockanalysis.com data (13 Oct closes). LRC RULE: only BUY/SELL-rated names with technical clearance are tradeable. LONGS: only NVDA qualifies; INTU and DECK are BUY-rated but in downtrends (watch only). 2 long slots unfilled — the momentum names the long preset finds (DELL, HPE, KEYS, APH, AMD) all rate SELL on valuation. SHORTS: NKE, ANET, AMD, DELL, FAST (max 4 open; FAST only after its 14 Oct results). Event risk inside 14 days: WAB 21 Oct, DECK 22 Oct, META 21 Oct, APH/GOOGL 28 Oct. S&amp;P 500 above its 200-day; JSE All Share below (−7.4% in 6 months). Lesson: an un-entered trigger cost us the PCTY move (+9%) — set conditional orders when a setup is approved. — P. Nkuna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built by the LRC Watchlist Agent 2026-10-23T03:09+02:00: 3 long / 10 short candidates under house rules. Analyst to review before any trade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How to pick long-term investments (hold 5 to 10+ years) — every month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goal: own excellent businesses bought at sensible prices, and hold them while the business keeps compounding. Target: at least 5 new candidates a month, US and JSE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Step-by-step (about 2–3 hours a month)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Run the quality screen (15 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US: the Finviz 'Investment' preset on the Screener Settings tab. JSE: the TradingView preset, then check the annual report — JSE data on screeners is patchier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Shortlist on quality first (30 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prefer businesses with high returns on capital (ROE 15%+, ROIC 12%+), strong margins, low debt and steady growth for 5+ years. Price comes second: a great business at a fair price beats a fair business at a great price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Understand the business (60 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For each shortlisted name, answer in one line: what it sells, who pays, why customers stay (the moat), and what could break it. Read the latest annual report summary and results presentation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Judge moat and management (0–2 each)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moat: 2 = clear lasting advantage (brand, network, switching costs, scale, licence); 1 = some; 0 = none. Management: 2 = proven, honest, owner-like, sensible capital allocation; 1 = average or changing; 0 = concerns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Estimate fair value (optional, 30 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use the Valuation tab of the LRC Stock Analysis Template, or a simple check: FCF yield vs bond yield, P/E vs history and peers. The sheet then shows the margin of safety.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Enter in the sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add at least 5 candidates on 'Investment Watchlist' with this month's date. A = start the full LRC Stock Analysis Template; B = watch and re-check next month; C = reject.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Review what you own (monthly)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Update 'Price now'. Hold while the thesis is intact. Review if the price runs 20%+ above fair value, the quality score drops below 13, or a thesis-breaker appears (moat eroding, bad acquisition, management change).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What the scores mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality /6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROE 15%+ = 2 (10%+ = 1); ROIC 12%+ = 2 (8%+ = 1); operating margin 15%+ = 1; gross margin 40%+ = 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Growth /4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS growth past 5 years 10%+ = 2 (5%+ = 1); sales growth past 5 years 8%+ = 2 (4%+ = 1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balance sheet /3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt/equity 0.5 or less = 2 (1.0 or less = 1); current ratio 1.2+ = 1. Banks and insurers: use your judgement instead.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valuation /4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forward P/E 20 or less = 2 (30 or less = 1); price/free cash flow 20 or less = 2 (30 or less = 1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner /1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insiders own 1%+ or dividend yield 2%+.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Judgement /4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your moat + management scores.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margin of safety /2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fair value 25%+ above price = 2; 10%+ = 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A = 18+ out of 24 · B = 13–17 · C = under 13.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long-term means years. Don't sell a great business because of one bad quarter; do sell if the thesis breaks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diversify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aim for 10–20 holdings across sectors and both markets over time; no single holding above 10% at purchase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avoid traps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A very low P/E with falling sales is usually a value trap. High debt + cyclical earnings = danger in a downturn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investment Watchlist — monthly (hold 5 to 10+ years)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every month add at least 5 quality candidates (US from Finviz, JSE from TradingView / annual reports). A-grades go into the full LRC Stock Analysis Template. Type percentages with the % sign. 'Price' = price when screened; update 'Price now' at each monthly review.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current review month (1st of month)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Counts and the Top 5 use this month.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This month's candidates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum new candidates per month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">House rule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US / JSE this month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INPUTS FROM FINVIZ / TRADINGVIEW + YOUR JUDGEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCORE (automatic)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEXT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STATUS &amp; THESIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forward P/E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P/FCF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROIC / ROI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oper. margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt / Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS growth 5y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales growth 5y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dividend yield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insider own</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moat 0-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Management 0-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fair value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margin of safety</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MoS pts /2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCORE /24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One-line thesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date added</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change since added</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-disruption fear has priced a 40%-FCF-margin software franchise at ~12.6x forward EPS; we think QuickBooks and TurboTax are stickier than the market believes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRC Work-sheet 14 Oct: BUY, 6-m target $426.00 (+41%), score 4.0/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-compute leader growing 70-90% a year at ~19x forward EPS — cheaper than its chip peers despite better margins.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRC Work-sheet 14 Oct: BUY, 6-m target $262.56 (+15%), score 3.8/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two strong brands (HOKA, UGG), net cash and 23% margins at ~11x forward EPS; growth slowing but positive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRC Work-sheet 14 Oct: BUY, 6-m target $103.00 (+23%), score 3.8/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality payroll/HR software at 18x; our 6-month target is reached — accumulate below ~$146.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRC Work-sheet 14 Oct: HOLD, 6-m target $157.05 (-1%), score 3.8/5. Fair value = the 6-MONTH Work-sheet target (a long-term DCF value would be higher for the growers). Growth = FY2022-FY2026 (4-yr CAGR) CAGR. Data: stockanalysis.com 13 Oct 2026 (Finviz Investment preset applied manually — Finviz blocked). — P. Nkuna</t>
   </si>
   <si>
     <t xml:space="preserve">Meta Platforms, Inc.</t>
@@ -2630,13 +2540,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="0" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2646,12 +2556,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2673,13 +2582,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>420840</xdr:colOff>
+      <xdr:colOff>513360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2689,12 +2598,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2716,13 +2624,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2732,12 +2640,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2758,14 +2665,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>90360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2775,12 +2682,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2801,14 +2707,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2818,12 +2724,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2845,13 +2750,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2861,12 +2766,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2887,14 +2791,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>90360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="6" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2904,12 +2808,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2930,14 +2833,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="7" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2947,12 +2850,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2974,13 +2876,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>570600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="8" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2990,12 +2892,11 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865800" cy="570600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3014,34 +2915,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -3188,7 +3089,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="22"/>
@@ -3424,40 +3325,40 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="56" t="s">
-        <v>568</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="57" t="s">
-        <v>569</v>
+        <v>539</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>144</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>572</v>
+        <v>542</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="H3" s="57" t="s">
-        <v>575</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3465,7 +3366,7 @@
         <v>179</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>192</v>
@@ -3474,13 +3375,13 @@
         <v>183</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>577</v>
+        <v>547</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>578</v>
+        <v>548</v>
       </c>
       <c r="H4" s="58" t="s">
         <v>182</v>
@@ -3488,7 +3389,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>579</v>
+        <v>549</v>
       </c>
       <c r="B5" s="58" t="s">
         <v>184</v>
@@ -3503,38 +3404,38 @@
         <v>192</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="58" t="s">
-        <v>582</v>
+        <v>552</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>584</v>
+        <v>554</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>585</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="58" t="s">
-        <v>586</v>
+        <v>556</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>587</v>
+        <v>557</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>41</v>
@@ -3551,10 +3452,10 @@
         <v>185</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>588</v>
+        <v>558</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>589</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3562,7 +3463,7 @@
         <v>191</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="H9" s="58" t="s">
         <v>189</v>
@@ -3570,10 +3471,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="58" t="s">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>591</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3581,15 +3482,15 @@
         <v>211</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>592</v>
+        <v>562</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="58" t="s">
-        <v>593</v>
+        <v>563</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3597,12 +3498,12 @@
         <v>213</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>594</v>
+        <v>564</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="58" t="s">
-        <v>595</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -3623,7 +3524,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
@@ -3700,7 +3601,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="8" t="n">
         <f aca="false">IF('Swing Watchlist'!$C$4="","",'Swing Watchlist'!$C$4)</f>
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -3725,7 +3626,7 @@
       <c r="C6" s="7"/>
       <c r="D6" s="10" t="n">
         <f aca="false">'Swing Watchlist'!U4</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -3775,7 +3676,7 @@
       <c r="C8" s="7"/>
       <c r="D8" s="11" t="str">
         <f aca="false">'Swing Watchlist'!U5&amp;"  ·  "&amp;'Swing Watchlist'!U6</f>
-        <v>13 / 0  ·  3 / 10</v>
+        <v>8 / 0  ·  3 / 5</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -3800,7 +3701,7 @@
       <c r="C9" s="7"/>
       <c r="D9" s="11" t="str">
         <f aca="false">COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"A")&amp;" / "&amp;COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"B")&amp;" / "&amp;COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"C")</f>
-        <v>0 / 9 / 4</v>
+        <v>2 / 0 / 6</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -3956,23 +3857,23 @@
       </c>
       <c r="B16" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>NKE</v>
+        <v>NVDA</v>
       </c>
       <c r="C16" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
-        <v>Short</v>
+        <v>Long</v>
       </c>
       <c r="D16" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E16" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="F16" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Watch — wait for setup</v>
+        <v>Run Technical Review — LONG entry</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>1</v>
@@ -4005,7 +3906,7 @@
       </c>
       <c r="B17" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>KEYS</v>
+        <v>NKE</v>
       </c>
       <c r="C17" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -4013,15 +3914,15 @@
       </c>
       <c r="D17" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="F17" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Watch — wait for setup</v>
+        <v>Run Technical Review — SHORT entry</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>2</v>
@@ -4054,23 +3955,23 @@
       </c>
       <c r="B18" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>NVDA</v>
+        <v>ANET</v>
       </c>
       <c r="C18" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
-        <v>Long</v>
+        <v>Short</v>
       </c>
       <c r="D18" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="F18" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Watch — wait for setup</v>
+        <v>Drop or re-check next week</v>
       </c>
       <c r="H18" s="13" t="n">
         <v>3</v>
@@ -4103,7 +4004,7 @@
       </c>
       <c r="B19" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>GOOGL</v>
+        <v>FAST</v>
       </c>
       <c r="C19" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -4111,15 +4012,15 @@
       </c>
       <c r="D19" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="F19" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Watch — wait for setup</v>
+        <v>Drop or re-check next week</v>
       </c>
       <c r="H19" s="13" t="n">
         <v>4</v>
@@ -4152,7 +4053,7 @@
       </c>
       <c r="B20" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>ANET</v>
+        <v>AMD</v>
       </c>
       <c r="C20" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -4160,15 +4061,15 @@
       </c>
       <c r="D20" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="F20" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Watch — wait for setup</v>
+        <v>Drop or re-check next week</v>
       </c>
       <c r="H20" s="13" t="n">
         <v>5</v>
@@ -4298,7 +4199,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="16"/>
@@ -4819,7 +4720,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AX210"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
@@ -4970,7 +4871,7 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="19" t="n">
-        <v>46316</v>
+        <v>46312</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>118</v>
@@ -4999,7 +4900,7 @@
       <c r="T4" s="22"/>
       <c r="U4" s="23" t="n">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$C$11:$C$210,"?*")</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V4" s="24" t="str">
         <f aca="false">IF(U4&gt;=$C$5,"✔ minimum met","⚠ need "&amp;($C$5-U4)&amp;" more")</f>
@@ -5043,7 +4944,7 @@
       <c r="T5" s="22"/>
       <c r="U5" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$B$11:$B$210,"US")&amp;" / "&amp;COUNTIFS($A$11:$A$210,$C$4,$B$11:$B$210,"JSE")</f>
-        <v>13 / 0</v>
+        <v>8 / 0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5081,7 +4982,7 @@
       <c r="T6" s="22"/>
       <c r="U6" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$C$11:$C$210,"?*",$F$11:$F$210,"&lt;&gt;Short")&amp;" / "&amp;COUNTIFS($A$11:$A$210,$C$4,$F$11:$F$210,"Short")</f>
-        <v>3 / 10</v>
+        <v>3 / 5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5119,7 +5020,7 @@
       <c r="T7" s="22"/>
       <c r="U7" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$AK$11:$AK$210,"A")&amp;" / "&amp;COUNTIF($AP$11:$AP$210,"Open position")</f>
-        <v>0 / 0</v>
+        <v>2 / 0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5975,9 +5876,9 @@
       <c r="AV14" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="AX14" s="43" t="str">
+      <c r="AX14" s="43" t="n">
         <f aca="false">IF(AND(C14&lt;&gt;"",A14=$C$4,ISNUMBER(AJ14)),AJ14+ROW()/100000,"")</f>
-        <v/>
+        <v>17.00014</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6137,9 +6038,9 @@
       <c r="AV15" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="AX15" s="43" t="str">
+      <c r="AX15" s="43" t="n">
         <f aca="false">IF(AND(C15&lt;&gt;"",A15=$C$4,ISNUMBER(AJ15)),AJ15+ROW()/100000,"")</f>
-        <v/>
+        <v>8.00015</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6299,9 +6200,9 @@
       <c r="AV16" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="AX16" s="43" t="str">
+      <c r="AX16" s="43" t="n">
         <f aca="false">IF(AND(C16&lt;&gt;"",A16=$C$4,ISNUMBER(AJ16)),AJ16+ROW()/100000,"")</f>
-        <v/>
+        <v>8.00016</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6459,9 +6360,9 @@
       <c r="AV17" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="AX17" s="43" t="str">
+      <c r="AX17" s="43" t="n">
         <f aca="false">IF(AND(C17&lt;&gt;"",A17=$C$4,ISNUMBER(AJ17)),AJ17+ROW()/100000,"")</f>
-        <v/>
+        <v>16.00017</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6621,9 +6522,9 @@
       <c r="AV18" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="AX18" s="43" t="str">
+      <c r="AX18" s="43" t="n">
         <f aca="false">IF(AND(C18&lt;&gt;"",A18=$C$4,ISNUMBER(AJ18)),AJ18+ROW()/100000,"")</f>
-        <v/>
+        <v>9.00018</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6785,9 +6686,9 @@
       <c r="AV19" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="AX19" s="43" t="str">
+      <c r="AX19" s="43" t="n">
         <f aca="false">IF(AND(C19&lt;&gt;"",A19=$C$4,ISNUMBER(AJ19)),AJ19+ROW()/100000,"")</f>
-        <v/>
+        <v>8.00019</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6949,9 +6850,9 @@
       <c r="AV20" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="AX20" s="43" t="str">
+      <c r="AX20" s="43" t="n">
         <f aca="false">IF(AND(C20&lt;&gt;"",A20=$C$4,ISNUMBER(AJ20)),AJ20+ROW()/100000,"")</f>
-        <v/>
+        <v>7.0002</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7111,149 +7012,99 @@
       <c r="AV21" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="AX21" s="43" t="str">
+      <c r="AX21" s="43" t="n">
         <f aca="false">IF(AND(C21&lt;&gt;"",A21=$C$4,ISNUMBER(AJ21)),AJ21+ROW()/100000,"")</f>
-        <v/>
+        <v>8.00021</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="E22" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F22" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="G22" s="26" t="n">
-        <v>221.97</v>
-      </c>
+      <c r="A22" s="19"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="26"/>
-      <c r="I22" s="36" t="n">
-        <v>117533575</v>
-      </c>
-      <c r="J22" s="37" t="n">
+      <c r="I22" s="36"/>
+      <c r="J22" s="37" t="str">
         <f aca="false">IF(OR(G22="",I22=""),"",G22*I22/1000000)</f>
-        <v>26088.92764275</v>
-      </c>
-      <c r="K22" s="21" t="n">
-        <v>-0.0216</v>
-      </c>
-      <c r="L22" s="21" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="M22" s="21" t="n">
-        <v>0.0911</v>
-      </c>
-      <c r="N22" s="25" t="n">
-        <v>47.91</v>
-      </c>
-      <c r="O22" s="21" t="n">
-        <v>0.0633</v>
-      </c>
-      <c r="P22" s="21" t="n">
-        <v>0.0961</v>
-      </c>
-      <c r="Q22" s="21" t="n">
-        <v>-0.0879</v>
-      </c>
-      <c r="R22" s="21" t="n">
-        <v>0.3513</v>
-      </c>
-      <c r="S22" s="38" t="n">
-        <v>0.74</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="38"/>
       <c r="T22" s="21"/>
-      <c r="U22" s="21" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="V22" s="19" t="n">
-        <v>46344</v>
-      </c>
-      <c r="W22" s="26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="X22" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y22" s="26" t="n">
-        <v>222.63</v>
-      </c>
-      <c r="Z22" s="26" t="n">
-        <v>210.83</v>
-      </c>
-      <c r="AA22" s="26" t="n">
-        <v>258.03</v>
-      </c>
-      <c r="AB22" s="16" t="n">
+      <c r="U22" s="21"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="26"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="26"/>
+      <c r="Z22" s="26"/>
+      <c r="AA22" s="26"/>
+      <c r="AB22" s="16" t="str">
         <f aca="false">IF(C22="","",IF(F22="Short",(AND(M22&lt;&gt;"",N(M22)&lt;0))+(AND(L22&lt;&gt;"",N(L22)&lt;0))+(AND(K22&lt;&gt;"",N(K22)&lt;0))+AND(L22&lt;&gt;"",M22&lt;&gt;"",N(M22)&lt;N(L22)),(N(M22)&gt;0)+(N(L22)&gt;0)+(N(K22)&gt;0)+AND(L22&lt;&gt;"",M22&lt;&gt;"",N(M22)&gt;N(L22))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC22" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC22" s="16" t="str">
         <f aca="false">IF(C22="","",IF(F22="Short",IF(N22="",0,IF(AND(N22&gt;=30,N22&lt;=50),2,IF(OR(AND(N22&gt;=25,N22&lt;30),AND(N22&gt;50,N22&lt;=60)),1,0)))+IF(P22="",0,IF(AND(IF(B22="JSE",$L$5,$L$4)&lt;&gt;"",P22&lt;IF(B22="JSE",$L$5,$L$4)),2,IF(P22&lt;0,1,0))),IF(N22="",0,IF(AND(N22&gt;=50,N22&lt;=70),2,IF(OR(AND(N22&gt;=40,N22&lt;50),AND(N22&gt;70,N22&lt;=75)),1,0)))+IF(P22="",0,IF(AND(IF(B22="JSE",$L$5,$L$4)&lt;&gt;"",P22&gt;IF(B22="JSE",$L$5,$L$4)),2,IF(P22&gt;0,1,0)))))</f>
-        <v>2</v>
-      </c>
-      <c r="AD22" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD22" s="16" t="str">
         <f aca="false">IF(C22="","",IF(F22="Short",IF(R22="",0,IF(R22&lt;=0.1,2,IF(R22&lt;=0.25,1,0))),IF(Q22="",0,IF(Q22&gt;=-0.1,2,IF(Q22&gt;=-0.25,1,0)))))</f>
-        <v>2</v>
-      </c>
-      <c r="AE22" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE22" s="16" t="str">
         <f aca="false">IF(C22="","",IF(J22="",0,IF(J22&gt;=IF(B22="JSE",$L$7,$L$6),2,IF(J22&gt;=IF(B22="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF22" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF22" s="16" t="str">
         <f aca="false">IF(C22="","",IF(F22="Short",AND(T22&lt;&gt;"",N(T22)&lt;0),N(T22)&gt;0)+(N(S22)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG22" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG22" s="16" t="str">
         <f aca="false">IF(C22="","",IF(AL22="",0,IF(AL22&gt;=3,4,IF(AL22&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH22" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH22" s="16" t="str">
         <f aca="false">IF(C22="","",IF(AND(ISNUMBER(V22),ISNUMBER(A22),V22&gt;=A22,V22-A22&lt;=14),-2,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI22" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI22" s="16" t="str">
         <f aca="false">IF(C22="","",IF(AND(F22="Short",N(U22)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ22" s="23" t="str">
         <f aca="false">IF(C22="","",SUM(AB22:AI22))</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="AK22" s="24" t="str">
         <f aca="false">IF(C22="","",IF(AJ22&gt;=14,"A",IF(AJ22&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL22" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL22" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y22="",Z22="",AA22=""),"",IF(F22="Short",IF(Z22&lt;=Y22,"",(Y22-AA22)/(Z22-Y22)),IF(Y22&lt;=Z22,"",(AA22-Y22)/(Y22-Z22)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM22" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM22" s="37" t="str">
         <f aca="false">IF(OR(Y22="",Z22="",N(Y22)=N(Z22)),"",IF(OR(AND(F22="Short",Z22&lt;Y22),AND(NOT(F22="Short"),Z22&gt;Y22)),"stop on wrong side",ABS(Y22-Z22)))</f>
-        <v>11.8</v>
-      </c>
-      <c r="AN22" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN22" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM22)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM22,2)),"")</f>
-        <v>0.03</v>
-      </c>
-      <c r="AO22" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO22" s="37" t="str">
         <f aca="false">IFERROR(IF(AN22="","",AN22*Y22),"")</f>
-        <v>6.6789</v>
-      </c>
-      <c r="AP22" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP22" s="35"/>
       <c r="AQ22" s="19"/>
       <c r="AR22" s="26"/>
       <c r="AS22" s="41" t="str">
@@ -7266,156 +7117,102 @@
       </c>
       <c r="AU22" s="14" t="str">
         <f aca="false">IF(C22="","",IF(AP22="Open position",IF(IF(F22="Short",AND(ISNUMBER(AR22),ISNUMBER(Z22),AR22&gt;=Z22),AND(ISNUMBER(AR22),ISNUMBER(Z22),AR22&lt;=Z22)),IF(F22="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F22="Short",AND(ISNUMBER(AR22),ISNUMBER(AA22),AR22&lt;=AA22),AND(ISNUMBER(AR22),ISNUMBER(AA22),AR22&gt;=AA22)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT22),AT22&gt;182),IF(F22="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT22),AT22&gt;42,ISNUMBER(AS22),AS22&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F22="Short",AND(L22&lt;&gt;"",N(L22)&gt;0),AND(L22&lt;&gt;"",N(L22)&lt;0)),IF(F22="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP22="Closed",AP22="Dropped"),"Closed",IF(AK22="A",IF(F22="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK22="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV22" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="AX22" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV22" s="35"/>
+      <c r="AX22" s="43" t="str">
         <f aca="false">IF(AND(C22&lt;&gt;"",A22=$C$4,ISNUMBER(AJ22)),AJ22+ROW()/100000,"")</f>
-        <v>12.00022</v>
+        <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C23" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="E23" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F23" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="G23" s="26" t="n">
-        <v>335.61</v>
-      </c>
+      <c r="A23" s="19"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="26"/>
-      <c r="I23" s="36" t="n">
-        <v>3793417</v>
-      </c>
-      <c r="J23" s="37" t="n">
+      <c r="I23" s="36"/>
+      <c r="J23" s="37" t="str">
         <f aca="false">IF(OR(G23="",I23=""),"",G23*I23/1000000)</f>
-        <v>1273.10867937</v>
-      </c>
-      <c r="K23" s="21" t="n">
-        <v>0.1228</v>
-      </c>
-      <c r="L23" s="21" t="n">
-        <v>0.0454</v>
-      </c>
-      <c r="M23" s="21" t="n">
-        <v>-0.0948</v>
-      </c>
-      <c r="N23" s="25" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="O23" s="21" t="n">
-        <v>0.1921</v>
-      </c>
-      <c r="P23" s="21" t="n">
-        <v>-0.1788</v>
-      </c>
-      <c r="Q23" s="21" t="n">
-        <v>-0.513</v>
-      </c>
-      <c r="R23" s="21" t="n">
-        <v>0.3274</v>
-      </c>
-      <c r="S23" s="38" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="T23" s="21" t="n">
-        <v>-0.0133</v>
-      </c>
-      <c r="U23" s="21" t="n">
-        <v>0.0279</v>
-      </c>
-      <c r="V23" s="19" t="n">
-        <v>46345</v>
-      </c>
-      <c r="W23" s="26" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="X23" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y23" s="26" t="n">
-        <v>342.47</v>
-      </c>
-      <c r="Z23" s="26" t="n">
-        <v>318.21</v>
-      </c>
-      <c r="AA23" s="26" t="n">
-        <v>415.25</v>
-      </c>
-      <c r="AB23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="21"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="26"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="26"/>
+      <c r="Z23" s="26"/>
+      <c r="AA23" s="26"/>
+      <c r="AB23" s="16" t="str">
         <f aca="false">IF(C23="","",IF(F23="Short",(AND(M23&lt;&gt;"",N(M23)&lt;0))+(AND(L23&lt;&gt;"",N(L23)&lt;0))+(AND(K23&lt;&gt;"",N(K23)&lt;0))+AND(L23&lt;&gt;"",M23&lt;&gt;"",N(M23)&lt;N(L23)),(N(M23)&gt;0)+(N(L23)&gt;0)+(N(K23)&gt;0)+AND(L23&lt;&gt;"",M23&lt;&gt;"",N(M23)&gt;N(L23))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC23" s="16" t="str">
         <f aca="false">IF(C23="","",IF(F23="Short",IF(N23="",0,IF(AND(N23&gt;=30,N23&lt;=50),2,IF(OR(AND(N23&gt;=25,N23&lt;30),AND(N23&gt;50,N23&lt;=60)),1,0)))+IF(P23="",0,IF(AND(IF(B23="JSE",$L$5,$L$4)&lt;&gt;"",P23&lt;IF(B23="JSE",$L$5,$L$4)),2,IF(P23&lt;0,1,0))),IF(N23="",0,IF(AND(N23&gt;=50,N23&lt;=70),2,IF(OR(AND(N23&gt;=40,N23&lt;50),AND(N23&gt;70,N23&lt;=75)),1,0)))+IF(P23="",0,IF(AND(IF(B23="JSE",$L$5,$L$4)&lt;&gt;"",P23&gt;IF(B23="JSE",$L$5,$L$4)),2,IF(P23&gt;0,1,0)))))</f>
-        <v>2</v>
-      </c>
-      <c r="AD23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD23" s="16" t="str">
         <f aca="false">IF(C23="","",IF(F23="Short",IF(R23="",0,IF(R23&lt;=0.1,2,IF(R23&lt;=0.25,1,0))),IF(Q23="",0,IF(Q23&gt;=-0.1,2,IF(Q23&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE23" s="16" t="str">
         <f aca="false">IF(C23="","",IF(J23="",0,IF(J23&gt;=IF(B23="JSE",$L$7,$L$6),2,IF(J23&gt;=IF(B23="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF23" s="16" t="str">
         <f aca="false">IF(C23="","",IF(F23="Short",AND(T23&lt;&gt;"",N(T23)&lt;0),N(T23)&gt;0)+(N(S23)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG23" s="16" t="str">
         <f aca="false">IF(C23="","",IF(AL23="",0,IF(AL23&gt;=3,4,IF(AL23&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH23" s="16" t="str">
         <f aca="false">IF(C23="","",IF(AND(ISNUMBER(V23),ISNUMBER(A23),V23&gt;=A23,V23-A23&lt;=14),-2,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI23" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI23" s="16" t="str">
         <f aca="false">IF(C23="","",IF(AND(F23="Short",N(U23)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ23" s="23" t="str">
         <f aca="false">IF(C23="","",SUM(AB23:AI23))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AK23" s="24" t="str">
         <f aca="false">IF(C23="","",IF(AJ23&gt;=14,"A",IF(AJ23&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL23" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL23" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y23="",Z23="",AA23=""),"",IF(F23="Short",IF(Z23&lt;=Y23,"",(Y23-AA23)/(Z23-Y23)),IF(Y23&lt;=Z23,"",(AA23-Y23)/(Y23-Z23)))),"")</f>
-        <v>2.99999999999999</v>
-      </c>
-      <c r="AM23" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM23" s="37" t="str">
         <f aca="false">IF(OR(Y23="",Z23="",N(Y23)=N(Z23)),"",IF(OR(AND(F23="Short",Z23&lt;Y23),AND(NOT(F23="Short"),Z23&gt;Y23)),"stop on wrong side",ABS(Y23-Z23)))</f>
-        <v>24.26</v>
-      </c>
-      <c r="AN23" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN23" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM23)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM23,2)),"")</f>
-        <v>0.01</v>
-      </c>
-      <c r="AO23" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO23" s="37" t="str">
         <f aca="false">IFERROR(IF(AN23="","",AN23*Y23),"")</f>
-        <v>3.4247</v>
-      </c>
-      <c r="AP23" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP23" s="35"/>
       <c r="AQ23" s="19"/>
       <c r="AR23" s="26"/>
       <c r="AS23" s="41" t="str">
@@ -7428,154 +7225,102 @@
       </c>
       <c r="AU23" s="14" t="str">
         <f aca="false">IF(C23="","",IF(AP23="Open position",IF(IF(F23="Short",AND(ISNUMBER(AR23),ISNUMBER(Z23),AR23&gt;=Z23),AND(ISNUMBER(AR23),ISNUMBER(Z23),AR23&lt;=Z23)),IF(F23="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F23="Short",AND(ISNUMBER(AR23),ISNUMBER(AA23),AR23&lt;=AA23),AND(ISNUMBER(AR23),ISNUMBER(AA23),AR23&gt;=AA23)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT23),AT23&gt;182),IF(F23="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT23),AT23&gt;42,ISNUMBER(AS23),AS23&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F23="Short",AND(L23&lt;&gt;"",N(L23)&gt;0),AND(L23&lt;&gt;"",N(L23)&lt;0)),IF(F23="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP23="Closed",AP23="Dropped"),"Closed",IF(AK23="A",IF(F23="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK23="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV23" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="AX23" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV23" s="35"/>
+      <c r="AX23" s="43" t="str">
         <f aca="false">IF(AND(C23&lt;&gt;"",A23=$C$4,ISNUMBER(AJ23)),AJ23+ROW()/100000,"")</f>
-        <v>10.00023</v>
+        <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="D24" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="E24" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F24" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="G24" s="26" t="n">
-        <v>85.49</v>
-      </c>
+      <c r="A24" s="19"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="26"/>
-      <c r="I24" s="36" t="n">
-        <v>2911073</v>
-      </c>
-      <c r="J24" s="37" t="n">
+      <c r="I24" s="36"/>
+      <c r="J24" s="37" t="str">
         <f aca="false">IF(OR(G24="",I24=""),"",G24*I24/1000000)</f>
-        <v>248.86763077</v>
-      </c>
-      <c r="K24" s="21" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="L24" s="21" t="n">
-        <v>0.0183</v>
-      </c>
-      <c r="M24" s="21" t="n">
-        <v>-0.1454</v>
-      </c>
-      <c r="N24" s="25" t="n">
-        <v>55.85</v>
-      </c>
-      <c r="O24" s="21" t="n">
-        <v>-0.1116</v>
-      </c>
-      <c r="P24" s="21" t="n">
-        <v>-0.2061</v>
-      </c>
-      <c r="Q24" s="21" t="n">
-        <v>-0.3009</v>
-      </c>
-      <c r="R24" s="21" t="n">
-        <v>0.1074</v>
-      </c>
-      <c r="S24" s="38" t="n">
-        <v>1.01</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="38"/>
       <c r="T24" s="21"/>
-      <c r="U24" s="21" t="n">
-        <v>0.0877</v>
-      </c>
-      <c r="V24" s="19" t="n">
-        <v>46317</v>
-      </c>
-      <c r="W24" s="26" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="X24" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y24" s="26" t="n">
-        <v>88.16</v>
-      </c>
-      <c r="Z24" s="26" t="n">
-        <v>83.18</v>
-      </c>
-      <c r="AA24" s="26" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="AB24" s="16" t="n">
+      <c r="U24" s="21"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="26"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="26"/>
+      <c r="Z24" s="26"/>
+      <c r="AA24" s="26"/>
+      <c r="AB24" s="16" t="str">
         <f aca="false">IF(C24="","",IF(F24="Short",(AND(M24&lt;&gt;"",N(M24)&lt;0))+(AND(L24&lt;&gt;"",N(L24)&lt;0))+(AND(K24&lt;&gt;"",N(K24)&lt;0))+AND(L24&lt;&gt;"",M24&lt;&gt;"",N(M24)&lt;N(L24)),(N(M24)&gt;0)+(N(L24)&gt;0)+(N(K24)&gt;0)+AND(L24&lt;&gt;"",M24&lt;&gt;"",N(M24)&gt;N(L24))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC24" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC24" s="16" t="str">
         <f aca="false">IF(C24="","",IF(F24="Short",IF(N24="",0,IF(AND(N24&gt;=30,N24&lt;=50),2,IF(OR(AND(N24&gt;=25,N24&lt;30),AND(N24&gt;50,N24&lt;=60)),1,0)))+IF(P24="",0,IF(AND(IF(B24="JSE",$L$5,$L$4)&lt;&gt;"",P24&lt;IF(B24="JSE",$L$5,$L$4)),2,IF(P24&lt;0,1,0))),IF(N24="",0,IF(AND(N24&gt;=50,N24&lt;=70),2,IF(OR(AND(N24&gt;=40,N24&lt;50),AND(N24&gt;70,N24&lt;=75)),1,0)))+IF(P24="",0,IF(AND(IF(B24="JSE",$L$5,$L$4)&lt;&gt;"",P24&gt;IF(B24="JSE",$L$5,$L$4)),2,IF(P24&gt;0,1,0)))))</f>
-        <v>2</v>
-      </c>
-      <c r="AD24" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD24" s="16" t="str">
         <f aca="false">IF(C24="","",IF(F24="Short",IF(R24="",0,IF(R24&lt;=0.1,2,IF(R24&lt;=0.25,1,0))),IF(Q24="",0,IF(Q24&gt;=-0.1,2,IF(Q24&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE24" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE24" s="16" t="str">
         <f aca="false">IF(C24="","",IF(J24="",0,IF(J24&gt;=IF(B24="JSE",$L$7,$L$6),2,IF(J24&gt;=IF(B24="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF24" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF24" s="16" t="str">
         <f aca="false">IF(C24="","",IF(F24="Short",AND(T24&lt;&gt;"",N(T24)&lt;0),N(T24)&gt;0)+(N(S24)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG24" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG24" s="16" t="str">
         <f aca="false">IF(C24="","",IF(AL24="",0,IF(AL24&gt;=3,4,IF(AL24&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH24" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH24" s="16" t="str">
         <f aca="false">IF(C24="","",IF(AND(ISNUMBER(V24),ISNUMBER(A24),V24&gt;=A24,V24-A24&lt;=14),-2,0))</f>
-        <v>-2</v>
-      </c>
-      <c r="AI24" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI24" s="16" t="str">
         <f aca="false">IF(C24="","",IF(AND(F24="Short",N(U24)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ24" s="23" t="str">
         <f aca="false">IF(C24="","",SUM(AB24:AI24))</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="AK24" s="24" t="str">
         <f aca="false">IF(C24="","",IF(AJ24&gt;=14,"A",IF(AJ24&gt;=10,"B","C")))</f>
-        <v>C</v>
-      </c>
-      <c r="AL24" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL24" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y24="",Z24="",AA24=""),"",IF(F24="Short",IF(Z24&lt;=Y24,"",(Y24-AA24)/(Z24-Y24)),IF(Y24&lt;=Z24,"",(AA24-Y24)/(Y24-Z24)))),"")</f>
-        <v>3.00000000000001</v>
-      </c>
-      <c r="AM24" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM24" s="37" t="str">
         <f aca="false">IF(OR(Y24="",Z24="",N(Y24)=N(Z24)),"",IF(OR(AND(F24="Short",Z24&lt;Y24),AND(NOT(F24="Short"),Z24&gt;Y24)),"stop on wrong side",ABS(Y24-Z24)))</f>
-        <v>4.97999999999999</v>
-      </c>
-      <c r="AN24" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN24" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM24)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM24,2)),"")</f>
-        <v>0.09</v>
-      </c>
-      <c r="AO24" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO24" s="37" t="str">
         <f aca="false">IFERROR(IF(AN24="","",AN24*Y24),"")</f>
-        <v>7.9344</v>
-      </c>
-      <c r="AP24" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP24" s="35"/>
       <c r="AQ24" s="19"/>
       <c r="AR24" s="26"/>
       <c r="AS24" s="41" t="str">
@@ -7588,154 +7333,102 @@
       </c>
       <c r="AU24" s="14" t="str">
         <f aca="false">IF(C24="","",IF(AP24="Open position",IF(IF(F24="Short",AND(ISNUMBER(AR24),ISNUMBER(Z24),AR24&gt;=Z24),AND(ISNUMBER(AR24),ISNUMBER(Z24),AR24&lt;=Z24)),IF(F24="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F24="Short",AND(ISNUMBER(AR24),ISNUMBER(AA24),AR24&lt;=AA24),AND(ISNUMBER(AR24),ISNUMBER(AA24),AR24&gt;=AA24)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT24),AT24&gt;182),IF(F24="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT24),AT24&gt;42,ISNUMBER(AS24),AS24&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F24="Short",AND(L24&lt;&gt;"",N(L24)&gt;0),AND(L24&lt;&gt;"",N(L24)&lt;0)),IF(F24="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP24="Closed",AP24="Dropped"),"Closed",IF(AK24="A",IF(F24="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK24="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Drop or re-check next week</v>
-      </c>
-      <c r="AV24" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="AX24" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV24" s="35"/>
+      <c r="AX24" s="43" t="str">
         <f aca="false">IF(AND(C24&lt;&gt;"",A24=$C$4,ISNUMBER(AJ24)),AJ24+ROW()/100000,"")</f>
-        <v>8.00024</v>
+        <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="D25" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="E25" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G25" s="26" t="n">
-        <v>334.76</v>
-      </c>
+      <c r="A25" s="19"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="26"/>
       <c r="H25" s="26"/>
-      <c r="I25" s="36" t="n">
-        <v>25764278</v>
-      </c>
-      <c r="J25" s="37" t="n">
+      <c r="I25" s="36"/>
+      <c r="J25" s="37" t="str">
         <f aca="false">IF(OR(G25="",I25=""),"",G25*I25/1000000)</f>
-        <v>8624.84970328</v>
-      </c>
-      <c r="K25" s="21" t="n">
-        <v>-0.0302</v>
-      </c>
-      <c r="L25" s="21" t="n">
-        <v>-0.0264</v>
-      </c>
-      <c r="M25" s="21" t="n">
-        <v>-0.0191</v>
-      </c>
-      <c r="N25" s="25" t="n">
-        <v>40.25</v>
-      </c>
-      <c r="O25" s="21" t="n">
-        <v>0.0537</v>
-      </c>
-      <c r="P25" s="21" t="n">
-        <v>-0.0134</v>
-      </c>
-      <c r="Q25" s="21" t="n">
-        <v>-0.1807</v>
-      </c>
-      <c r="R25" s="21" t="n">
-        <v>0.3711</v>
-      </c>
-      <c r="S25" s="38" t="n">
-        <v>1.13</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="38"/>
       <c r="T25" s="21"/>
-      <c r="U25" s="21" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="V25" s="19" t="n">
-        <v>46323</v>
-      </c>
-      <c r="W25" s="26" t="n">
-        <v>8.63</v>
-      </c>
-      <c r="X25" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y25" s="26" t="n">
-        <v>329.72</v>
-      </c>
-      <c r="Z25" s="26" t="n">
-        <v>346.98</v>
-      </c>
-      <c r="AA25" s="26" t="n">
-        <v>277.94</v>
-      </c>
-      <c r="AB25" s="16" t="n">
+      <c r="U25" s="21"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="26"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="26"/>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="16" t="str">
         <f aca="false">IF(C25="","",IF(F25="Short",(AND(M25&lt;&gt;"",N(M25)&lt;0))+(AND(L25&lt;&gt;"",N(L25)&lt;0))+(AND(K25&lt;&gt;"",N(K25)&lt;0))+AND(L25&lt;&gt;"",M25&lt;&gt;"",N(M25)&lt;N(L25)),(N(M25)&gt;0)+(N(L25)&gt;0)+(N(K25)&gt;0)+AND(L25&lt;&gt;"",M25&lt;&gt;"",N(M25)&gt;N(L25))))</f>
-        <v>3</v>
-      </c>
-      <c r="AC25" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC25" s="16" t="str">
         <f aca="false">IF(C25="","",IF(F25="Short",IF(N25="",0,IF(AND(N25&gt;=30,N25&lt;=50),2,IF(OR(AND(N25&gt;=25,N25&lt;30),AND(N25&gt;50,N25&lt;=60)),1,0)))+IF(P25="",0,IF(AND(IF(B25="JSE",$L$5,$L$4)&lt;&gt;"",P25&lt;IF(B25="JSE",$L$5,$L$4)),2,IF(P25&lt;0,1,0))),IF(N25="",0,IF(AND(N25&gt;=50,N25&lt;=70),2,IF(OR(AND(N25&gt;=40,N25&lt;50),AND(N25&gt;70,N25&lt;=75)),1,0)))+IF(P25="",0,IF(AND(IF(B25="JSE",$L$5,$L$4)&lt;&gt;"",P25&gt;IF(B25="JSE",$L$5,$L$4)),2,IF(P25&gt;0,1,0)))))</f>
-        <v>4</v>
-      </c>
-      <c r="AD25" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD25" s="16" t="str">
         <f aca="false">IF(C25="","",IF(F25="Short",IF(R25="",0,IF(R25&lt;=0.1,2,IF(R25&lt;=0.25,1,0))),IF(Q25="",0,IF(Q25&gt;=-0.1,2,IF(Q25&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE25" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE25" s="16" t="str">
         <f aca="false">IF(C25="","",IF(J25="",0,IF(J25&gt;=IF(B25="JSE",$L$7,$L$6),2,IF(J25&gt;=IF(B25="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF25" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF25" s="16" t="str">
         <f aca="false">IF(C25="","",IF(F25="Short",AND(T25&lt;&gt;"",N(T25)&lt;0),N(T25)&gt;0)+(N(S25)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG25" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG25" s="16" t="str">
         <f aca="false">IF(C25="","",IF(AL25="",0,IF(AL25&gt;=3,4,IF(AL25&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH25" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH25" s="16" t="str">
         <f aca="false">IF(C25="","",IF(AND(ISNUMBER(V25),ISNUMBER(A25),V25&gt;=A25,V25-A25&lt;=14),-2,0))</f>
-        <v>-2</v>
-      </c>
-      <c r="AI25" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI25" s="16" t="str">
         <f aca="false">IF(C25="","",IF(AND(F25="Short",N(U25)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ25" s="23" t="str">
         <f aca="false">IF(C25="","",SUM(AB25:AI25))</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="AK25" s="24" t="str">
         <f aca="false">IF(C25="","",IF(AJ25&gt;=14,"A",IF(AJ25&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL25" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL25" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y25="",Z25="",AA25=""),"",IF(F25="Short",IF(Z25&lt;=Y25,"",(Y25-AA25)/(Z25-Y25)),IF(Y25&lt;=Z25,"",(AA25-Y25)/(Y25-Z25)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM25" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM25" s="37" t="str">
         <f aca="false">IF(OR(Y25="",Z25="",N(Y25)=N(Z25)),"",IF(OR(AND(F25="Short",Z25&lt;Y25),AND(NOT(F25="Short"),Z25&gt;Y25)),"stop on wrong side",ABS(Y25-Z25)))</f>
-        <v>17.26</v>
-      </c>
-      <c r="AN25" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN25" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM25)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM25,2)),"")</f>
-        <v>0.02</v>
-      </c>
-      <c r="AO25" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO25" s="37" t="str">
         <f aca="false">IFERROR(IF(AN25="","",AN25*Y25),"")</f>
-        <v>6.5944</v>
-      </c>
-      <c r="AP25" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP25" s="35"/>
       <c r="AQ25" s="19"/>
       <c r="AR25" s="26"/>
       <c r="AS25" s="41" t="str">
@@ -7748,156 +7441,102 @@
       </c>
       <c r="AU25" s="14" t="str">
         <f aca="false">IF(C25="","",IF(AP25="Open position",IF(IF(F25="Short",AND(ISNUMBER(AR25),ISNUMBER(Z25),AR25&gt;=Z25),AND(ISNUMBER(AR25),ISNUMBER(Z25),AR25&lt;=Z25)),IF(F25="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F25="Short",AND(ISNUMBER(AR25),ISNUMBER(AA25),AR25&lt;=AA25),AND(ISNUMBER(AR25),ISNUMBER(AA25),AR25&gt;=AA25)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT25),AT25&gt;182),IF(F25="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT25),AT25&gt;42,ISNUMBER(AS25),AS25&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F25="Short",AND(L25&lt;&gt;"",N(L25)&gt;0),AND(L25&lt;&gt;"",N(L25)&lt;0)),IF(F25="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP25="Closed",AP25="Dropped"),"Closed",IF(AK25="A",IF(F25="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK25="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV25" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="AX25" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV25" s="35"/>
+      <c r="AX25" s="43" t="str">
         <f aca="false">IF(AND(C25&lt;&gt;"",A25=$C$4,ISNUMBER(AJ25)),AJ25+ROW()/100000,"")</f>
-        <v>11.00025</v>
+        <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="D26" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="E26" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F26" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G26" s="26" t="n">
-        <v>485.88</v>
-      </c>
+      <c r="A26" s="19"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="26"/>
       <c r="H26" s="26"/>
-      <c r="I26" s="36" t="n">
-        <v>7680617</v>
-      </c>
-      <c r="J26" s="37" t="n">
+      <c r="I26" s="36"/>
+      <c r="J26" s="37" t="str">
         <f aca="false">IF(OR(G26="",I26=""),"",G26*I26/1000000)</f>
-        <v>3731.85818796</v>
-      </c>
-      <c r="K26" s="21" t="n">
-        <v>-0.0897</v>
-      </c>
-      <c r="L26" s="21" t="n">
-        <v>-0.0552</v>
-      </c>
-      <c r="M26" s="21" t="n">
-        <v>0.5226</v>
-      </c>
-      <c r="N26" s="25" t="n">
-        <v>42.44</v>
-      </c>
-      <c r="O26" s="21" t="n">
-        <v>0.1059</v>
-      </c>
-      <c r="P26" s="21" t="n">
-        <v>1.2636</v>
-      </c>
-      <c r="Q26" s="21" t="n">
-        <v>-0.1841</v>
-      </c>
-      <c r="R26" s="21" t="n">
-        <v>3.4083</v>
-      </c>
-      <c r="S26" s="38" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="T26" s="21" t="n">
-        <v>1.514</v>
-      </c>
-      <c r="U26" s="21" t="n">
-        <v>0.0469</v>
-      </c>
-      <c r="V26" s="19" t="n">
-        <v>46350</v>
-      </c>
-      <c r="W26" s="26" t="n">
-        <v>31.67</v>
-      </c>
-      <c r="X26" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y26" s="26" t="n">
-        <v>438.62</v>
-      </c>
-      <c r="Z26" s="26" t="n">
-        <v>501.96</v>
-      </c>
-      <c r="AA26" s="26" t="n">
-        <v>248.6</v>
-      </c>
-      <c r="AB26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="26"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="26"/>
+      <c r="Z26" s="26"/>
+      <c r="AA26" s="26"/>
+      <c r="AB26" s="16" t="str">
         <f aca="false">IF(C26="","",IF(F26="Short",(AND(M26&lt;&gt;"",N(M26)&lt;0))+(AND(L26&lt;&gt;"",N(L26)&lt;0))+(AND(K26&lt;&gt;"",N(K26)&lt;0))+AND(L26&lt;&gt;"",M26&lt;&gt;"",N(M26)&lt;N(L26)),(N(M26)&gt;0)+(N(L26)&gt;0)+(N(K26)&gt;0)+AND(L26&lt;&gt;"",M26&lt;&gt;"",N(M26)&gt;N(L26))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC26" s="16" t="str">
         <f aca="false">IF(C26="","",IF(F26="Short",IF(N26="",0,IF(AND(N26&gt;=30,N26&lt;=50),2,IF(OR(AND(N26&gt;=25,N26&lt;30),AND(N26&gt;50,N26&lt;=60)),1,0)))+IF(P26="",0,IF(AND(IF(B26="JSE",$L$5,$L$4)&lt;&gt;"",P26&lt;IF(B26="JSE",$L$5,$L$4)),2,IF(P26&lt;0,1,0))),IF(N26="",0,IF(AND(N26&gt;=50,N26&lt;=70),2,IF(OR(AND(N26&gt;=40,N26&lt;50),AND(N26&gt;70,N26&lt;=75)),1,0)))+IF(P26="",0,IF(AND(IF(B26="JSE",$L$5,$L$4)&lt;&gt;"",P26&gt;IF(B26="JSE",$L$5,$L$4)),2,IF(P26&gt;0,1,0)))))</f>
-        <v>2</v>
-      </c>
-      <c r="AD26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD26" s="16" t="str">
         <f aca="false">IF(C26="","",IF(F26="Short",IF(R26="",0,IF(R26&lt;=0.1,2,IF(R26&lt;=0.25,1,0))),IF(Q26="",0,IF(Q26&gt;=-0.1,2,IF(Q26&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE26" s="16" t="str">
         <f aca="false">IF(C26="","",IF(J26="",0,IF(J26&gt;=IF(B26="JSE",$L$7,$L$6),2,IF(J26&gt;=IF(B26="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF26" s="16" t="str">
         <f aca="false">IF(C26="","",IF(F26="Short",AND(T26&lt;&gt;"",N(T26)&lt;0),N(T26)&gt;0)+(N(S26)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG26" s="16" t="str">
         <f aca="false">IF(C26="","",IF(AL26="",0,IF(AL26&gt;=3,4,IF(AL26&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH26" s="16" t="str">
         <f aca="false">IF(C26="","",IF(AND(ISNUMBER(V26),ISNUMBER(A26),V26&gt;=A26,V26-A26&lt;=14),-2,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI26" s="16" t="str">
         <f aca="false">IF(C26="","",IF(AND(F26="Short",N(U26)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ26" s="23" t="str">
         <f aca="false">IF(C26="","",SUM(AB26:AI26))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AK26" s="24" t="str">
         <f aca="false">IF(C26="","",IF(AJ26&gt;=14,"A",IF(AJ26&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL26" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL26" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y26="",Z26="",AA26=""),"",IF(F26="Short",IF(Z26&lt;=Y26,"",(Y26-AA26)/(Z26-Y26)),IF(Y26&lt;=Z26,"",(AA26-Y26)/(Y26-Z26)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM26" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM26" s="37" t="str">
         <f aca="false">IF(OR(Y26="",Z26="",N(Y26)=N(Z26)),"",IF(OR(AND(F26="Short",Z26&lt;Y26),AND(NOT(F26="Short"),Z26&gt;Y26)),"stop on wrong side",ABS(Y26-Z26)))</f>
-        <v>63.34</v>
-      </c>
-      <c r="AN26" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN26" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM26)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM26,2)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AO26" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO26" s="37" t="str">
         <f aca="false">IFERROR(IF(AN26="","",AN26*Y26),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AP26" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP26" s="35"/>
       <c r="AQ26" s="19"/>
       <c r="AR26" s="26"/>
       <c r="AS26" s="41" t="str">
@@ -7910,156 +7549,102 @@
       </c>
       <c r="AU26" s="14" t="str">
         <f aca="false">IF(C26="","",IF(AP26="Open position",IF(IF(F26="Short",AND(ISNUMBER(AR26),ISNUMBER(Z26),AR26&gt;=Z26),AND(ISNUMBER(AR26),ISNUMBER(Z26),AR26&lt;=Z26)),IF(F26="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F26="Short",AND(ISNUMBER(AR26),ISNUMBER(AA26),AR26&lt;=AA26),AND(ISNUMBER(AR26),ISNUMBER(AA26),AR26&gt;=AA26)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT26),AT26&gt;182),IF(F26="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT26),AT26&gt;42,ISNUMBER(AS26),AS26&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F26="Short",AND(L26&lt;&gt;"",N(L26)&gt;0),AND(L26&lt;&gt;"",N(L26)&lt;0)),IF(F26="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP26="Closed",AP26="Dropped"),"Closed",IF(AK26="A",IF(F26="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK26="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV26" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="AX26" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV26" s="35"/>
+      <c r="AX26" s="43" t="str">
         <f aca="false">IF(AND(C26&lt;&gt;"",A26=$C$4,ISNUMBER(AJ26)),AJ26+ROW()/100000,"")</f>
-        <v>10.00026</v>
+        <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B27" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C27" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="D27" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="E27" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G27" s="26" t="n">
-        <v>341.35</v>
-      </c>
+      <c r="A27" s="19"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="26"/>
       <c r="H27" s="26"/>
-      <c r="I27" s="36" t="n">
-        <v>1226576</v>
-      </c>
-      <c r="J27" s="37" t="n">
+      <c r="I27" s="36"/>
+      <c r="J27" s="37" t="str">
         <f aca="false">IF(OR(G27="",I27=""),"",G27*I27/1000000)</f>
-        <v>418.6917176</v>
-      </c>
-      <c r="K27" s="21" t="n">
-        <v>-0.0601</v>
-      </c>
-      <c r="L27" s="21" t="n">
-        <v>-0.0068</v>
-      </c>
-      <c r="M27" s="21" t="n">
-        <v>0.0914</v>
-      </c>
-      <c r="N27" s="25" t="n">
-        <v>43.84</v>
-      </c>
-      <c r="O27" s="21" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="P27" s="21" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="Q27" s="21" t="n">
-        <v>-0.1246</v>
-      </c>
-      <c r="R27" s="21" t="n">
-        <v>1.0901</v>
-      </c>
-      <c r="S27" s="38" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="T27" s="21" t="n">
-        <v>0.6025</v>
-      </c>
-      <c r="U27" s="21" t="n">
-        <v>0.0144</v>
-      </c>
-      <c r="V27" s="19" t="n">
-        <v>46349</v>
-      </c>
-      <c r="W27" s="26" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="X27" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y27" s="26" t="n">
-        <v>322.42</v>
-      </c>
-      <c r="Z27" s="26" t="n">
-        <v>347.22</v>
-      </c>
-      <c r="AA27" s="26" t="n">
-        <v>248.02</v>
-      </c>
-      <c r="AB27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="21"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="35"/>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="26"/>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="16" t="str">
         <f aca="false">IF(C27="","",IF(F27="Short",(AND(M27&lt;&gt;"",N(M27)&lt;0))+(AND(L27&lt;&gt;"",N(L27)&lt;0))+(AND(K27&lt;&gt;"",N(K27)&lt;0))+AND(L27&lt;&gt;"",M27&lt;&gt;"",N(M27)&lt;N(L27)),(N(M27)&gt;0)+(N(L27)&gt;0)+(N(K27)&gt;0)+AND(L27&lt;&gt;"",M27&lt;&gt;"",N(M27)&gt;N(L27))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC27" s="16" t="str">
         <f aca="false">IF(C27="","",IF(F27="Short",IF(N27="",0,IF(AND(N27&gt;=30,N27&lt;=50),2,IF(OR(AND(N27&gt;=25,N27&lt;30),AND(N27&gt;50,N27&lt;=60)),1,0)))+IF(P27="",0,IF(AND(IF(B27="JSE",$L$5,$L$4)&lt;&gt;"",P27&lt;IF(B27="JSE",$L$5,$L$4)),2,IF(P27&lt;0,1,0))),IF(N27="",0,IF(AND(N27&gt;=50,N27&lt;=70),2,IF(OR(AND(N27&gt;=40,N27&lt;50),AND(N27&gt;70,N27&lt;=75)),1,0)))+IF(P27="",0,IF(AND(IF(B27="JSE",$L$5,$L$4)&lt;&gt;"",P27&gt;IF(B27="JSE",$L$5,$L$4)),2,IF(P27&gt;0,1,0)))))</f>
-        <v>4</v>
-      </c>
-      <c r="AD27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD27" s="16" t="str">
         <f aca="false">IF(C27="","",IF(F27="Short",IF(R27="",0,IF(R27&lt;=0.1,2,IF(R27&lt;=0.25,1,0))),IF(Q27="",0,IF(Q27&gt;=-0.1,2,IF(Q27&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE27" s="16" t="str">
         <f aca="false">IF(C27="","",IF(J27="",0,IF(J27&gt;=IF(B27="JSE",$L$7,$L$6),2,IF(J27&gt;=IF(B27="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF27" s="16" t="str">
         <f aca="false">IF(C27="","",IF(F27="Short",AND(T27&lt;&gt;"",N(T27)&lt;0),N(T27)&gt;0)+(N(S27)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG27" s="16" t="str">
         <f aca="false">IF(C27="","",IF(AL27="",0,IF(AL27&gt;=3,4,IF(AL27&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH27" s="16" t="str">
         <f aca="false">IF(C27="","",IF(AND(ISNUMBER(V27),ISNUMBER(A27),V27&gt;=A27,V27-A27&lt;=14),-2,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI27" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI27" s="16" t="str">
         <f aca="false">IF(C27="","",IF(AND(F27="Short",N(U27)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ27" s="23" t="str">
         <f aca="false">IF(C27="","",SUM(AB27:AI27))</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="AK27" s="24" t="str">
         <f aca="false">IF(C27="","",IF(AJ27&gt;=14,"A",IF(AJ27&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL27" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL27" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y27="",Z27="",AA27=""),"",IF(F27="Short",IF(Z27&lt;=Y27,"",(Y27-AA27)/(Z27-Y27)),IF(Y27&lt;=Z27,"",(AA27-Y27)/(Y27-Z27)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM27" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM27" s="37" t="str">
         <f aca="false">IF(OR(Y27="",Z27="",N(Y27)=N(Z27)),"",IF(OR(AND(F27="Short",Z27&lt;Y27),AND(NOT(F27="Short"),Z27&gt;Y27)),"stop on wrong side",ABS(Y27-Z27)))</f>
-        <v>24.8</v>
-      </c>
-      <c r="AN27" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN27" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM27)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM27,2)),"")</f>
-        <v>0.01</v>
-      </c>
-      <c r="AO27" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO27" s="37" t="str">
         <f aca="false">IFERROR(IF(AN27="","",AN27*Y27),"")</f>
-        <v>3.2242</v>
-      </c>
-      <c r="AP27" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP27" s="35"/>
       <c r="AQ27" s="19"/>
       <c r="AR27" s="26"/>
       <c r="AS27" s="41" t="str">
@@ -8072,156 +7657,102 @@
       </c>
       <c r="AU27" s="14" t="str">
         <f aca="false">IF(C27="","",IF(AP27="Open position",IF(IF(F27="Short",AND(ISNUMBER(AR27),ISNUMBER(Z27),AR27&gt;=Z27),AND(ISNUMBER(AR27),ISNUMBER(Z27),AR27&lt;=Z27)),IF(F27="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F27="Short",AND(ISNUMBER(AR27),ISNUMBER(AA27),AR27&lt;=AA27),AND(ISNUMBER(AR27),ISNUMBER(AA27),AR27&gt;=AA27)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT27),AT27&gt;182),IF(F27="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT27),AT27&gt;42,ISNUMBER(AS27),AS27&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F27="Short",AND(L27&lt;&gt;"",N(L27)&gt;0),AND(L27&lt;&gt;"",N(L27)&lt;0)),IF(F27="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP27="Closed",AP27="Dropped"),"Closed",IF(AK27="A",IF(F27="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK27="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV27" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="AX27" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV27" s="35"/>
+      <c r="AX27" s="43" t="str">
         <f aca="false">IF(AND(C27&lt;&gt;"",A27=$C$4,ISNUMBER(AJ27)),AJ27+ROW()/100000,"")</f>
-        <v>12.00027</v>
+        <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B28" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="D28" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="E28" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F28" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G28" s="26" t="n">
-        <v>79.2</v>
-      </c>
+      <c r="A28" s="19"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="26"/>
       <c r="H28" s="26"/>
-      <c r="I28" s="36" t="n">
-        <v>12129273</v>
-      </c>
-      <c r="J28" s="37" t="n">
+      <c r="I28" s="36"/>
+      <c r="J28" s="37" t="str">
         <f aca="false">IF(OR(G28="",I28=""),"",G28*I28/1000000)</f>
-        <v>960.6384216</v>
-      </c>
-      <c r="K28" s="21" t="n">
-        <v>-0.059</v>
-      </c>
-      <c r="L28" s="21" t="n">
-        <v>-0.0338</v>
-      </c>
-      <c r="M28" s="21" t="n">
-        <v>0.0532</v>
-      </c>
-      <c r="N28" s="25" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="O28" s="21" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>0.0693</v>
-      </c>
-      <c r="Q28" s="21" t="n">
-        <v>-0.1193</v>
-      </c>
-      <c r="R28" s="21" t="n">
-        <v>0.3421</v>
-      </c>
-      <c r="S28" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" s="21" t="n">
-        <v>0.6088</v>
-      </c>
-      <c r="U28" s="21" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="V28" s="19" t="n">
-        <v>46323</v>
-      </c>
-      <c r="W28" s="26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X28" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y28" s="26" t="n">
-        <v>77.72</v>
-      </c>
-      <c r="Z28" s="26" t="n">
-        <v>83.08</v>
-      </c>
-      <c r="AA28" s="26" t="n">
-        <v>61.64</v>
-      </c>
-      <c r="AB28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="21"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="26"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="26"/>
+      <c r="AA28" s="26"/>
+      <c r="AB28" s="16" t="str">
         <f aca="false">IF(C28="","",IF(F28="Short",(AND(M28&lt;&gt;"",N(M28)&lt;0))+(AND(L28&lt;&gt;"",N(L28)&lt;0))+(AND(K28&lt;&gt;"",N(K28)&lt;0))+AND(L28&lt;&gt;"",M28&lt;&gt;"",N(M28)&lt;N(L28)),(N(M28)&gt;0)+(N(L28)&gt;0)+(N(K28)&gt;0)+AND(L28&lt;&gt;"",M28&lt;&gt;"",N(M28)&gt;N(L28))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC28" s="16" t="str">
         <f aca="false">IF(C28="","",IF(F28="Short",IF(N28="",0,IF(AND(N28&gt;=30,N28&lt;=50),2,IF(OR(AND(N28&gt;=25,N28&lt;30),AND(N28&gt;50,N28&lt;=60)),1,0)))+IF(P28="",0,IF(AND(IF(B28="JSE",$L$5,$L$4)&lt;&gt;"",P28&lt;IF(B28="JSE",$L$5,$L$4)),2,IF(P28&lt;0,1,0))),IF(N28="",0,IF(AND(N28&gt;=50,N28&lt;=70),2,IF(OR(AND(N28&gt;=40,N28&lt;50),AND(N28&gt;70,N28&lt;=75)),1,0)))+IF(P28="",0,IF(AND(IF(B28="JSE",$L$5,$L$4)&lt;&gt;"",P28&gt;IF(B28="JSE",$L$5,$L$4)),2,IF(P28&gt;0,1,0)))))</f>
-        <v>4</v>
-      </c>
-      <c r="AD28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD28" s="16" t="str">
         <f aca="false">IF(C28="","",IF(F28="Short",IF(R28="",0,IF(R28&lt;=0.1,2,IF(R28&lt;=0.25,1,0))),IF(Q28="",0,IF(Q28&gt;=-0.1,2,IF(Q28&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE28" s="16" t="str">
         <f aca="false">IF(C28="","",IF(J28="",0,IF(J28&gt;=IF(B28="JSE",$L$7,$L$6),2,IF(J28&gt;=IF(B28="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF28" s="16" t="str">
         <f aca="false">IF(C28="","",IF(F28="Short",AND(T28&lt;&gt;"",N(T28)&lt;0),N(T28)&gt;0)+(N(S28)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG28" s="16" t="str">
         <f aca="false">IF(C28="","",IF(AL28="",0,IF(AL28&gt;=3,4,IF(AL28&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH28" s="16" t="str">
         <f aca="false">IF(C28="","",IF(AND(ISNUMBER(V28),ISNUMBER(A28),V28&gt;=A28,V28-A28&lt;=14),-2,0))</f>
-        <v>-2</v>
-      </c>
-      <c r="AI28" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI28" s="16" t="str">
         <f aca="false">IF(C28="","",IF(AND(F28="Short",N(U28)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ28" s="23" t="str">
         <f aca="false">IF(C28="","",SUM(AB28:AI28))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AK28" s="24" t="str">
         <f aca="false">IF(C28="","",IF(AJ28&gt;=14,"A",IF(AJ28&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL28" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL28" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y28="",Z28="",AA28=""),"",IF(F28="Short",IF(Z28&lt;=Y28,"",(Y28-AA28)/(Z28-Y28)),IF(Y28&lt;=Z28,"",(AA28-Y28)/(Y28-Z28)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM28" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM28" s="37" t="str">
         <f aca="false">IF(OR(Y28="",Z28="",N(Y28)=N(Z28)),"",IF(OR(AND(F28="Short",Z28&lt;Y28),AND(NOT(F28="Short"),Z28&gt;Y28)),"stop on wrong side",ABS(Y28-Z28)))</f>
-        <v>5.36</v>
-      </c>
-      <c r="AN28" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN28" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM28)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM28,2)),"")</f>
-        <v>0.08</v>
-      </c>
-      <c r="AO28" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO28" s="37" t="str">
         <f aca="false">IFERROR(IF(AN28="","",AN28*Y28),"")</f>
-        <v>6.2176</v>
-      </c>
-      <c r="AP28" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP28" s="35"/>
       <c r="AQ28" s="19"/>
       <c r="AR28" s="26"/>
       <c r="AS28" s="41" t="str">
@@ -8234,154 +7765,102 @@
       </c>
       <c r="AU28" s="14" t="str">
         <f aca="false">IF(C28="","",IF(AP28="Open position",IF(IF(F28="Short",AND(ISNUMBER(AR28),ISNUMBER(Z28),AR28&gt;=Z28),AND(ISNUMBER(AR28),ISNUMBER(Z28),AR28&lt;=Z28)),IF(F28="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F28="Short",AND(ISNUMBER(AR28),ISNUMBER(AA28),AR28&lt;=AA28),AND(ISNUMBER(AR28),ISNUMBER(AA28),AR28&gt;=AA28)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT28),AT28&gt;182),IF(F28="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT28),AT28&gt;42,ISNUMBER(AS28),AS28&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F28="Short",AND(L28&lt;&gt;"",N(L28)&gt;0),AND(L28&lt;&gt;"",N(L28)&lt;0)),IF(F28="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP28="Closed",AP28="Dropped"),"Closed",IF(AK28="A",IF(F28="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK28="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV28" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="AX28" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV28" s="35"/>
+      <c r="AX28" s="43" t="str">
         <f aca="false">IF(AND(C28&lt;&gt;"",A28=$C$4,ISNUMBER(AJ28)),AJ28+ROW()/100000,"")</f>
-        <v>10.00028</v>
+        <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B29" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="D29" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="E29" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F29" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G29" s="26" t="n">
-        <v>37.53</v>
-      </c>
+      <c r="A29" s="19"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="26"/>
       <c r="H29" s="26"/>
-      <c r="I29" s="36" t="n">
-        <v>33149133</v>
-      </c>
-      <c r="J29" s="37" t="n">
+      <c r="I29" s="36"/>
+      <c r="J29" s="37" t="str">
         <f aca="false">IF(OR(G29="",I29=""),"",G29*I29/1000000)</f>
-        <v>1244.08696149</v>
-      </c>
-      <c r="K29" s="21" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="L29" s="21" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="M29" s="21" t="n">
-        <v>-0.2017</v>
-      </c>
-      <c r="N29" s="25" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="O29" s="21" t="n">
-        <v>-0.0844</v>
-      </c>
-      <c r="P29" s="21" t="n">
-        <v>-0.1784</v>
-      </c>
-      <c r="Q29" s="21" t="n">
-        <v>-0.4672</v>
-      </c>
-      <c r="R29" s="21" t="n">
-        <v>0.1739</v>
-      </c>
-      <c r="S29" s="38" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T29" s="21" t="n">
-        <v>-0.1642</v>
-      </c>
-      <c r="U29" s="21" t="n">
-        <v>0.0842</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="21"/>
+      <c r="U29" s="21"/>
       <c r="V29" s="19"/>
-      <c r="W29" s="26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X29" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y29" s="26" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="Z29" s="26" t="n">
-        <v>34.03</v>
-      </c>
-      <c r="AA29" s="26" t="n">
-        <v>25.55</v>
-      </c>
-      <c r="AB29" s="16" t="n">
+      <c r="W29" s="26"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="26"/>
+      <c r="Z29" s="26"/>
+      <c r="AA29" s="26"/>
+      <c r="AB29" s="16" t="str">
         <f aca="false">IF(C29="","",IF(F29="Short",(AND(M29&lt;&gt;"",N(M29)&lt;0))+(AND(L29&lt;&gt;"",N(L29)&lt;0))+(AND(K29&lt;&gt;"",N(K29)&lt;0))+AND(L29&lt;&gt;"",M29&lt;&gt;"",N(M29)&lt;N(L29)),(N(M29)&gt;0)+(N(L29)&gt;0)+(N(K29)&gt;0)+AND(L29&lt;&gt;"",M29&lt;&gt;"",N(M29)&gt;N(L29))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC29" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC29" s="16" t="str">
         <f aca="false">IF(C29="","",IF(F29="Short",IF(N29="",0,IF(AND(N29&gt;=30,N29&lt;=50),2,IF(OR(AND(N29&gt;=25,N29&lt;30),AND(N29&gt;50,N29&lt;=60)),1,0)))+IF(P29="",0,IF(AND(IF(B29="JSE",$L$5,$L$4)&lt;&gt;"",P29&lt;IF(B29="JSE",$L$5,$L$4)),2,IF(P29&lt;0,1,0))),IF(N29="",0,IF(AND(N29&gt;=50,N29&lt;=70),2,IF(OR(AND(N29&gt;=40,N29&lt;50),AND(N29&gt;70,N29&lt;=75)),1,0)))+IF(P29="",0,IF(AND(IF(B29="JSE",$L$5,$L$4)&lt;&gt;"",P29&gt;IF(B29="JSE",$L$5,$L$4)),2,IF(P29&gt;0,1,0)))))</f>
-        <v>3</v>
-      </c>
-      <c r="AD29" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD29" s="16" t="str">
         <f aca="false">IF(C29="","",IF(F29="Short",IF(R29="",0,IF(R29&lt;=0.1,2,IF(R29&lt;=0.25,1,0))),IF(Q29="",0,IF(Q29&gt;=-0.1,2,IF(Q29&gt;=-0.25,1,0)))))</f>
-        <v>1</v>
-      </c>
-      <c r="AE29" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE29" s="16" t="str">
         <f aca="false">IF(C29="","",IF(J29="",0,IF(J29&gt;=IF(B29="JSE",$L$7,$L$6),2,IF(J29&gt;=IF(B29="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF29" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF29" s="16" t="str">
         <f aca="false">IF(C29="","",IF(F29="Short",AND(T29&lt;&gt;"",N(T29)&lt;0),N(T29)&gt;0)+(N(S29)&gt;=1.5))</f>
-        <v>1</v>
-      </c>
-      <c r="AG29" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG29" s="16" t="str">
         <f aca="false">IF(C29="","",IF(AL29="",0,IF(AL29&gt;=3,4,IF(AL29&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH29" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH29" s="16" t="str">
         <f aca="false">IF(C29="","",IF(AND(ISNUMBER(V29),ISNUMBER(A29),V29&gt;=A29,V29-A29&lt;=14),-2,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI29" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI29" s="16" t="str">
         <f aca="false">IF(C29="","",IF(AND(F29="Short",N(U29)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ29" s="23" t="str">
         <f aca="false">IF(C29="","",SUM(AB29:AI29))</f>
-        <v>13</v>
+        <v/>
       </c>
       <c r="AK29" s="24" t="str">
         <f aca="false">IF(C29="","",IF(AJ29&gt;=14,"A",IF(AJ29&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL29" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL29" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y29="",Z29="",AA29=""),"",IF(F29="Short",IF(Z29&lt;=Y29,"",(Y29-AA29)/(Z29-Y29)),IF(Y29&lt;=Z29,"",(AA29-Y29)/(Y29-Z29)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM29" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM29" s="37" t="str">
         <f aca="false">IF(OR(Y29="",Z29="",N(Y29)=N(Z29)),"",IF(OR(AND(F29="Short",Z29&lt;Y29),AND(NOT(F29="Short"),Z29&gt;Y29)),"stop on wrong side",ABS(Y29-Z29)))</f>
-        <v>2.12</v>
-      </c>
-      <c r="AN29" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN29" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM29)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM29,2)),"")</f>
-        <v>0.21</v>
-      </c>
-      <c r="AO29" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO29" s="37" t="str">
         <f aca="false">IFERROR(IF(AN29="","",AN29*Y29),"")</f>
-        <v>6.7011</v>
-      </c>
-      <c r="AP29" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP29" s="35"/>
       <c r="AQ29" s="19"/>
       <c r="AR29" s="26"/>
       <c r="AS29" s="41" t="str">
@@ -8394,154 +7873,102 @@
       </c>
       <c r="AU29" s="14" t="str">
         <f aca="false">IF(C29="","",IF(AP29="Open position",IF(IF(F29="Short",AND(ISNUMBER(AR29),ISNUMBER(Z29),AR29&gt;=Z29),AND(ISNUMBER(AR29),ISNUMBER(Z29),AR29&lt;=Z29)),IF(F29="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F29="Short",AND(ISNUMBER(AR29),ISNUMBER(AA29),AR29&lt;=AA29),AND(ISNUMBER(AR29),ISNUMBER(AA29),AR29&gt;=AA29)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT29),AT29&gt;182),IF(F29="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT29),AT29&gt;42,ISNUMBER(AS29),AS29&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F29="Short",AND(L29&lt;&gt;"",N(L29)&gt;0),AND(L29&lt;&gt;"",N(L29)&lt;0)),IF(F29="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP29="Closed",AP29="Dropped"),"Closed",IF(AK29="A",IF(F29="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK29="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV29" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="AX29" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV29" s="35"/>
+      <c r="AX29" s="43" t="str">
         <f aca="false">IF(AND(C29&lt;&gt;"",A29=$C$4,ISNUMBER(AJ29)),AJ29+ROW()/100000,"")</f>
-        <v>13.00029</v>
+        <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B30" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C30" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="D30" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="E30" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F30" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G30" s="26" t="n">
-        <v>697.52</v>
-      </c>
+      <c r="A30" s="19"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="26"/>
-      <c r="I30" s="36" t="n">
-        <v>19309160</v>
-      </c>
-      <c r="J30" s="37" t="n">
+      <c r="I30" s="36"/>
+      <c r="J30" s="37" t="str">
         <f aca="false">IF(OR(G30="",I30=""),"",G30*I30/1000000)</f>
-        <v>13468.5252832</v>
-      </c>
-      <c r="K30" s="21" t="n">
-        <v>-0.0439</v>
-      </c>
-      <c r="L30" s="21" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="M30" s="21" t="n">
-        <v>0.1026</v>
-      </c>
-      <c r="N30" s="25" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="O30" s="21" t="n">
-        <v>0.1508</v>
-      </c>
-      <c r="P30" s="21" t="n">
-        <v>0.0338</v>
-      </c>
-      <c r="Q30" s="21" t="n">
-        <v>-0.1055</v>
-      </c>
-      <c r="R30" s="21" t="n">
-        <v>0.3407</v>
-      </c>
-      <c r="S30" s="38" t="n">
-        <v>1.51</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="21"/>
+      <c r="S30" s="38"/>
       <c r="T30" s="21"/>
-      <c r="U30" s="21" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="V30" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="W30" s="26" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X30" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y30" s="26" t="n">
-        <v>679.69</v>
-      </c>
-      <c r="Z30" s="26" t="n">
-        <v>728.69</v>
-      </c>
-      <c r="AA30" s="26" t="n">
-        <v>532.69</v>
-      </c>
-      <c r="AB30" s="16" t="n">
+      <c r="U30" s="21"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="26"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="26"/>
+      <c r="Z30" s="26"/>
+      <c r="AA30" s="26"/>
+      <c r="AB30" s="16" t="str">
         <f aca="false">IF(C30="","",IF(F30="Short",(AND(M30&lt;&gt;"",N(M30)&lt;0))+(AND(L30&lt;&gt;"",N(L30)&lt;0))+(AND(K30&lt;&gt;"",N(K30)&lt;0))+AND(L30&lt;&gt;"",M30&lt;&gt;"",N(M30)&lt;N(L30)),(N(M30)&gt;0)+(N(L30)&gt;0)+(N(K30)&gt;0)+AND(L30&lt;&gt;"",M30&lt;&gt;"",N(M30)&gt;N(L30))))</f>
-        <v>1</v>
-      </c>
-      <c r="AC30" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC30" s="16" t="str">
         <f aca="false">IF(C30="","",IF(F30="Short",IF(N30="",0,IF(AND(N30&gt;=30,N30&lt;=50),2,IF(OR(AND(N30&gt;=25,N30&lt;30),AND(N30&gt;50,N30&lt;=60)),1,0)))+IF(P30="",0,IF(AND(IF(B30="JSE",$L$5,$L$4)&lt;&gt;"",P30&lt;IF(B30="JSE",$L$5,$L$4)),2,IF(P30&lt;0,1,0))),IF(N30="",0,IF(AND(N30&gt;=50,N30&lt;=70),2,IF(OR(AND(N30&gt;=40,N30&lt;50),AND(N30&gt;70,N30&lt;=75)),1,0)))+IF(P30="",0,IF(AND(IF(B30="JSE",$L$5,$L$4)&lt;&gt;"",P30&gt;IF(B30="JSE",$L$5,$L$4)),2,IF(P30&gt;0,1,0)))))</f>
-        <v>4</v>
-      </c>
-      <c r="AD30" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD30" s="16" t="str">
         <f aca="false">IF(C30="","",IF(F30="Short",IF(R30="",0,IF(R30&lt;=0.1,2,IF(R30&lt;=0.25,1,0))),IF(Q30="",0,IF(Q30&gt;=-0.1,2,IF(Q30&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE30" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE30" s="16" t="str">
         <f aca="false">IF(C30="","",IF(J30="",0,IF(J30&gt;=IF(B30="JSE",$L$7,$L$6),2,IF(J30&gt;=IF(B30="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF30" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF30" s="16" t="str">
         <f aca="false">IF(C30="","",IF(F30="Short",AND(T30&lt;&gt;"",N(T30)&lt;0),N(T30)&gt;0)+(N(S30)&gt;=1.5))</f>
-        <v>1</v>
-      </c>
-      <c r="AG30" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG30" s="16" t="str">
         <f aca="false">IF(C30="","",IF(AL30="",0,IF(AL30&gt;=3,4,IF(AL30&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH30" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH30" s="16" t="str">
         <f aca="false">IF(C30="","",IF(AND(ISNUMBER(V30),ISNUMBER(A30),V30&gt;=A30,V30-A30&lt;=14),-2,0))</f>
-        <v>-2</v>
-      </c>
-      <c r="AI30" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI30" s="16" t="str">
         <f aca="false">IF(C30="","",IF(AND(F30="Short",N(U30)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ30" s="23" t="str">
         <f aca="false">IF(C30="","",SUM(AB30:AI30))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AK30" s="24" t="str">
         <f aca="false">IF(C30="","",IF(AJ30&gt;=14,"A",IF(AJ30&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL30" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL30" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y30="",Z30="",AA30=""),"",IF(F30="Short",IF(Z30&lt;=Y30,"",(Y30-AA30)/(Z30-Y30)),IF(Y30&lt;=Z30,"",(AA30-Y30)/(Y30-Z30)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM30" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM30" s="37" t="str">
         <f aca="false">IF(OR(Y30="",Z30="",N(Y30)=N(Z30)),"",IF(OR(AND(F30="Short",Z30&lt;Y30),AND(NOT(F30="Short"),Z30&gt;Y30)),"stop on wrong side",ABS(Y30-Z30)))</f>
-        <v>49</v>
-      </c>
-      <c r="AN30" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN30" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM30)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM30,2)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AO30" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO30" s="37" t="str">
         <f aca="false">IFERROR(IF(AN30="","",AN30*Y30),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AP30" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP30" s="35"/>
       <c r="AQ30" s="19"/>
       <c r="AR30" s="26"/>
       <c r="AS30" s="41" t="str">
@@ -8554,154 +7981,102 @@
       </c>
       <c r="AU30" s="14" t="str">
         <f aca="false">IF(C30="","",IF(AP30="Open position",IF(IF(F30="Short",AND(ISNUMBER(AR30),ISNUMBER(Z30),AR30&gt;=Z30),AND(ISNUMBER(AR30),ISNUMBER(Z30),AR30&lt;=Z30)),IF(F30="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F30="Short",AND(ISNUMBER(AR30),ISNUMBER(AA30),AR30&lt;=AA30),AND(ISNUMBER(AR30),ISNUMBER(AA30),AR30&gt;=AA30)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT30),AT30&gt;182),IF(F30="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT30),AT30&gt;42,ISNUMBER(AS30),AS30&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F30="Short",AND(L30&lt;&gt;"",N(L30)&gt;0),AND(L30&lt;&gt;"",N(L30)&lt;0)),IF(F30="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP30="Closed",AP30="Dropped"),"Closed",IF(AK30="A",IF(F30="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK30="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV30" s="35" t="s">
-        <v>245</v>
-      </c>
-      <c r="AX30" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV30" s="35"/>
+      <c r="AX30" s="43" t="str">
         <f aca="false">IF(AND(C30&lt;&gt;"",A30=$C$4,ISNUMBER(AJ30)),AJ30+ROW()/100000,"")</f>
-        <v>10.0003</v>
+        <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B31" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C31" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D31" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="E31" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F31" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G31" s="26" t="n">
-        <v>184.33</v>
-      </c>
+      <c r="A31" s="19"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="26"/>
-      <c r="I31" s="36" t="n">
-        <v>6108406</v>
-      </c>
-      <c r="J31" s="37" t="n">
+      <c r="I31" s="36"/>
+      <c r="J31" s="37" t="str">
         <f aca="false">IF(OR(G31="",I31=""),"",G31*I31/1000000)</f>
-        <v>1125.96247798</v>
-      </c>
-      <c r="K31" s="21" t="n">
-        <v>-0.0837</v>
-      </c>
-      <c r="L31" s="21" t="n">
-        <v>-0.0682</v>
-      </c>
-      <c r="M31" s="21" t="n">
-        <v>0.1283</v>
-      </c>
-      <c r="N31" s="25" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="O31" s="21" t="n">
-        <v>0.0437</v>
-      </c>
-      <c r="P31" s="21" t="n">
-        <v>0.0371</v>
-      </c>
-      <c r="Q31" s="21" t="n">
-        <v>-0.1522</v>
-      </c>
-      <c r="R31" s="21" t="n">
-        <v>0.6096</v>
-      </c>
-      <c r="S31" s="38" t="n">
-        <v>1.08</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="38"/>
       <c r="T31" s="21"/>
-      <c r="U31" s="21" t="n">
-        <v>0.0114</v>
-      </c>
-      <c r="V31" s="19" t="n">
-        <v>46329</v>
-      </c>
-      <c r="W31" s="26" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="X31" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y31" s="26" t="n">
-        <v>176.42</v>
-      </c>
-      <c r="Z31" s="26" t="n">
-        <v>192.82</v>
-      </c>
-      <c r="AA31" s="26" t="n">
-        <v>127.22</v>
-      </c>
-      <c r="AB31" s="16" t="n">
+      <c r="U31" s="21"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="26"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="26"/>
+      <c r="Z31" s="26"/>
+      <c r="AA31" s="26"/>
+      <c r="AB31" s="16" t="str">
         <f aca="false">IF(C31="","",IF(F31="Short",(AND(M31&lt;&gt;"",N(M31)&lt;0))+(AND(L31&lt;&gt;"",N(L31)&lt;0))+(AND(K31&lt;&gt;"",N(K31)&lt;0))+AND(L31&lt;&gt;"",M31&lt;&gt;"",N(M31)&lt;N(L31)),(N(M31)&gt;0)+(N(L31)&gt;0)+(N(K31)&gt;0)+AND(L31&lt;&gt;"",M31&lt;&gt;"",N(M31)&gt;N(L31))))</f>
-        <v>2</v>
-      </c>
-      <c r="AC31" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC31" s="16" t="str">
         <f aca="false">IF(C31="","",IF(F31="Short",IF(N31="",0,IF(AND(N31&gt;=30,N31&lt;=50),2,IF(OR(AND(N31&gt;=25,N31&lt;30),AND(N31&gt;50,N31&lt;=60)),1,0)))+IF(P31="",0,IF(AND(IF(B31="JSE",$L$5,$L$4)&lt;&gt;"",P31&lt;IF(B31="JSE",$L$5,$L$4)),2,IF(P31&lt;0,1,0))),IF(N31="",0,IF(AND(N31&gt;=50,N31&lt;=70),2,IF(OR(AND(N31&gt;=40,N31&lt;50),AND(N31&gt;70,N31&lt;=75)),1,0)))+IF(P31="",0,IF(AND(IF(B31="JSE",$L$5,$L$4)&lt;&gt;"",P31&gt;IF(B31="JSE",$L$5,$L$4)),2,IF(P31&gt;0,1,0)))))</f>
-        <v>4</v>
-      </c>
-      <c r="AD31" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD31" s="16" t="str">
         <f aca="false">IF(C31="","",IF(F31="Short",IF(R31="",0,IF(R31&lt;=0.1,2,IF(R31&lt;=0.25,1,0))),IF(Q31="",0,IF(Q31&gt;=-0.1,2,IF(Q31&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE31" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE31" s="16" t="str">
         <f aca="false">IF(C31="","",IF(J31="",0,IF(J31&gt;=IF(B31="JSE",$L$7,$L$6),2,IF(J31&gt;=IF(B31="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF31" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF31" s="16" t="str">
         <f aca="false">IF(C31="","",IF(F31="Short",AND(T31&lt;&gt;"",N(T31)&lt;0),N(T31)&gt;0)+(N(S31)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG31" s="16" t="str">
         <f aca="false">IF(C31="","",IF(AL31="",0,IF(AL31&gt;=3,4,IF(AL31&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH31" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH31" s="16" t="str">
         <f aca="false">IF(C31="","",IF(AND(ISNUMBER(V31),ISNUMBER(A31),V31&gt;=A31,V31-A31&lt;=14),-2,0))</f>
-        <v>-2</v>
-      </c>
-      <c r="AI31" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI31" s="16" t="str">
         <f aca="false">IF(C31="","",IF(AND(F31="Short",N(U31)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ31" s="23" t="str">
         <f aca="false">IF(C31="","",SUM(AB31:AI31))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="AK31" s="24" t="str">
         <f aca="false">IF(C31="","",IF(AJ31&gt;=14,"A",IF(AJ31&gt;=10,"B","C")))</f>
-        <v>B</v>
-      </c>
-      <c r="AL31" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL31" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y31="",Z31="",AA31=""),"",IF(F31="Short",IF(Z31&lt;=Y31,"",(Y31-AA31)/(Z31-Y31)),IF(Y31&lt;=Z31,"",(AA31-Y31)/(Y31-Z31)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM31" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM31" s="37" t="str">
         <f aca="false">IF(OR(Y31="",Z31="",N(Y31)=N(Z31)),"",IF(OR(AND(F31="Short",Z31&lt;Y31),AND(NOT(F31="Short"),Z31&gt;Y31)),"stop on wrong side",ABS(Y31-Z31)))</f>
-        <v>16.4</v>
-      </c>
-      <c r="AN31" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN31" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM31)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM31,2)),"")</f>
-        <v>0.02</v>
-      </c>
-      <c r="AO31" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO31" s="37" t="str">
         <f aca="false">IFERROR(IF(AN31="","",AN31*Y31),"")</f>
-        <v>3.5284</v>
-      </c>
-      <c r="AP31" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP31" s="35"/>
       <c r="AQ31" s="19"/>
       <c r="AR31" s="26"/>
       <c r="AS31" s="41" t="str">
@@ -8714,154 +8089,102 @@
       </c>
       <c r="AU31" s="14" t="str">
         <f aca="false">IF(C31="","",IF(AP31="Open position",IF(IF(F31="Short",AND(ISNUMBER(AR31),ISNUMBER(Z31),AR31&gt;=Z31),AND(ISNUMBER(AR31),ISNUMBER(Z31),AR31&lt;=Z31)),IF(F31="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F31="Short",AND(ISNUMBER(AR31),ISNUMBER(AA31),AR31&lt;=AA31),AND(ISNUMBER(AR31),ISNUMBER(AA31),AR31&gt;=AA31)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT31),AT31&gt;182),IF(F31="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT31),AT31&gt;42,ISNUMBER(AS31),AS31&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F31="Short",AND(L31&lt;&gt;"",N(L31)&gt;0),AND(L31&lt;&gt;"",N(L31)&lt;0)),IF(F31="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP31="Closed",AP31="Dropped"),"Closed",IF(AK31="A",IF(F31="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK31="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Watch — wait for setup</v>
-      </c>
-      <c r="AV31" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="AX31" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV31" s="35"/>
+      <c r="AX31" s="43" t="str">
         <f aca="false">IF(AND(C31&lt;&gt;"",A31=$C$4,ISNUMBER(AJ31)),AJ31+ROW()/100000,"")</f>
-        <v>10.00031</v>
+        <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F32" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G32" s="26" t="n">
-        <v>52.49</v>
-      </c>
+      <c r="A32" s="19"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="26"/>
-      <c r="I32" s="36" t="n">
-        <v>7468324</v>
-      </c>
-      <c r="J32" s="37" t="n">
+      <c r="I32" s="36"/>
+      <c r="J32" s="37" t="str">
         <f aca="false">IF(OR(G32="",I32=""),"",G32*I32/1000000)</f>
-        <v>392.01232676</v>
-      </c>
-      <c r="K32" s="21" t="n">
-        <v>0.0331</v>
-      </c>
-      <c r="L32" s="21" t="n">
-        <v>0.0421</v>
-      </c>
-      <c r="M32" s="21" t="n">
-        <v>0.1204</v>
-      </c>
-      <c r="N32" s="25" t="n">
-        <v>62.92</v>
-      </c>
-      <c r="O32" s="21" t="n">
-        <v>0.1374</v>
-      </c>
-      <c r="P32" s="21" t="n">
-        <v>0.1714</v>
-      </c>
-      <c r="Q32" s="21" t="n">
-        <v>-0.0081</v>
-      </c>
-      <c r="R32" s="21" t="n">
-        <v>0.3469</v>
-      </c>
-      <c r="S32" s="38" t="n">
-        <v>0.85</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="38"/>
       <c r="T32" s="21"/>
-      <c r="U32" s="21" t="n">
-        <v>0.0302</v>
-      </c>
-      <c r="V32" s="19" t="n">
-        <v>46309</v>
-      </c>
-      <c r="W32" s="26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X32" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y32" s="26" t="n">
-        <v>47.21</v>
-      </c>
-      <c r="Z32" s="26" t="n">
-        <v>49.85</v>
-      </c>
-      <c r="AA32" s="26" t="n">
-        <v>39.29</v>
-      </c>
-      <c r="AB32" s="16" t="n">
+      <c r="U32" s="21"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="35"/>
+      <c r="Y32" s="26"/>
+      <c r="Z32" s="26"/>
+      <c r="AA32" s="26"/>
+      <c r="AB32" s="16" t="str">
         <f aca="false">IF(C32="","",IF(F32="Short",(AND(M32&lt;&gt;"",N(M32)&lt;0))+(AND(L32&lt;&gt;"",N(L32)&lt;0))+(AND(K32&lt;&gt;"",N(K32)&lt;0))+AND(L32&lt;&gt;"",M32&lt;&gt;"",N(M32)&lt;N(L32)),(N(M32)&gt;0)+(N(L32)&gt;0)+(N(K32)&gt;0)+AND(L32&lt;&gt;"",M32&lt;&gt;"",N(M32)&gt;N(L32))))</f>
-        <v>0</v>
-      </c>
-      <c r="AC32" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC32" s="16" t="str">
         <f aca="false">IF(C32="","",IF(F32="Short",IF(N32="",0,IF(AND(N32&gt;=30,N32&lt;=50),2,IF(OR(AND(N32&gt;=25,N32&lt;30),AND(N32&gt;50,N32&lt;=60)),1,0)))+IF(P32="",0,IF(AND(IF(B32="JSE",$L$5,$L$4)&lt;&gt;"",P32&lt;IF(B32="JSE",$L$5,$L$4)),2,IF(P32&lt;0,1,0))),IF(N32="",0,IF(AND(N32&gt;=50,N32&lt;=70),2,IF(OR(AND(N32&gt;=40,N32&lt;50),AND(N32&gt;70,N32&lt;=75)),1,0)))+IF(P32="",0,IF(AND(IF(B32="JSE",$L$5,$L$4)&lt;&gt;"",P32&gt;IF(B32="JSE",$L$5,$L$4)),2,IF(P32&gt;0,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AD32" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD32" s="16" t="str">
         <f aca="false">IF(C32="","",IF(F32="Short",IF(R32="",0,IF(R32&lt;=0.1,2,IF(R32&lt;=0.25,1,0))),IF(Q32="",0,IF(Q32&gt;=-0.1,2,IF(Q32&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE32" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE32" s="16" t="str">
         <f aca="false">IF(C32="","",IF(J32="",0,IF(J32&gt;=IF(B32="JSE",$L$7,$L$6),2,IF(J32&gt;=IF(B32="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF32" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF32" s="16" t="str">
         <f aca="false">IF(C32="","",IF(F32="Short",AND(T32&lt;&gt;"",N(T32)&lt;0),N(T32)&gt;0)+(N(S32)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG32" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG32" s="16" t="str">
         <f aca="false">IF(C32="","",IF(AL32="",0,IF(AL32&gt;=3,4,IF(AL32&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH32" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH32" s="16" t="str">
         <f aca="false">IF(C32="","",IF(AND(ISNUMBER(V32),ISNUMBER(A32),V32&gt;=A32,V32-A32&lt;=14),-2,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AI32" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI32" s="16" t="str">
         <f aca="false">IF(C32="","",IF(AND(F32="Short",N(U32)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ32" s="23" t="str">
         <f aca="false">IF(C32="","",SUM(AB32:AI32))</f>
-        <v>6</v>
+        <v/>
       </c>
       <c r="AK32" s="24" t="str">
         <f aca="false">IF(C32="","",IF(AJ32&gt;=14,"A",IF(AJ32&gt;=10,"B","C")))</f>
-        <v>C</v>
-      </c>
-      <c r="AL32" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL32" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y32="",Z32="",AA32=""),"",IF(F32="Short",IF(Z32&lt;=Y32,"",(Y32-AA32)/(Z32-Y32)),IF(Y32&lt;=Z32,"",(AA32-Y32)/(Y32-Z32)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM32" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM32" s="37" t="str">
         <f aca="false">IF(OR(Y32="",Z32="",N(Y32)=N(Z32)),"",IF(OR(AND(F32="Short",Z32&lt;Y32),AND(NOT(F32="Short"),Z32&gt;Y32)),"stop on wrong side",ABS(Y32-Z32)))</f>
-        <v>2.64</v>
-      </c>
-      <c r="AN32" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN32" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM32)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM32,2)),"")</f>
-        <v>0.17</v>
-      </c>
-      <c r="AO32" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO32" s="37" t="str">
         <f aca="false">IFERROR(IF(AN32="","",AN32*Y32),"")</f>
-        <v>8.0257</v>
-      </c>
-      <c r="AP32" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP32" s="35"/>
       <c r="AQ32" s="19"/>
       <c r="AR32" s="26"/>
       <c r="AS32" s="41" t="str">
@@ -8874,156 +8197,102 @@
       </c>
       <c r="AU32" s="14" t="str">
         <f aca="false">IF(C32="","",IF(AP32="Open position",IF(IF(F32="Short",AND(ISNUMBER(AR32),ISNUMBER(Z32),AR32&gt;=Z32),AND(ISNUMBER(AR32),ISNUMBER(Z32),AR32&lt;=Z32)),IF(F32="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F32="Short",AND(ISNUMBER(AR32),ISNUMBER(AA32),AR32&lt;=AA32),AND(ISNUMBER(AR32),ISNUMBER(AA32),AR32&gt;=AA32)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT32),AT32&gt;182),IF(F32="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT32),AT32&gt;42,ISNUMBER(AS32),AS32&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F32="Short",AND(L32&lt;&gt;"",N(L32)&gt;0),AND(L32&lt;&gt;"",N(L32)&lt;0)),IF(F32="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP32="Closed",AP32="Dropped"),"Closed",IF(AK32="A",IF(F32="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK32="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Drop or re-check next week</v>
-      </c>
-      <c r="AV32" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="AX32" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV32" s="35"/>
+      <c r="AX32" s="43" t="str">
         <f aca="false">IF(AND(C32&lt;&gt;"",A32=$C$4,ISNUMBER(AJ32)),AJ32+ROW()/100000,"")</f>
-        <v>6.00032</v>
+        <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B33" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="E33" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F33" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G33" s="26" t="n">
-        <v>552.72</v>
-      </c>
+      <c r="A33" s="19"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="26"/>
-      <c r="I33" s="36" t="n">
-        <v>22280195</v>
-      </c>
-      <c r="J33" s="37" t="n">
+      <c r="I33" s="36"/>
+      <c r="J33" s="37" t="str">
         <f aca="false">IF(OR(G33="",I33=""),"",G33*I33/1000000)</f>
-        <v>12314.7093804</v>
-      </c>
-      <c r="K33" s="21" t="n">
-        <v>-0.0772</v>
-      </c>
-      <c r="L33" s="21" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="M33" s="21" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="N33" s="25" t="n">
-        <v>45.07</v>
-      </c>
-      <c r="O33" s="21" t="n">
-        <v>0.0241</v>
-      </c>
-      <c r="P33" s="21" t="n">
-        <v>0.8214</v>
-      </c>
-      <c r="Q33" s="21" t="n">
-        <v>-0.1607</v>
-      </c>
-      <c r="R33" s="21" t="n">
-        <v>1.9366</v>
-      </c>
-      <c r="S33" s="38" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="T33" s="21" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="U33" s="21" t="n">
-        <v>0.0242</v>
-      </c>
-      <c r="V33" s="19" t="n">
-        <v>46329</v>
-      </c>
-      <c r="W33" s="26" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="X33" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y33" s="26" t="n">
-        <v>523.55</v>
-      </c>
-      <c r="Z33" s="26" t="n">
-        <v>576.65</v>
-      </c>
-      <c r="AA33" s="26" t="n">
-        <v>364.25</v>
-      </c>
-      <c r="AB33" s="16" t="n">
+        <v/>
+      </c>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="38"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="26"/>
+      <c r="X33" s="35"/>
+      <c r="Y33" s="26"/>
+      <c r="Z33" s="26"/>
+      <c r="AA33" s="26"/>
+      <c r="AB33" s="16" t="str">
         <f aca="false">IF(C33="","",IF(F33="Short",(AND(M33&lt;&gt;"",N(M33)&lt;0))+(AND(L33&lt;&gt;"",N(L33)&lt;0))+(AND(K33&lt;&gt;"",N(K33)&lt;0))+AND(L33&lt;&gt;"",M33&lt;&gt;"",N(M33)&lt;N(L33)),(N(M33)&gt;0)+(N(L33)&gt;0)+(N(K33)&gt;0)+AND(L33&lt;&gt;"",M33&lt;&gt;"",N(M33)&gt;N(L33))))</f>
-        <v>1</v>
-      </c>
-      <c r="AC33" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC33" s="16" t="str">
         <f aca="false">IF(C33="","",IF(F33="Short",IF(N33="",0,IF(AND(N33&gt;=30,N33&lt;=50),2,IF(OR(AND(N33&gt;=25,N33&lt;30),AND(N33&gt;50,N33&lt;=60)),1,0)))+IF(P33="",0,IF(AND(IF(B33="JSE",$L$5,$L$4)&lt;&gt;"",P33&lt;IF(B33="JSE",$L$5,$L$4)),2,IF(P33&lt;0,1,0))),IF(N33="",0,IF(AND(N33&gt;=50,N33&lt;=70),2,IF(OR(AND(N33&gt;=40,N33&lt;50),AND(N33&gt;70,N33&lt;=75)),1,0)))+IF(P33="",0,IF(AND(IF(B33="JSE",$L$5,$L$4)&lt;&gt;"",P33&gt;IF(B33="JSE",$L$5,$L$4)),2,IF(P33&gt;0,1,0)))))</f>
-        <v>2</v>
-      </c>
-      <c r="AD33" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD33" s="16" t="str">
         <f aca="false">IF(C33="","",IF(F33="Short",IF(R33="",0,IF(R33&lt;=0.1,2,IF(R33&lt;=0.25,1,0))),IF(Q33="",0,IF(Q33&gt;=-0.1,2,IF(Q33&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE33" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE33" s="16" t="str">
         <f aca="false">IF(C33="","",IF(J33="",0,IF(J33&gt;=IF(B33="JSE",$L$7,$L$6),2,IF(J33&gt;=IF(B33="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF33" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF33" s="16" t="str">
         <f aca="false">IF(C33="","",IF(F33="Short",AND(T33&lt;&gt;"",N(T33)&lt;0),N(T33)&gt;0)+(N(S33)&gt;=1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AG33" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG33" s="16" t="str">
         <f aca="false">IF(C33="","",IF(AL33="",0,IF(AL33&gt;=3,4,IF(AL33&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH33" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH33" s="16" t="str">
         <f aca="false">IF(C33="","",IF(AND(ISNUMBER(V33),ISNUMBER(A33),V33&gt;=A33,V33-A33&lt;=14),-2,0))</f>
-        <v>-2</v>
-      </c>
-      <c r="AI33" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI33" s="16" t="str">
         <f aca="false">IF(C33="","",IF(AND(F33="Short",N(U33)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ33" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ33" s="23" t="str">
         <f aca="false">IF(C33="","",SUM(AB33:AI33))</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="AK33" s="24" t="str">
         <f aca="false">IF(C33="","",IF(AJ33&gt;=14,"A",IF(AJ33&gt;=10,"B","C")))</f>
-        <v>C</v>
-      </c>
-      <c r="AL33" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL33" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y33="",Z33="",AA33=""),"",IF(F33="Short",IF(Z33&lt;=Y33,"",(Y33-AA33)/(Z33-Y33)),IF(Y33&lt;=Z33,"",(AA33-Y33)/(Y33-Z33)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM33" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM33" s="37" t="str">
         <f aca="false">IF(OR(Y33="",Z33="",N(Y33)=N(Z33)),"",IF(OR(AND(F33="Short",Z33&lt;Y33),AND(NOT(F33="Short"),Z33&gt;Y33)),"stop on wrong side",ABS(Y33-Z33)))</f>
-        <v>53.1</v>
-      </c>
-      <c r="AN33" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN33" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM33)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM33,2)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AO33" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO33" s="37" t="str">
         <f aca="false">IFERROR(IF(AN33="","",AN33*Y33),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AP33" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP33" s="35"/>
       <c r="AQ33" s="19"/>
       <c r="AR33" s="26"/>
       <c r="AS33" s="41" t="str">
@@ -9036,154 +8305,102 @@
       </c>
       <c r="AU33" s="14" t="str">
         <f aca="false">IF(C33="","",IF(AP33="Open position",IF(IF(F33="Short",AND(ISNUMBER(AR33),ISNUMBER(Z33),AR33&gt;=Z33),AND(ISNUMBER(AR33),ISNUMBER(Z33),AR33&lt;=Z33)),IF(F33="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F33="Short",AND(ISNUMBER(AR33),ISNUMBER(AA33),AR33&lt;=AA33),AND(ISNUMBER(AR33),ISNUMBER(AA33),AR33&gt;=AA33)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT33),AT33&gt;182),IF(F33="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT33),AT33&gt;42,ISNUMBER(AS33),AS33&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F33="Short",AND(L33&lt;&gt;"",N(L33)&gt;0),AND(L33&lt;&gt;"",N(L33)&lt;0)),IF(F33="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP33="Closed",AP33="Dropped"),"Closed",IF(AK33="A",IF(F33="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK33="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Drop or re-check next week</v>
-      </c>
-      <c r="AV33" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="AX33" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV33" s="35"/>
+      <c r="AX33" s="43" t="str">
         <f aca="false">IF(AND(C33&lt;&gt;"",A33=$C$4,ISNUMBER(AJ33)),AJ33+ROW()/100000,"")</f>
-        <v>7.00033</v>
+        <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B34" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="E34" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F34" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="G34" s="26" t="n">
-        <v>288.96</v>
-      </c>
+      <c r="A34" s="19"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="26"/>
-      <c r="I34" s="36" t="n">
-        <v>891537</v>
-      </c>
-      <c r="J34" s="37" t="n">
+      <c r="I34" s="36"/>
+      <c r="J34" s="37" t="str">
         <f aca="false">IF(OR(G34="",I34=""),"",G34*I34/1000000)</f>
-        <v>257.61853152</v>
-      </c>
-      <c r="K34" s="21" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="L34" s="21" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="M34" s="21" t="n">
-        <v>0.0862</v>
-      </c>
-      <c r="N34" s="25" t="n">
-        <v>53.74</v>
-      </c>
-      <c r="O34" s="21" t="n">
-        <v>-0.0303</v>
-      </c>
-      <c r="P34" s="21" t="n">
-        <v>0.1049</v>
-      </c>
-      <c r="Q34" s="21" t="n">
-        <v>-0.0577</v>
-      </c>
-      <c r="R34" s="21" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="S34" s="38" t="n">
-        <v>2.87</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
+      <c r="R34" s="21"/>
+      <c r="S34" s="38"/>
       <c r="T34" s="21"/>
-      <c r="U34" s="21" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="V34" s="19" t="n">
-        <v>46316</v>
-      </c>
-      <c r="W34" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="X34" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="Y34" s="26" t="n">
-        <v>274.58</v>
-      </c>
-      <c r="Z34" s="26" t="n">
-        <v>288.58</v>
-      </c>
-      <c r="AA34" s="26" t="n">
-        <v>232.58</v>
-      </c>
-      <c r="AB34" s="16" t="n">
+      <c r="U34" s="21"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="26"/>
+      <c r="X34" s="35"/>
+      <c r="Y34" s="26"/>
+      <c r="Z34" s="26"/>
+      <c r="AA34" s="26"/>
+      <c r="AB34" s="16" t="str">
         <f aca="false">IF(C34="","",IF(F34="Short",(AND(M34&lt;&gt;"",N(M34)&lt;0))+(AND(L34&lt;&gt;"",N(L34)&lt;0))+(AND(K34&lt;&gt;"",N(K34)&lt;0))+AND(L34&lt;&gt;"",M34&lt;&gt;"",N(M34)&lt;N(L34)),(N(M34)&gt;0)+(N(L34)&gt;0)+(N(K34)&gt;0)+AND(L34&lt;&gt;"",M34&lt;&gt;"",N(M34)&gt;N(L34))))</f>
-        <v>0</v>
-      </c>
-      <c r="AC34" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AC34" s="16" t="str">
         <f aca="false">IF(C34="","",IF(F34="Short",IF(N34="",0,IF(AND(N34&gt;=30,N34&lt;=50),2,IF(OR(AND(N34&gt;=25,N34&lt;30),AND(N34&gt;50,N34&lt;=60)),1,0)))+IF(P34="",0,IF(AND(IF(B34="JSE",$L$5,$L$4)&lt;&gt;"",P34&lt;IF(B34="JSE",$L$5,$L$4)),2,IF(P34&lt;0,1,0))),IF(N34="",0,IF(AND(N34&gt;=50,N34&lt;=70),2,IF(OR(AND(N34&gt;=40,N34&lt;50),AND(N34&gt;70,N34&lt;=75)),1,0)))+IF(P34="",0,IF(AND(IF(B34="JSE",$L$5,$L$4)&lt;&gt;"",P34&gt;IF(B34="JSE",$L$5,$L$4)),2,IF(P34&gt;0,1,0)))))</f>
-        <v>3</v>
-      </c>
-      <c r="AD34" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AD34" s="16" t="str">
         <f aca="false">IF(C34="","",IF(F34="Short",IF(R34="",0,IF(R34&lt;=0.1,2,IF(R34&lt;=0.25,1,0))),IF(Q34="",0,IF(Q34&gt;=-0.1,2,IF(Q34&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="AE34" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AE34" s="16" t="str">
         <f aca="false">IF(C34="","",IF(J34="",0,IF(J34&gt;=IF(B34="JSE",$L$7,$L$6),2,IF(J34&gt;=IF(B34="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v>2</v>
-      </c>
-      <c r="AF34" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AF34" s="16" t="str">
         <f aca="false">IF(C34="","",IF(F34="Short",AND(T34&lt;&gt;"",N(T34)&lt;0),N(T34)&gt;0)+(N(S34)&gt;=1.5))</f>
-        <v>1</v>
-      </c>
-      <c r="AG34" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AG34" s="16" t="str">
         <f aca="false">IF(C34="","",IF(AL34="",0,IF(AL34&gt;=3,4,IF(AL34&gt;=2,2,0))))</f>
-        <v>4</v>
-      </c>
-      <c r="AH34" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AH34" s="16" t="str">
         <f aca="false">IF(C34="","",IF(AND(ISNUMBER(V34),ISNUMBER(A34),V34&gt;=A34,V34-A34&lt;=14),-2,0))</f>
-        <v>-2</v>
-      </c>
-      <c r="AI34" s="16" t="n">
+        <v/>
+      </c>
+      <c r="AI34" s="16" t="str">
         <f aca="false">IF(C34="","",IF(AND(F34="Short",N(U34)&gt;=0.2),-1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AJ34" s="23" t="str">
         <f aca="false">IF(C34="","",SUM(AB34:AI34))</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="AK34" s="24" t="str">
         <f aca="false">IF(C34="","",IF(AJ34&gt;=14,"A",IF(AJ34&gt;=10,"B","C")))</f>
-        <v>C</v>
-      </c>
-      <c r="AL34" s="39" t="n">
+        <v/>
+      </c>
+      <c r="AL34" s="39" t="str">
         <f aca="false">IFERROR(IF(OR(Y34="",Z34="",AA34=""),"",IF(F34="Short",IF(Z34&lt;=Y34,"",(Y34-AA34)/(Z34-Y34)),IF(Y34&lt;=Z34,"",(AA34-Y34)/(Y34-Z34)))),"")</f>
-        <v>3</v>
-      </c>
-      <c r="AM34" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AM34" s="37" t="str">
         <f aca="false">IF(OR(Y34="",Z34="",N(Y34)=N(Z34)),"",IF(OR(AND(F34="Short",Z34&lt;Y34),AND(NOT(F34="Short"),Z34&gt;Y34)),"stop on wrong side",ABS(Y34-Z34)))</f>
-        <v>14</v>
-      </c>
-      <c r="AN34" s="40" t="n">
+        <v/>
+      </c>
+      <c r="AN34" s="40" t="str">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM34)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM34,2)),"")</f>
-        <v>0.03</v>
-      </c>
-      <c r="AO34" s="37" t="n">
+        <v/>
+      </c>
+      <c r="AO34" s="37" t="str">
         <f aca="false">IFERROR(IF(AN34="","",AN34*Y34),"")</f>
-        <v>8.2374</v>
-      </c>
-      <c r="AP34" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v/>
+      </c>
+      <c r="AP34" s="35"/>
       <c r="AQ34" s="19"/>
       <c r="AR34" s="26"/>
       <c r="AS34" s="41" t="str">
@@ -9196,14 +8413,12 @@
       </c>
       <c r="AU34" s="14" t="str">
         <f aca="false">IF(C34="","",IF(AP34="Open position",IF(IF(F34="Short",AND(ISNUMBER(AR34),ISNUMBER(Z34),AR34&gt;=Z34),AND(ISNUMBER(AR34),ISNUMBER(Z34),AR34&lt;=Z34)),IF(F34="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F34="Short",AND(ISNUMBER(AR34),ISNUMBER(AA34),AR34&lt;=AA34),AND(ISNUMBER(AR34),ISNUMBER(AA34),AR34&gt;=AA34)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT34),AT34&gt;182),IF(F34="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT34),AT34&gt;42,ISNUMBER(AS34),AS34&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F34="Short",AND(L34&lt;&gt;"",N(L34)&gt;0),AND(L34&lt;&gt;"",N(L34)&lt;0)),IF(F34="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP34="Closed",AP34="Dropped"),"Closed",IF(AK34="A",IF(F34="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK34="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v>Drop or re-check next week</v>
-      </c>
-      <c r="AV34" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="AX34" s="43" t="n">
+        <v/>
+      </c>
+      <c r="AV34" s="35"/>
+      <c r="AX34" s="43" t="str">
         <f aca="false">IF(AND(C34&lt;&gt;"",A34=$C$4,ISNUMBER(AJ34)),AJ34+ROW()/100000,"")</f>
-        <v>8.00034</v>
+        <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28362,7 +27577,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I68"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
@@ -28376,7 +27591,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -28387,7 +27602,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -28400,7 +27615,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -28413,7 +27628,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -28423,12 +27638,12 @@
       <c r="G5" s="44"/>
       <c r="H5" s="44"/>
       <c r="I5" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44"/>
@@ -28438,12 +27653,12 @@
       <c r="G6" s="44"/>
       <c r="H6" s="44"/>
       <c r="I6" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="B7" s="44"/>
       <c r="C7" s="44"/>
@@ -28453,12 +27668,12 @@
       <c r="G7" s="44"/>
       <c r="H7" s="44"/>
       <c r="I7" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="B8" s="44"/>
       <c r="C8" s="44"/>
@@ -28468,12 +27683,12 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="B9" s="44"/>
       <c r="C9" s="44"/>
@@ -28483,12 +27698,12 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -28498,12 +27713,12 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="B11" s="44"/>
       <c r="C11" s="44"/>
@@ -28513,12 +27728,12 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
@@ -28528,12 +27743,12 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -28543,12 +27758,12 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -28564,39 +27779,39 @@
         <v>33</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>35</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="n">
         <v>46298</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="D17" s="15" t="str">
         <f aca="false">IF(OR(B17="",C17=""),"",IF(AND(B17="Y",C17="Y"),"RISK-ON → favour longs",IF(AND(B17="N",C17="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
@@ -28614,21 +27829,21 @@
         <v>0</v>
       </c>
       <c r="H17" s="47" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="I17" s="47" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="n">
         <v>46312</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="D18" s="15" t="str">
         <f aca="false">IF(OR(B18="",C18=""),"",IF(AND(B18="Y",C18="Y"),"RISK-ON → favour longs",IF(AND(B18="N",C18="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
@@ -28646,37 +27861,31 @@
         <v>0</v>
       </c>
       <c r="H18" s="47" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="I18" s="47" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="n">
-        <v>46316</v>
-      </c>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19"/>
       <c r="B19" s="46"/>
       <c r="C19" s="46"/>
       <c r="D19" s="15" t="str">
         <f aca="false">IF(OR(B19="",C19=""),"",IF(AND(B19="Y",C19="Y"),"RISK-ON → favour longs",IF(AND(B19="N",C19="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
         <v/>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="15" t="str">
         <f aca="false">IF(A19="","",COUNTIFS('Swing Watchlist'!$A$11:$A$210,A19,'Swing Watchlist'!$C$11:$C$210,"?*"))</f>
-        <v>13</v>
-      </c>
-      <c r="F19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F19" s="15" t="str">
         <f aca="false">IF(A19="","",COUNTIFS('Swing Watchlist'!$A$11:$A$210,A19,'Swing Watchlist'!$AK$11:$AK$210,"A"))</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="47" t="n">
-        <v>0</v>
-      </c>
+        <v/>
+      </c>
+      <c r="G19" s="47"/>
       <c r="H19" s="47"/>
-      <c r="I19" s="47" t="s">
-        <v>281</v>
-      </c>
+      <c r="I19" s="47"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19"/>
@@ -29718,7 +28927,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="16"/>
@@ -29726,7 +28935,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>282</v>
+        <v>251</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -29736,7 +28945,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -29748,7 +28957,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>284</v>
+        <v>253</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -29760,10 +28969,10 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -29774,10 +28983,10 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -29788,10 +28997,10 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -29802,10 +29011,10 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -29816,10 +29025,10 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -29830,10 +29039,10 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -29844,10 +29053,10 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -29858,7 +29067,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -29870,10 +29079,10 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -29884,10 +29093,10 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -29898,10 +29107,10 @@
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -29912,10 +29121,10 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -29926,10 +29135,10 @@
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -29940,10 +29149,10 @@
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -29954,10 +29163,10 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -29971,7 +29180,7 @@
         <v>88</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -29982,7 +29191,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -29994,10 +29203,10 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>316</v>
+        <v>285</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -30008,10 +29217,10 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>318</v>
+        <v>287</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -30022,10 +29231,10 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -30078,7 +29287,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AP158"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
@@ -30109,7 +29318,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -30151,7 +29360,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -30195,20 +29404,20 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="19" t="n">
         <v>46296</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
       <c r="J4" s="22" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="K4" s="22"/>
       <c r="L4" s="23" t="n">
@@ -30224,20 +29433,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="25" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="E5" s="20"/>
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
       <c r="J5" s="22" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="K5" s="22"/>
       <c r="L5" s="24" t="str">
@@ -30247,7 +29456,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="27"/>
@@ -30272,7 +29481,7 @@
       <c r="V7" s="27"/>
       <c r="W7" s="27"/>
       <c r="X7" s="28" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="Y7" s="28"/>
       <c r="Z7" s="28"/>
@@ -30284,10 +29493,10 @@
       <c r="AF7" s="28"/>
       <c r="AG7" s="28"/>
       <c r="AH7" s="48" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="AI7" s="30" t="s">
-        <v>333</v>
+        <v>302</v>
       </c>
       <c r="AJ7" s="30"/>
       <c r="AK7" s="30"/>
@@ -30318,79 +29527,79 @@
         <v>146</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>334</v>
+        <v>303</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="L8" s="31" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="M8" s="31" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="O8" s="31" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="P8" s="31" t="s">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="Q8" s="31" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="R8" s="31" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="S8" s="31" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="T8" s="31" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="V8" s="31" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="W8" s="31" t="s">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="X8" s="32" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="Y8" s="32" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="Z8" s="32" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="AA8" s="32" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="AB8" s="32" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="AC8" s="32" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="AD8" s="32" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="AE8" s="32" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="AF8" s="32" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="AG8" s="32" t="s">
         <v>51</v>
@@ -30402,19 +29611,19 @@
         <v>172</v>
       </c>
       <c r="AJ8" s="34" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="AK8" s="34" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="AL8" s="34" t="s">
         <v>174</v>
       </c>
       <c r="AM8" s="34" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="AN8" s="34" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30532,10 +29741,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI9" s="35" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="AJ9" s="35" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="AK9" s="19" t="n">
         <v>46309</v>
@@ -30548,7 +29757,7 @@
         <v>0</v>
       </c>
       <c r="AN9" s="35" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="AP9" s="43" t="n">
         <f aca="false">IF(AND(C9&lt;&gt;"",A9=$C$4,ISNUMBER(AF9)),AF9+ROW()/100000,"")</f>
@@ -30670,10 +29879,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI10" s="35" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="AJ10" s="35" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
       <c r="AK10" s="19" t="n">
         <v>46309</v>
@@ -30686,7 +29895,7 @@
         <v>0</v>
       </c>
       <c r="AN10" s="35" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="AP10" s="43" t="n">
         <f aca="false">IF(AND(C10&lt;&gt;"",A10=$C$4,ISNUMBER(AF10)),AF10+ROW()/100000,"")</f>
@@ -30806,10 +30015,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI11" s="35" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="AJ11" s="35" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="AK11" s="19" t="n">
         <v>46309</v>
@@ -30822,7 +30031,7 @@
         <v>0</v>
       </c>
       <c r="AN11" s="35" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="AP11" s="43" t="n">
         <f aca="false">IF(AND(C11&lt;&gt;"",A11=$C$4,ISNUMBER(AF11)),AF11+ROW()/100000,"")</f>
@@ -30945,7 +30154,7 @@
         <v>192</v>
       </c>
       <c r="AJ12" s="35" t="s">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="AK12" s="19" t="n">
         <v>46309</v>
@@ -30958,7 +30167,7 @@
         <v>0</v>
       </c>
       <c r="AN12" s="35" t="s">
-        <v>365</v>
+        <v>334</v>
       </c>
       <c r="AP12" s="43" t="n">
         <f aca="false">IF(AND(C12&lt;&gt;"",A12=$C$4,ISNUMBER(AF12)),AF12+ROW()/100000,"")</f>
@@ -30973,13 +30182,13 @@
         <v>179</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>243</v>
+        <v>335</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>762.5</v>
@@ -31083,7 +30292,7 @@
         <v>192</v>
       </c>
       <c r="AJ13" s="35" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="AK13" s="19" t="n">
         <v>46309</v>
@@ -31096,7 +30305,7 @@
         <v>0</v>
       </c>
       <c r="AN13" s="35" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="AP13" s="43" t="n">
         <f aca="false">IF(AND(C13&lt;&gt;"",A13=$C$4,ISNUMBER(AF13)),AF13+ROW()/100000,"")</f>
@@ -31214,10 +30423,10 @@
         <v>Closed</v>
       </c>
       <c r="AI14" s="35" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AJ14" s="35" t="s">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="AK14" s="19" t="n">
         <v>46309</v>
@@ -31230,7 +30439,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="35" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="AP14" s="43" t="n">
         <f aca="false">IF(AND(C14&lt;&gt;"",A14=$C$4,ISNUMBER(AF14)),AF14+ROW()/100000,"")</f>
@@ -31346,10 +30555,10 @@
         <v>Closed</v>
       </c>
       <c r="AI15" s="35" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AJ15" s="35" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="AK15" s="19" t="n">
         <v>46309</v>
@@ -31362,7 +30571,7 @@
         <v>0</v>
       </c>
       <c r="AN15" s="35" t="s">
-        <v>374</v>
+        <v>344</v>
       </c>
       <c r="AP15" s="43" t="n">
         <f aca="false">IF(AND(C15&lt;&gt;"",A15=$C$4,ISNUMBER(AF15)),AF15+ROW()/100000,"")</f>
@@ -31478,10 +30687,10 @@
         <v>Closed</v>
       </c>
       <c r="AI16" s="35" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AJ16" s="35" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="AK16" s="19" t="n">
         <v>46309</v>
@@ -31494,7 +30703,7 @@
         <v>0</v>
       </c>
       <c r="AN16" s="35" t="s">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="AP16" s="43" t="n">
         <f aca="false">IF(AND(C16&lt;&gt;"",A16=$C$4,ISNUMBER(AF16)),AF16+ROW()/100000,"")</f>
@@ -31614,10 +30823,10 @@
         <v>Closed</v>
       </c>
       <c r="AI17" s="35" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AJ17" s="35" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="AK17" s="19" t="n">
         <v>46309</v>
@@ -31630,7 +30839,7 @@
         <v>0</v>
       </c>
       <c r="AN17" s="35" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="AP17" s="43" t="n">
         <f aca="false">IF(AND(C17&lt;&gt;"",A17=$C$4,ISNUMBER(AF17)),AF17+ROW()/100000,"")</f>
@@ -31750,10 +30959,10 @@
         <v>Closed</v>
       </c>
       <c r="AI18" s="35" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AJ18" s="35" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="AK18" s="19" t="n">
         <v>46309</v>
@@ -31766,7 +30975,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="35" t="s">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AP18" s="43" t="n">
         <f aca="false">IF(AND(C18&lt;&gt;"",A18=$C$4,ISNUMBER(AF18)),AF18+ROW()/100000,"")</f>
@@ -43343,7 +42552,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
@@ -43355,7 +42564,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -43364,7 +42573,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -43375,7 +42584,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -43386,7 +42595,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -43394,12 +42603,12 @@
       <c r="E5" s="44"/>
       <c r="F5" s="44"/>
       <c r="G5" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44"/>
@@ -43407,12 +42616,12 @@
       <c r="E6" s="44"/>
       <c r="F6" s="44"/>
       <c r="G6" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="B7" s="44"/>
       <c r="C7" s="44"/>
@@ -43420,12 +42629,12 @@
       <c r="E7" s="44"/>
       <c r="F7" s="44"/>
       <c r="G7" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="B8" s="44"/>
       <c r="C8" s="44"/>
@@ -43433,12 +42642,12 @@
       <c r="E8" s="44"/>
       <c r="F8" s="44"/>
       <c r="G8" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="B9" s="44"/>
       <c r="C9" s="44"/>
@@ -43446,12 +42655,12 @@
       <c r="E9" s="44"/>
       <c r="F9" s="44"/>
       <c r="G9" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -43459,12 +42668,12 @@
       <c r="E10" s="44"/>
       <c r="F10" s="44"/>
       <c r="G10" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="B11" s="44"/>
       <c r="C11" s="44"/>
@@ -43472,12 +42681,12 @@
       <c r="E11" s="44"/>
       <c r="F11" s="44"/>
       <c r="G11" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
@@ -43485,12 +42694,12 @@
       <c r="E12" s="44"/>
       <c r="F12" s="44"/>
       <c r="G12" s="45" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -43498,12 +42707,12 @@
       <c r="E13" s="44"/>
       <c r="F13" s="44"/>
       <c r="G13" s="45" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -43520,22 +42729,22 @@
         <v>35</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>43</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="n">
         <v>46296</v>
       </c>
@@ -43548,16 +42757,16 @@
         <v>5</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="G17" s="47" t="s">
-        <v>399</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43950,7 +43159,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -43959,7 +43168,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -43967,7 +43176,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -43977,7 +43186,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -43987,587 +43196,587 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="52" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="52" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="52" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="52" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="52" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="E15" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F15" s="52" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="52" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>451</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>452</v>
+        <v>422</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>453</v>
+        <v>423</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>454</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>426</v>
+      </c>
+      <c r="F18" s="52" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>396</v>
+      </c>
+      <c r="E19" s="52" t="s">
         <v>429</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>426</v>
-      </c>
-      <c r="D18" s="52" t="s">
-        <v>426</v>
-      </c>
-      <c r="E18" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="F18" s="52" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="52" t="s">
-        <v>429</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>426</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>426</v>
-      </c>
-      <c r="E19" s="52" t="s">
-        <v>459</v>
-      </c>
       <c r="F19" s="52" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>461</v>
+        <v>431</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>462</v>
+        <v>432</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>463</v>
+        <v>433</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>464</v>
+        <v>434</v>
       </c>
       <c r="C21" s="52" t="s">
+        <v>411</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>412</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>435</v>
+      </c>
+      <c r="F21" s="52" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>438</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>439</v>
+      </c>
+      <c r="E22" s="52" t="s">
+        <v>440</v>
+      </c>
+      <c r="F22" s="52" t="s">
         <v>441</v>
-      </c>
-      <c r="D21" s="52" t="s">
-        <v>442</v>
-      </c>
-      <c r="E21" s="52" t="s">
-        <v>465</v>
-      </c>
-      <c r="F21" s="52" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="52" t="s">
-        <v>429</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="C22" s="52" t="s">
-        <v>468</v>
-      </c>
-      <c r="D22" s="52" t="s">
-        <v>469</v>
-      </c>
-      <c r="E22" s="52" t="s">
-        <v>470</v>
-      </c>
-      <c r="F22" s="52" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>474</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>334</v>
+        <v>303</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D24" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E24" s="52" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="F24" s="52" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="52" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E25" s="52" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="52" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="E26" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="52" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="C27" s="52" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="D27" s="52" t="s">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="E27" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="52" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>489</v>
+        <v>459</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="E28" s="52" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
       <c r="F28" s="52" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="52" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>493</v>
+        <v>463</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>495</v>
+        <v>465</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="52" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="C30" s="52" t="s">
-        <v>498</v>
+        <v>468</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="E30" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F30" s="52" t="s">
-        <v>500</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="52" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>152</v>
       </c>
       <c r="C31" s="52" t="s">
-        <v>501</v>
+        <v>471</v>
       </c>
       <c r="D31" s="52" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>503</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="52" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
       <c r="C32" s="52" t="s">
-        <v>505</v>
+        <v>475</v>
       </c>
       <c r="D32" s="52" t="s">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="E32" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F32" s="52" t="s">
-        <v>507</v>
+        <v>477</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="52" t="s">
-        <v>508</v>
+        <v>478</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>509</v>
+        <v>479</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D33" s="52" t="s">
-        <v>511</v>
+        <v>481</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>513</v>
+        <v>483</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="53" t="s">
-        <v>514</v>
+        <v>484</v>
       </c>
       <c r="B34" s="53"/>
       <c r="C34" s="53"/>
@@ -44577,7 +43786,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>515</v>
+        <v>485</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -44587,10 +43796,10 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="54" t="s">
-        <v>516</v>
+        <v>486</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>517</v>
+        <v>487</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -44599,10 +43808,10 @@
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="54" t="s">
-        <v>518</v>
+        <v>488</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>519</v>
+        <v>489</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -44611,7 +43820,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -44621,92 +43830,92 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="55" t="s">
-        <v>521</v>
+        <v>491</v>
       </c>
       <c r="B42" s="55"/>
       <c r="C42" s="52" t="s">
-        <v>522</v>
+        <v>492</v>
       </c>
       <c r="D42" s="52" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="E42" s="52" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="F42" s="52" t="s">
-        <v>524</v>
+        <v>494</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="55" t="s">
-        <v>525</v>
+        <v>495</v>
       </c>
       <c r="B43" s="55"/>
       <c r="C43" s="52" t="s">
-        <v>526</v>
+        <v>496</v>
       </c>
       <c r="D43" s="52" t="s">
-        <v>527</v>
+        <v>497</v>
       </c>
       <c r="E43" s="52" t="s">
-        <v>528</v>
+        <v>498</v>
       </c>
       <c r="F43" s="52" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="55" t="s">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="B44" s="55"/>
       <c r="C44" s="52" t="s">
-        <v>531</v>
+        <v>501</v>
       </c>
       <c r="D44" s="52" t="s">
-        <v>532</v>
+        <v>502</v>
       </c>
       <c r="E44" s="52" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
       <c r="F44" s="52" t="s">
-        <v>534</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="55" t="s">
-        <v>535</v>
+        <v>505</v>
       </c>
       <c r="B45" s="55"/>
       <c r="C45" s="52" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
       <c r="D45" s="52" t="s">
-        <v>537</v>
+        <v>507</v>
       </c>
       <c r="E45" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F45" s="52" t="s">
-        <v>538</v>
+        <v>508</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -44715,139 +43924,139 @@
       </c>
       <c r="B46" s="55"/>
       <c r="C46" s="52" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="D46" s="52" t="s">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="E46" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F46" s="52" t="s">
-        <v>541</v>
+        <v>511</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="55" t="s">
-        <v>542</v>
+        <v>512</v>
       </c>
       <c r="B47" s="55"/>
       <c r="C47" s="52" t="s">
-        <v>543</v>
+        <v>513</v>
       </c>
       <c r="D47" s="52" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="E47" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>545</v>
+        <v>515</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="55" t="s">
-        <v>546</v>
+        <v>516</v>
       </c>
       <c r="B48" s="55"/>
       <c r="C48" s="52" t="s">
-        <v>547</v>
+        <v>517</v>
       </c>
       <c r="D48" s="52" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="E48" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="F48" s="52" t="s">
-        <v>548</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="55" t="s">
-        <v>549</v>
+        <v>519</v>
       </c>
       <c r="B49" s="55"/>
       <c r="C49" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D49" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E49" s="52" t="s">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="F49" s="52" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="55" t="s">
-        <v>552</v>
+        <v>522</v>
       </c>
       <c r="B50" s="55"/>
       <c r="C50" s="52" t="s">
-        <v>553</v>
+        <v>523</v>
       </c>
       <c r="D50" s="52" t="s">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="E50" s="52" t="s">
-        <v>555</v>
+        <v>525</v>
       </c>
       <c r="F50" s="52" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="55" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="B51" s="55"/>
       <c r="C51" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="D51" s="52" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="E51" s="52" t="s">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="F51" s="52" t="s">
-        <v>559</v>
+        <v>529</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="55" t="s">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="B52" s="55"/>
       <c r="C52" s="52" t="s">
-        <v>561</v>
+        <v>531</v>
       </c>
       <c r="D52" s="52" t="s">
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="E52" s="52" t="s">
-        <v>563</v>
+        <v>533</v>
       </c>
       <c r="F52" s="52" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="55" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="B53" s="55"/>
       <c r="C53" s="52" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
       <c r="D53" s="52" t="s">
-        <v>566</v>
+        <v>536</v>
       </c>
       <c r="E53" s="52" t="s">
-        <v>567</v>
+        <v>537</v>
       </c>
       <c r="F53" s="52"/>
     </row>

--- a/templates/LRC_Watchlist_master.xlsx
+++ b/templates/LRC_Watchlist_master.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="585">
   <si>
     <t xml:space="preserve">LRC Watchlist Builder — Swing &amp; Investment</t>
   </si>
@@ -707,6 +707,63 @@
     <t xml:space="preserve">Trigger: Sell stop below the 15-day low (49.11) — only AFTER the 14 Oct results are digested. Short entry 49.00, stop 50.96 (2×ATR 0.98), target 43.12 (3R). LRC Work-sheet 14 Oct: SELL (6-m target ~$38.37, -25%; score 3.5/5; technical: CLEARED — STAGED ENTRY). SELL (−25%) + technical clearance. Results 14 Oct (today) — wait for the reaction. 5th short: house limit is 4 open shorts, so only if one of the others has not triggered. Data 13 Oct close: stockanalysis statistics + daily history to 13 Oct (SMA20/ATR14 computed); Perf Half vs ~13 Apr close; EPS growth this yr = consensus current FY (adjusted). Perf Quarter n/f (history page holds 50 sessions). Finviz itself blocked for us — same filters applied manually. — P. Nkuna</t>
   </si>
   <si>
+    <t xml:space="preserve">Intuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONG: Trend continuation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating BUY (6-m value 426.0); NOT CLEARED. Entry 358.75, stop 332.97 (2×ATR), target 436.09 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating BUY (6-m value 262.56); NOT CLEARED. Entry 219.32, stop 207.2 (2×ATR), target 255.68 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deckers Outdoor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating BUY (6-m value 103.0); NOT CLEARED. Entry 88.1, stop 82.28 (2×ATR), target 105.56 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wabtec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 248.07); CLEARED. Entry 270.6, stop 285.66 (2×ATR), target 225.42 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 29.75); CLEARED. Entry 32.69, stop 34.87 (2×ATR), target 26.15 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arista Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 144.61); CLEARED — results within 14 days. Entry 167.9, stop 185.06 (2×ATR), target 116.42 (3R). Results 2026-11-03 — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dell Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 404.7); CLEARED. Entry 438.62, stop 500.56 (2×ATR), target 252.8 (3R).  — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Micro Devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 402.73); CLEARED — results within 14 days. Entry 501.59, stop 556.31 (2×ATR), target 337.43 (3R). Results 2026-11-03; house limit: max 4 shorts — LRC Watchlist Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fastenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 38.37); CLEARED. Entry 47.21, stop 49.87 (2×ATR), target 39.23 (3R). house limit: max 4 shorts — LRC Watchlist Agent</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weekly Review — swing (every weekend)</t>
   </si>
   <si>
@@ -788,6 +845,9 @@
     <t xml:space="preserve">Finviz is blocked for our tools, so the Swing Long / Swing Short presets were applied manually on stockanalysis.com data (13 Oct closes). LRC RULE: only BUY/SELL-rated names with technical clearance are tradeable. LONGS: only NVDA qualifies; INTU and DECK are BUY-rated but in downtrends (watch only). 2 long slots unfilled — the momentum names the long preset finds (DELL, HPE, KEYS, APH, AMD) all rate SELL on valuation. SHORTS: NKE, ANET, AMD, DELL, FAST (max 4 open; FAST only after its 14 Oct results). Event risk inside 14 days: WAB 21 Oct, DECK 22 Oct, META 21 Oct, APH/GOOGL 28 Oct. S&amp;P 500 above its 200-day; JSE All Share below (−7.4% in 6 months). Lesson: an un-entered trigger cost us the PCTY move (+9%) — set conditional orders when a setup is approved. — P. Nkuna</t>
   </si>
   <si>
+    <t xml:space="preserve">Built by the LRC Watchlist Agent 2026-10-24T06:26+02:00: 3 long / 6 short candidates under house rules. Analyst to review before any trade.</t>
+  </si>
+  <si>
     <t xml:space="preserve">How to pick long-term investments (hold 5 to 10+ years) — every month</t>
   </si>
   <si>
@@ -1689,9 +1749,6 @@
   </si>
   <si>
     <t xml:space="preserve">Financials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONG: Trend continuation</t>
   </si>
   <si>
     <t xml:space="preserve">Open position</t>
@@ -2540,13 +2597,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865800</xdr:colOff>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2556,11 +2613,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2582,13 +2640,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>513360</xdr:colOff>
+      <xdr:colOff>420840</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2598,11 +2656,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2624,13 +2683,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865800</xdr:colOff>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2640,11 +2699,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2665,14 +2725,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>90360</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2682,11 +2742,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2707,14 +2768,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19800</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2724,11 +2785,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2750,13 +2812,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865800</xdr:colOff>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="6" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2766,11 +2828,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2791,14 +2854,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>90360</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="7" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2808,11 +2871,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2833,14 +2897,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19800</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="8" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2850,11 +2914,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2876,13 +2941,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865800</xdr:colOff>
+      <xdr:colOff>865440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570600</xdr:rowOff>
+      <xdr:rowOff>570240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="9" name="Image 1" descr="Picture"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2892,11 +2957,12 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865800" cy="570600"/>
+          <a:ext cx="865440" cy="570240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2915,34 +2981,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -3089,7 +3155,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="22"/>
@@ -3325,40 +3391,40 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="1" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="56" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="57" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>144</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="H3" s="57" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3366,7 +3432,7 @@
         <v>179</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>192</v>
@@ -3375,13 +3441,13 @@
         <v>183</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="H4" s="58" t="s">
         <v>182</v>
@@ -3389,7 +3455,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="B5" s="58" t="s">
         <v>184</v>
@@ -3404,38 +3470,38 @@
         <v>192</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="58" t="s">
-        <v>552</v>
+        <v>225</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="58" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>41</v>
@@ -3452,10 +3518,10 @@
         <v>185</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="H8" s="58" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3463,7 +3529,7 @@
         <v>191</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="H9" s="58" t="s">
         <v>189</v>
@@ -3471,10 +3537,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="58" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="H10" s="58" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3482,15 +3548,15 @@
         <v>211</v>
       </c>
       <c r="H11" s="58" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="58" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3498,12 +3564,12 @@
         <v>213</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="58" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -3524,7 +3590,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
@@ -3601,7 +3667,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="8" t="n">
         <f aca="false">IF('Swing Watchlist'!$C$4="","",'Swing Watchlist'!$C$4)</f>
-        <v>46312</v>
+        <v>46318</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -3626,7 +3692,7 @@
       <c r="C6" s="7"/>
       <c r="D6" s="10" t="n">
         <f aca="false">'Swing Watchlist'!U4</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -3676,7 +3742,7 @@
       <c r="C8" s="7"/>
       <c r="D8" s="11" t="str">
         <f aca="false">'Swing Watchlist'!U5&amp;"  ·  "&amp;'Swing Watchlist'!U6</f>
-        <v>8 / 0  ·  3 / 5</v>
+        <v>9 / 0  ·  3 / 6</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -3701,7 +3767,7 @@
       <c r="C9" s="7"/>
       <c r="D9" s="11" t="str">
         <f aca="false">COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"A")&amp;" / "&amp;COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"B")&amp;" / "&amp;COUNTIFS('Swing Watchlist'!$A$11:$A$210,'Swing Watchlist'!$C$4,'Swing Watchlist'!$AK$11:$AK$210,"C")</f>
-        <v>2 / 0 / 6</v>
+        <v>0 / 6 / 3</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -3857,23 +3923,23 @@
       </c>
       <c r="B16" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>NVDA</v>
+        <v>NKE</v>
       </c>
       <c r="C16" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
-        <v>Long</v>
+        <v>Short</v>
       </c>
       <c r="D16" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="F16" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,1),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Run Technical Review — LONG entry</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>1</v>
@@ -3906,7 +3972,7 @@
       </c>
       <c r="B17" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>NKE</v>
+        <v>WAB</v>
       </c>
       <c r="C17" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -3914,15 +3980,15 @@
       </c>
       <c r="D17" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="F17" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,2),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Run Technical Review — SHORT entry</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>2</v>
@@ -3955,7 +4021,7 @@
       </c>
       <c r="B18" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>ANET</v>
+        <v>DELL</v>
       </c>
       <c r="C18" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -3963,15 +4029,15 @@
       </c>
       <c r="D18" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F18" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Drop or re-check next week</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H18" s="13" t="n">
         <v>3</v>
@@ -4004,7 +4070,7 @@
       </c>
       <c r="B19" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>FAST</v>
+        <v>ANET</v>
       </c>
       <c r="C19" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -4012,15 +4078,15 @@
       </c>
       <c r="D19" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F19" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Drop or re-check next week</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H19" s="13" t="n">
         <v>4</v>
@@ -4053,23 +4119,23 @@
       </c>
       <c r="B20" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>AMD</v>
+        <v>NVDA</v>
       </c>
       <c r="C20" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
-        <v>Short</v>
+        <v>Long</v>
       </c>
       <c r="D20" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F20" s="17" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AU$11:$AU$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>Drop or re-check next week</v>
+        <v>Watch — wait for setup</v>
       </c>
       <c r="H20" s="13" t="n">
         <v>5</v>
@@ -4199,7 +4265,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="16"/>
@@ -4720,7 +4786,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AX210"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
@@ -4871,7 +4937,7 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="19" t="n">
-        <v>46312</v>
+        <v>46318</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>118</v>
@@ -4900,7 +4966,7 @@
       <c r="T4" s="22"/>
       <c r="U4" s="23" t="n">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$C$11:$C$210,"?*")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4" s="24" t="str">
         <f aca="false">IF(U4&gt;=$C$5,"✔ minimum met","⚠ need "&amp;($C$5-U4)&amp;" more")</f>
@@ -4944,7 +5010,7 @@
       <c r="T5" s="22"/>
       <c r="U5" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$B$11:$B$210,"US")&amp;" / "&amp;COUNTIFS($A$11:$A$210,$C$4,$B$11:$B$210,"JSE")</f>
-        <v>8 / 0</v>
+        <v>9 / 0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4982,7 +5048,7 @@
       <c r="T6" s="22"/>
       <c r="U6" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$C$11:$C$210,"?*",$F$11:$F$210,"&lt;&gt;Short")&amp;" / "&amp;COUNTIFS($A$11:$A$210,$C$4,$F$11:$F$210,"Short")</f>
-        <v>3 / 5</v>
+        <v>3 / 6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5020,7 +5086,7 @@
       <c r="T7" s="22"/>
       <c r="U7" s="24" t="str">
         <f aca="false">COUNTIFS($A$11:$A$210,$C$4,$AK$11:$AK$210,"A")&amp;" / "&amp;COUNTIF($AP$11:$AP$210,"Open position")</f>
-        <v>2 / 0</v>
+        <v>0 / 0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5876,9 +5942,9 @@
       <c r="AV14" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="AX14" s="43" t="n">
+      <c r="AX14" s="43" t="str">
         <f aca="false">IF(AND(C14&lt;&gt;"",A14=$C$4,ISNUMBER(AJ14)),AJ14+ROW()/100000,"")</f>
-        <v>17.00014</v>
+        <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6038,9 +6104,9 @@
       <c r="AV15" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="AX15" s="43" t="n">
+      <c r="AX15" s="43" t="str">
         <f aca="false">IF(AND(C15&lt;&gt;"",A15=$C$4,ISNUMBER(AJ15)),AJ15+ROW()/100000,"")</f>
-        <v>8.00015</v>
+        <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6200,9 +6266,9 @@
       <c r="AV16" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="AX16" s="43" t="n">
+      <c r="AX16" s="43" t="str">
         <f aca="false">IF(AND(C16&lt;&gt;"",A16=$C$4,ISNUMBER(AJ16)),AJ16+ROW()/100000,"")</f>
-        <v>8.00016</v>
+        <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6360,9 +6426,9 @@
       <c r="AV17" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="AX17" s="43" t="n">
+      <c r="AX17" s="43" t="str">
         <f aca="false">IF(AND(C17&lt;&gt;"",A17=$C$4,ISNUMBER(AJ17)),AJ17+ROW()/100000,"")</f>
-        <v>16.00017</v>
+        <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6522,9 +6588,9 @@
       <c r="AV18" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="AX18" s="43" t="n">
+      <c r="AX18" s="43" t="str">
         <f aca="false">IF(AND(C18&lt;&gt;"",A18=$C$4,ISNUMBER(AJ18)),AJ18+ROW()/100000,"")</f>
-        <v>9.00018</v>
+        <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6686,9 +6752,9 @@
       <c r="AV19" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="AX19" s="43" t="n">
+      <c r="AX19" s="43" t="str">
         <f aca="false">IF(AND(C19&lt;&gt;"",A19=$C$4,ISNUMBER(AJ19)),AJ19+ROW()/100000,"")</f>
-        <v>8.00019</v>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6850,9 +6916,9 @@
       <c r="AV20" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="AX20" s="43" t="n">
+      <c r="AX20" s="43" t="str">
         <f aca="false">IF(AND(C20&lt;&gt;"",A20=$C$4,ISNUMBER(AJ20)),AJ20+ROW()/100000,"")</f>
-        <v>7.0002</v>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7012,99 +7078,151 @@
       <c r="AV21" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="AX21" s="43" t="n">
+      <c r="AX21" s="43" t="str">
         <f aca="false">IF(AND(C21&lt;&gt;"",A21=$C$4,ISNUMBER(AJ21)),AJ21+ROW()/100000,"")</f>
-        <v>8.00021</v>
+        <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="26"/>
+      <c r="A22" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G22" s="26" t="n">
+        <v>343.39</v>
+      </c>
       <c r="H22" s="26"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="37" t="str">
+      <c r="I22" s="36" t="n">
+        <v>3794424</v>
+      </c>
+      <c r="J22" s="37" t="n">
         <f aca="false">IF(OR(G22="",I22=""),"",G22*I22/1000000)</f>
-        <v/>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="38"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="26"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="26"/>
-      <c r="Z22" s="26"/>
-      <c r="AA22" s="26"/>
-      <c r="AB22" s="16" t="str">
+        <v>1302.96725736</v>
+      </c>
+      <c r="K22" s="21" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="L22" s="21" t="n">
+        <v>0.0694</v>
+      </c>
+      <c r="M22" s="21" t="n">
+        <v>-0.0662</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="O22" s="21" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="P22" s="21" t="n">
+        <v>-0.1327</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>-0.5017</v>
+      </c>
+      <c r="R22" s="21" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="S22" s="38" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T22" s="21" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="U22" s="21" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="V22" s="19" t="n">
+        <v>46345</v>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="X22" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y22" s="26" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="Z22" s="26" t="n">
+        <v>332.97</v>
+      </c>
+      <c r="AA22" s="26" t="n">
+        <v>436.09</v>
+      </c>
+      <c r="AB22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",(AND(M22&lt;&gt;"",N(M22)&lt;0))+(AND(L22&lt;&gt;"",N(L22)&lt;0))+(AND(K22&lt;&gt;"",N(K22)&lt;0))+AND(L22&lt;&gt;"",M22&lt;&gt;"",N(M22)&lt;N(L22)),(N(M22)&gt;0)+(N(L22)&gt;0)+(N(K22)&gt;0)+AND(L22&lt;&gt;"",M22&lt;&gt;"",N(M22)&gt;N(L22))))</f>
-        <v/>
-      </c>
-      <c r="AC22" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",IF(N22="",0,IF(AND(N22&gt;=30,N22&lt;=50),2,IF(OR(AND(N22&gt;=25,N22&lt;30),AND(N22&gt;50,N22&lt;=60)),1,0)))+IF(P22="",0,IF(AND(IF(B22="JSE",$L$5,$L$4)&lt;&gt;"",P22&lt;IF(B22="JSE",$L$5,$L$4)),2,IF(P22&lt;0,1,0))),IF(N22="",0,IF(AND(N22&gt;=50,N22&lt;=70),2,IF(OR(AND(N22&gt;=40,N22&lt;50),AND(N22&gt;70,N22&lt;=75)),1,0)))+IF(P22="",0,IF(AND(IF(B22="JSE",$L$5,$L$4)&lt;&gt;"",P22&gt;IF(B22="JSE",$L$5,$L$4)),2,IF(P22&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD22" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AD22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",IF(R22="",0,IF(R22&lt;=0.1,2,IF(R22&lt;=0.25,1,0))),IF(Q22="",0,IF(Q22&gt;=-0.1,2,IF(Q22&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE22" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(J22="",0,IF(J22&gt;=IF(B22="JSE",$L$7,$L$6),2,IF(J22&gt;=IF(B22="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF22" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",AND(T22&lt;&gt;"",N(T22)&lt;0),N(T22)&gt;0)+(N(S22)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG22" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(AL22="",0,IF(AL22&gt;=3,4,IF(AL22&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH22" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(AND(ISNUMBER(V22),ISNUMBER(A22),V22&gt;=A22,V22-A22&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI22" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(AND(F22="Short",N(U22)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="23" t="n">
         <f aca="false">IF(C22="","",SUM(AB22:AI22))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK22" s="24" t="str">
         <f aca="false">IF(C22="","",IF(AJ22&gt;=14,"A",IF(AJ22&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL22" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL22" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y22="",Z22="",AA22=""),"",IF(F22="Short",IF(Z22&lt;=Y22,"",(Y22-AA22)/(Z22-Y22)),IF(Y22&lt;=Z22,"",(AA22-Y22)/(Y22-Z22)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM22" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="37" t="n">
         <f aca="false">IF(OR(Y22="",Z22="",N(Y22)=N(Z22)),"",IF(OR(AND(F22="Short",Z22&lt;Y22),AND(NOT(F22="Short"),Z22&gt;Y22)),"stop on wrong side",ABS(Y22-Z22)))</f>
-        <v/>
-      </c>
-      <c r="AN22" s="40" t="str">
+        <v>25.78</v>
+      </c>
+      <c r="AN22" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM22)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM22,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO22" s="37" t="str">
+        <v>0.01</v>
+      </c>
+      <c r="AO22" s="37" t="n">
         <f aca="false">IFERROR(IF(AN22="","",AN22*Y22),"")</f>
-        <v/>
-      </c>
-      <c r="AP22" s="35"/>
+        <v>3.5875</v>
+      </c>
+      <c r="AP22" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ22" s="19"/>
       <c r="AR22" s="26"/>
       <c r="AS22" s="41" t="str">
@@ -7117,102 +7235,154 @@
       </c>
       <c r="AU22" s="14" t="str">
         <f aca="false">IF(C22="","",IF(AP22="Open position",IF(IF(F22="Short",AND(ISNUMBER(AR22),ISNUMBER(Z22),AR22&gt;=Z22),AND(ISNUMBER(AR22),ISNUMBER(Z22),AR22&lt;=Z22)),IF(F22="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F22="Short",AND(ISNUMBER(AR22),ISNUMBER(AA22),AR22&lt;=AA22),AND(ISNUMBER(AR22),ISNUMBER(AA22),AR22&gt;=AA22)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT22),AT22&gt;182),IF(F22="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT22),AT22&gt;42,ISNUMBER(AS22),AS22&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F22="Short",AND(L22&lt;&gt;"",N(L22)&gt;0),AND(L22&lt;&gt;"",N(L22)&lt;0)),IF(F22="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP22="Closed",AP22="Dropped"),"Closed",IF(AK22="A",IF(F22="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK22="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV22" s="35"/>
-      <c r="AX22" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV22" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="AX22" s="43" t="n">
         <f aca="false">IF(AND(C22&lt;&gt;"",A22=$C$4,ISNUMBER(AJ22)),AJ22+ROW()/100000,"")</f>
-        <v/>
+        <v>10.00022</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="26"/>
+      <c r="A23" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F23" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="26" t="n">
+        <v>210.96</v>
+      </c>
       <c r="H23" s="26"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="37" t="str">
+      <c r="I23" s="36" t="n">
+        <v>116520944</v>
+      </c>
+      <c r="J23" s="37" t="n">
         <f aca="false">IF(OR(G23="",I23=""),"",G23*I23/1000000)</f>
-        <v/>
-      </c>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="38"/>
+        <v>24581.25834624</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <v>-0.0646</v>
+      </c>
+      <c r="L23" s="21" t="n">
+        <v>-0.0518</v>
+      </c>
+      <c r="M23" s="21" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="N23" s="25" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="O23" s="21" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="P23" s="21" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="Q23" s="21" t="n">
+        <v>-0.1332</v>
+      </c>
+      <c r="R23" s="21" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="S23" s="38" t="n">
+        <v>0.69</v>
+      </c>
       <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="26"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="26"/>
-      <c r="Z23" s="26"/>
-      <c r="AA23" s="26"/>
-      <c r="AB23" s="16" t="str">
+      <c r="U23" s="21" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="V23" s="19" t="n">
+        <v>46344</v>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="X23" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y23" s="26" t="n">
+        <v>219.32</v>
+      </c>
+      <c r="Z23" s="26" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="AA23" s="26" t="n">
+        <v>255.68</v>
+      </c>
+      <c r="AB23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",(AND(M23&lt;&gt;"",N(M23)&lt;0))+(AND(L23&lt;&gt;"",N(L23)&lt;0))+(AND(K23&lt;&gt;"",N(K23)&lt;0))+AND(L23&lt;&gt;"",M23&lt;&gt;"",N(M23)&lt;N(L23)),(N(M23)&gt;0)+(N(L23)&gt;0)+(N(K23)&gt;0)+AND(L23&lt;&gt;"",M23&lt;&gt;"",N(M23)&gt;N(L23))))</f>
-        <v/>
-      </c>
-      <c r="AC23" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",IF(N23="",0,IF(AND(N23&gt;=30,N23&lt;=50),2,IF(OR(AND(N23&gt;=25,N23&lt;30),AND(N23&gt;50,N23&lt;=60)),1,0)))+IF(P23="",0,IF(AND(IF(B23="JSE",$L$5,$L$4)&lt;&gt;"",P23&lt;IF(B23="JSE",$L$5,$L$4)),2,IF(P23&lt;0,1,0))),IF(N23="",0,IF(AND(N23&gt;=50,N23&lt;=70),2,IF(OR(AND(N23&gt;=40,N23&lt;50),AND(N23&gt;70,N23&lt;=75)),1,0)))+IF(P23="",0,IF(AND(IF(B23="JSE",$L$5,$L$4)&lt;&gt;"",P23&gt;IF(B23="JSE",$L$5,$L$4)),2,IF(P23&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD23" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",IF(R23="",0,IF(R23&lt;=0.1,2,IF(R23&lt;=0.25,1,0))),IF(Q23="",0,IF(Q23&gt;=-0.1,2,IF(Q23&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE23" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AE23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(J23="",0,IF(J23&gt;=IF(B23="JSE",$L$7,$L$6),2,IF(J23&gt;=IF(B23="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF23" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",AND(T23&lt;&gt;"",N(T23)&lt;0),N(T23)&gt;0)+(N(S23)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG23" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(AL23="",0,IF(AL23&gt;=3,4,IF(AL23&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH23" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(AND(ISNUMBER(V23),ISNUMBER(A23),V23&gt;=A23,V23-A23&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI23" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(AND(F23="Short",N(U23)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="23" t="n">
         <f aca="false">IF(C23="","",SUM(AB23:AI23))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK23" s="24" t="str">
         <f aca="false">IF(C23="","",IF(AJ23&gt;=14,"A",IF(AJ23&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL23" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL23" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y23="",Z23="",AA23=""),"",IF(F23="Short",IF(Z23&lt;=Y23,"",(Y23-AA23)/(Z23-Y23)),IF(Y23&lt;=Z23,"",(AA23-Y23)/(Y23-Z23)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM23" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="37" t="n">
         <f aca="false">IF(OR(Y23="",Z23="",N(Y23)=N(Z23)),"",IF(OR(AND(F23="Short",Z23&lt;Y23),AND(NOT(F23="Short"),Z23&gt;Y23)),"stop on wrong side",ABS(Y23-Z23)))</f>
-        <v/>
-      </c>
-      <c r="AN23" s="40" t="str">
+        <v>12.12</v>
+      </c>
+      <c r="AN23" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM23)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM23,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO23" s="37" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="AO23" s="37" t="n">
         <f aca="false">IFERROR(IF(AN23="","",AN23*Y23),"")</f>
-        <v/>
-      </c>
-      <c r="AP23" s="35"/>
+        <v>6.5796</v>
+      </c>
+      <c r="AP23" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ23" s="19"/>
       <c r="AR23" s="26"/>
       <c r="AS23" s="41" t="str">
@@ -7225,102 +7395,154 @@
       </c>
       <c r="AU23" s="14" t="str">
         <f aca="false">IF(C23="","",IF(AP23="Open position",IF(IF(F23="Short",AND(ISNUMBER(AR23),ISNUMBER(Z23),AR23&gt;=Z23),AND(ISNUMBER(AR23),ISNUMBER(Z23),AR23&lt;=Z23)),IF(F23="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F23="Short",AND(ISNUMBER(AR23),ISNUMBER(AA23),AR23&lt;=AA23),AND(ISNUMBER(AR23),ISNUMBER(AA23),AR23&gt;=AA23)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT23),AT23&gt;182),IF(F23="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT23),AT23&gt;42,ISNUMBER(AS23),AS23&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F23="Short",AND(L23&lt;&gt;"",N(L23)&gt;0),AND(L23&lt;&gt;"",N(L23)&lt;0)),IF(F23="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP23="Closed",AP23="Dropped"),"Closed",IF(AK23="A",IF(F23="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK23="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV23" s="35"/>
-      <c r="AX23" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV23" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="AX23" s="43" t="n">
         <f aca="false">IF(AND(C23&lt;&gt;"",A23=$C$4,ISNUMBER(AJ23)),AJ23+ROW()/100000,"")</f>
-        <v/>
+        <v>10.00023</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="26"/>
+      <c r="A24" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>81.09</v>
+      </c>
       <c r="H24" s="26"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="37" t="str">
+      <c r="I24" s="36" t="n">
+        <v>3058068</v>
+      </c>
+      <c r="J24" s="37" t="n">
         <f aca="false">IF(OR(G24="",I24=""),"",G24*I24/1000000)</f>
-        <v/>
-      </c>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="38"/>
+        <v>247.97873412</v>
+      </c>
+      <c r="K24" s="21" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="M24" s="21" t="n">
+        <v>-0.1876</v>
+      </c>
+      <c r="N24" s="25" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="O24" s="21" t="n">
+        <v>-0.1703</v>
+      </c>
+      <c r="P24" s="21" t="n">
+        <v>-0.2528</v>
+      </c>
+      <c r="Q24" s="21" t="n">
+        <v>-0.3369</v>
+      </c>
+      <c r="R24" s="21" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="S24" s="38" t="n">
+        <v>3.04</v>
+      </c>
       <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="26"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="26"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="26"/>
-      <c r="AB24" s="16" t="str">
+      <c r="U24" s="21" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="V24" s="19" t="n">
+        <v>46317</v>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X24" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y24" s="26" t="n">
+        <v>88.1</v>
+      </c>
+      <c r="Z24" s="26" t="n">
+        <v>82.28</v>
+      </c>
+      <c r="AA24" s="26" t="n">
+        <v>105.56</v>
+      </c>
+      <c r="AB24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",(AND(M24&lt;&gt;"",N(M24)&lt;0))+(AND(L24&lt;&gt;"",N(L24)&lt;0))+(AND(K24&lt;&gt;"",N(K24)&lt;0))+AND(L24&lt;&gt;"",M24&lt;&gt;"",N(M24)&lt;N(L24)),(N(M24)&gt;0)+(N(L24)&gt;0)+(N(K24)&gt;0)+AND(L24&lt;&gt;"",M24&lt;&gt;"",N(M24)&gt;N(L24))))</f>
-        <v/>
-      </c>
-      <c r="AC24" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",IF(N24="",0,IF(AND(N24&gt;=30,N24&lt;=50),2,IF(OR(AND(N24&gt;=25,N24&lt;30),AND(N24&gt;50,N24&lt;=60)),1,0)))+IF(P24="",0,IF(AND(IF(B24="JSE",$L$5,$L$4)&lt;&gt;"",P24&lt;IF(B24="JSE",$L$5,$L$4)),2,IF(P24&lt;0,1,0))),IF(N24="",0,IF(AND(N24&gt;=50,N24&lt;=70),2,IF(OR(AND(N24&gt;=40,N24&lt;50),AND(N24&gt;70,N24&lt;=75)),1,0)))+IF(P24="",0,IF(AND(IF(B24="JSE",$L$5,$L$4)&lt;&gt;"",P24&gt;IF(B24="JSE",$L$5,$L$4)),2,IF(P24&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD24" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",IF(R24="",0,IF(R24&lt;=0.1,2,IF(R24&lt;=0.25,1,0))),IF(Q24="",0,IF(Q24&gt;=-0.1,2,IF(Q24&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE24" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(J24="",0,IF(J24&gt;=IF(B24="JSE",$L$7,$L$6),2,IF(J24&gt;=IF(B24="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF24" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",AND(T24&lt;&gt;"",N(T24)&lt;0),N(T24)&gt;0)+(N(S24)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG24" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(AL24="",0,IF(AL24&gt;=3,4,IF(AL24&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH24" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(AND(ISNUMBER(V24),ISNUMBER(A24),V24&gt;=A24,V24-A24&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI24" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(AND(F24="Short",N(U24)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ24" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="23" t="n">
         <f aca="false">IF(C24="","",SUM(AB24:AI24))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AK24" s="24" t="str">
         <f aca="false">IF(C24="","",IF(AJ24&gt;=14,"A",IF(AJ24&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL24" s="39" t="str">
+        <v>C</v>
+      </c>
+      <c r="AL24" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y24="",Z24="",AA24=""),"",IF(F24="Short",IF(Z24&lt;=Y24,"",(Y24-AA24)/(Z24-Y24)),IF(Y24&lt;=Z24,"",(AA24-Y24)/(Y24-Z24)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM24" s="37" t="str">
+        <v>3.00000000000001</v>
+      </c>
+      <c r="AM24" s="37" t="n">
         <f aca="false">IF(OR(Y24="",Z24="",N(Y24)=N(Z24)),"",IF(OR(AND(F24="Short",Z24&lt;Y24),AND(NOT(F24="Short"),Z24&gt;Y24)),"stop on wrong side",ABS(Y24-Z24)))</f>
-        <v/>
-      </c>
-      <c r="AN24" s="40" t="str">
+        <v>5.81999999999999</v>
+      </c>
+      <c r="AN24" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM24)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM24,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO24" s="37" t="str">
+        <v>0.07</v>
+      </c>
+      <c r="AO24" s="37" t="n">
         <f aca="false">IFERROR(IF(AN24="","",AN24*Y24),"")</f>
-        <v/>
-      </c>
-      <c r="AP24" s="35"/>
+        <v>6.167</v>
+      </c>
+      <c r="AP24" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ24" s="19"/>
       <c r="AR24" s="26"/>
       <c r="AS24" s="41" t="str">
@@ -7333,102 +7555,154 @@
       </c>
       <c r="AU24" s="14" t="str">
         <f aca="false">IF(C24="","",IF(AP24="Open position",IF(IF(F24="Short",AND(ISNUMBER(AR24),ISNUMBER(Z24),AR24&gt;=Z24),AND(ISNUMBER(AR24),ISNUMBER(Z24),AR24&lt;=Z24)),IF(F24="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F24="Short",AND(ISNUMBER(AR24),ISNUMBER(AA24),AR24&lt;=AA24),AND(ISNUMBER(AR24),ISNUMBER(AA24),AR24&gt;=AA24)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT24),AT24&gt;182),IF(F24="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT24),AT24&gt;42,ISNUMBER(AS24),AS24&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F24="Short",AND(L24&lt;&gt;"",N(L24)&gt;0),AND(L24&lt;&gt;"",N(L24)&lt;0)),IF(F24="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP24="Closed",AP24="Dropped"),"Closed",IF(AK24="A",IF(F24="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK24="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV24" s="35"/>
-      <c r="AX24" s="43" t="str">
+        <v>Drop or re-check next week</v>
+      </c>
+      <c r="AV24" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX24" s="43" t="n">
         <f aca="false">IF(AND(C24&lt;&gt;"",A24=$C$4,ISNUMBER(AJ24)),AJ24+ROW()/100000,"")</f>
-        <v/>
+        <v>8.00024</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="26"/>
+      <c r="A25" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="26" t="n">
+        <v>272.35</v>
+      </c>
       <c r="H25" s="26"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="37" t="str">
+      <c r="I25" s="36" t="n">
+        <v>906852</v>
+      </c>
+      <c r="J25" s="37" t="n">
         <f aca="false">IF(OR(G25="",I25=""),"",G25*I25/1000000)</f>
-        <v/>
-      </c>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="38"/>
+        <v>246.9811422</v>
+      </c>
+      <c r="K25" s="21" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>-0.0513</v>
+      </c>
+      <c r="M25" s="21" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="N25" s="25" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="O25" s="21" t="n">
+        <v>-0.0949</v>
+      </c>
+      <c r="P25" s="21" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="Q25" s="21" t="n">
+        <v>-0.1118</v>
+      </c>
+      <c r="R25" s="21" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="S25" s="38" t="n">
+        <v>1.71</v>
+      </c>
       <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="26"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="26"/>
-      <c r="Z25" s="26"/>
-      <c r="AA25" s="26"/>
-      <c r="AB25" s="16" t="str">
+      <c r="U25" s="21" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="V25" s="19" t="n">
+        <v>46316</v>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="X25" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y25" s="26" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="Z25" s="26" t="n">
+        <v>285.66</v>
+      </c>
+      <c r="AA25" s="26" t="n">
+        <v>225.42</v>
+      </c>
+      <c r="AB25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(F25="Short",(AND(M25&lt;&gt;"",N(M25)&lt;0))+(AND(L25&lt;&gt;"",N(L25)&lt;0))+(AND(K25&lt;&gt;"",N(K25)&lt;0))+AND(L25&lt;&gt;"",M25&lt;&gt;"",N(M25)&lt;N(L25)),(N(M25)&gt;0)+(N(L25)&gt;0)+(N(K25)&gt;0)+AND(L25&lt;&gt;"",M25&lt;&gt;"",N(M25)&gt;N(L25))))</f>
-        <v/>
-      </c>
-      <c r="AC25" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(F25="Short",IF(N25="",0,IF(AND(N25&gt;=30,N25&lt;=50),2,IF(OR(AND(N25&gt;=25,N25&lt;30),AND(N25&gt;50,N25&lt;=60)),1,0)))+IF(P25="",0,IF(AND(IF(B25="JSE",$L$5,$L$4)&lt;&gt;"",P25&lt;IF(B25="JSE",$L$5,$L$4)),2,IF(P25&lt;0,1,0))),IF(N25="",0,IF(AND(N25&gt;=50,N25&lt;=70),2,IF(OR(AND(N25&gt;=40,N25&lt;50),AND(N25&gt;70,N25&lt;=75)),1,0)))+IF(P25="",0,IF(AND(IF(B25="JSE",$L$5,$L$4)&lt;&gt;"",P25&gt;IF(B25="JSE",$L$5,$L$4)),2,IF(P25&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD25" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AD25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(F25="Short",IF(R25="",0,IF(R25&lt;=0.1,2,IF(R25&lt;=0.25,1,0))),IF(Q25="",0,IF(Q25&gt;=-0.1,2,IF(Q25&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE25" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(J25="",0,IF(J25&gt;=IF(B25="JSE",$L$7,$L$6),2,IF(J25&gt;=IF(B25="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF25" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(F25="Short",AND(T25&lt;&gt;"",N(T25)&lt;0),N(T25)&gt;0)+(N(S25)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG25" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(AL25="",0,IF(AL25&gt;=3,4,IF(AL25&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH25" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(AND(ISNUMBER(V25),ISNUMBER(A25),V25&gt;=A25,V25-A25&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI25" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="16" t="n">
         <f aca="false">IF(C25="","",IF(AND(F25="Short",N(U25)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ25" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="23" t="n">
         <f aca="false">IF(C25="","",SUM(AB25:AI25))</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="AK25" s="24" t="str">
         <f aca="false">IF(C25="","",IF(AJ25&gt;=14,"A",IF(AJ25&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL25" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL25" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y25="",Z25="",AA25=""),"",IF(F25="Short",IF(Z25&lt;=Y25,"",(Y25-AA25)/(Z25-Y25)),IF(Y25&lt;=Z25,"",(AA25-Y25)/(Y25-Z25)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM25" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="37" t="n">
         <f aca="false">IF(OR(Y25="",Z25="",N(Y25)=N(Z25)),"",IF(OR(AND(F25="Short",Z25&lt;Y25),AND(NOT(F25="Short"),Z25&gt;Y25)),"stop on wrong side",ABS(Y25-Z25)))</f>
-        <v/>
-      </c>
-      <c r="AN25" s="40" t="str">
+        <v>15.06</v>
+      </c>
+      <c r="AN25" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM25)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM25,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO25" s="37" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="AO25" s="37" t="n">
         <f aca="false">IFERROR(IF(AN25="","",AN25*Y25),"")</f>
-        <v/>
-      </c>
-      <c r="AP25" s="35"/>
+        <v>8.118</v>
+      </c>
+      <c r="AP25" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ25" s="19"/>
       <c r="AR25" s="26"/>
       <c r="AS25" s="41" t="str">
@@ -7441,102 +7715,154 @@
       </c>
       <c r="AU25" s="14" t="str">
         <f aca="false">IF(C25="","",IF(AP25="Open position",IF(IF(F25="Short",AND(ISNUMBER(AR25),ISNUMBER(Z25),AR25&gt;=Z25),AND(ISNUMBER(AR25),ISNUMBER(Z25),AR25&lt;=Z25)),IF(F25="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F25="Short",AND(ISNUMBER(AR25),ISNUMBER(AA25),AR25&lt;=AA25),AND(ISNUMBER(AR25),ISNUMBER(AA25),AR25&gt;=AA25)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT25),AT25&gt;182),IF(F25="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT25),AT25&gt;42,ISNUMBER(AS25),AS25&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F25="Short",AND(L25&lt;&gt;"",N(L25)&gt;0),AND(L25&lt;&gt;"",N(L25)&lt;0)),IF(F25="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP25="Closed",AP25="Dropped"),"Closed",IF(AK25="A",IF(F25="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK25="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV25" s="35"/>
-      <c r="AX25" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV25" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX25" s="43" t="n">
         <f aca="false">IF(AND(C25&lt;&gt;"",A25=$C$4,ISNUMBER(AJ25)),AJ25+ROW()/100000,"")</f>
-        <v/>
+        <v>13.00025</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="26"/>
+      <c r="A26" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>37.3</v>
+      </c>
       <c r="H26" s="26"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="37" t="str">
+      <c r="I26" s="36" t="n">
+        <v>33320533</v>
+      </c>
+      <c r="J26" s="37" t="n">
         <f aca="false">IF(OR(G26="",I26=""),"",G26*I26/1000000)</f>
-        <v/>
-      </c>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="38"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
+        <v>1242.8558809</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="L26" s="21" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="M26" s="21" t="n">
+        <v>-0.202</v>
+      </c>
+      <c r="N26" s="25" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="O26" s="21" t="n">
+        <v>-0.1149</v>
+      </c>
+      <c r="P26" s="21" t="n">
+        <v>-0.1654</v>
+      </c>
+      <c r="Q26" s="21" t="n">
+        <v>-0.4705</v>
+      </c>
+      <c r="R26" s="21" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="S26" s="38" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T26" s="21" t="n">
+        <v>-0.1642</v>
+      </c>
+      <c r="U26" s="21" t="n">
+        <v>0.0842</v>
+      </c>
       <c r="V26" s="19"/>
-      <c r="W26" s="26"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="26"/>
-      <c r="Z26" s="26"/>
-      <c r="AA26" s="26"/>
-      <c r="AB26" s="16" t="str">
+      <c r="W26" s="26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X26" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y26" s="26" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="Z26" s="26" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="AA26" s="26" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AB26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(F26="Short",(AND(M26&lt;&gt;"",N(M26)&lt;0))+(AND(L26&lt;&gt;"",N(L26)&lt;0))+(AND(K26&lt;&gt;"",N(K26)&lt;0))+AND(L26&lt;&gt;"",M26&lt;&gt;"",N(M26)&lt;N(L26)),(N(M26)&gt;0)+(N(L26)&gt;0)+(N(K26)&gt;0)+AND(L26&lt;&gt;"",M26&lt;&gt;"",N(M26)&gt;N(L26))))</f>
-        <v/>
-      </c>
-      <c r="AC26" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(F26="Short",IF(N26="",0,IF(AND(N26&gt;=30,N26&lt;=50),2,IF(OR(AND(N26&gt;=25,N26&lt;30),AND(N26&gt;50,N26&lt;=60)),1,0)))+IF(P26="",0,IF(AND(IF(B26="JSE",$L$5,$L$4)&lt;&gt;"",P26&lt;IF(B26="JSE",$L$5,$L$4)),2,IF(P26&lt;0,1,0))),IF(N26="",0,IF(AND(N26&gt;=50,N26&lt;=70),2,IF(OR(AND(N26&gt;=40,N26&lt;50),AND(N26&gt;70,N26&lt;=75)),1,0)))+IF(P26="",0,IF(AND(IF(B26="JSE",$L$5,$L$4)&lt;&gt;"",P26&gt;IF(B26="JSE",$L$5,$L$4)),2,IF(P26&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD26" s="16" t="str">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(F26="Short",IF(R26="",0,IF(R26&lt;=0.1,2,IF(R26&lt;=0.25,1,0))),IF(Q26="",0,IF(Q26&gt;=-0.1,2,IF(Q26&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE26" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(J26="",0,IF(J26&gt;=IF(B26="JSE",$L$7,$L$6),2,IF(J26&gt;=IF(B26="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF26" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(F26="Short",AND(T26&lt;&gt;"",N(T26)&lt;0),N(T26)&gt;0)+(N(S26)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG26" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(AL26="",0,IF(AL26&gt;=3,4,IF(AL26&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH26" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(AND(ISNUMBER(V26),ISNUMBER(A26),V26&gt;=A26,V26-A26&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI26" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="16" t="n">
         <f aca="false">IF(C26="","",IF(AND(F26="Short",N(U26)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ26" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="23" t="n">
         <f aca="false">IF(C26="","",SUM(AB26:AI26))</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="AK26" s="24" t="str">
         <f aca="false">IF(C26="","",IF(AJ26&gt;=14,"A",IF(AJ26&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL26" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL26" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y26="",Z26="",AA26=""),"",IF(F26="Short",IF(Z26&lt;=Y26,"",(Y26-AA26)/(Z26-Y26)),IF(Y26&lt;=Z26,"",(AA26-Y26)/(Y26-Z26)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM26" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="37" t="n">
         <f aca="false">IF(OR(Y26="",Z26="",N(Y26)=N(Z26)),"",IF(OR(AND(F26="Short",Z26&lt;Y26),AND(NOT(F26="Short"),Z26&gt;Y26)),"stop on wrong side",ABS(Y26-Z26)))</f>
-        <v/>
-      </c>
-      <c r="AN26" s="40" t="str">
+        <v>2.18</v>
+      </c>
+      <c r="AN26" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM26)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM26,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO26" s="37" t="str">
+        <v>0.21</v>
+      </c>
+      <c r="AO26" s="37" t="n">
         <f aca="false">IFERROR(IF(AN26="","",AN26*Y26),"")</f>
-        <v/>
-      </c>
-      <c r="AP26" s="35"/>
+        <v>6.8649</v>
+      </c>
+      <c r="AP26" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ26" s="19"/>
       <c r="AR26" s="26"/>
       <c r="AS26" s="41" t="str">
@@ -7549,102 +7875,154 @@
       </c>
       <c r="AU26" s="14" t="str">
         <f aca="false">IF(C26="","",IF(AP26="Open position",IF(IF(F26="Short",AND(ISNUMBER(AR26),ISNUMBER(Z26),AR26&gt;=Z26),AND(ISNUMBER(AR26),ISNUMBER(Z26),AR26&lt;=Z26)),IF(F26="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F26="Short",AND(ISNUMBER(AR26),ISNUMBER(AA26),AR26&lt;=AA26),AND(ISNUMBER(AR26),ISNUMBER(AA26),AR26&gt;=AA26)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT26),AT26&gt;182),IF(F26="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT26),AT26&gt;42,ISNUMBER(AS26),AS26&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F26="Short",AND(L26&lt;&gt;"",N(L26)&gt;0),AND(L26&lt;&gt;"",N(L26)&lt;0)),IF(F26="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP26="Closed",AP26="Dropped"),"Closed",IF(AK26="A",IF(F26="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK26="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV26" s="35"/>
-      <c r="AX26" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV26" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="AX26" s="43" t="n">
         <f aca="false">IF(AND(C26&lt;&gt;"",A26=$C$4,ISNUMBER(AJ26)),AJ26+ROW()/100000,"")</f>
-        <v/>
+        <v>13.00026</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="26"/>
+      <c r="A27" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>172.37</v>
+      </c>
       <c r="H27" s="26"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="37" t="str">
+      <c r="I27" s="36" t="n">
+        <v>6149214</v>
+      </c>
+      <c r="J27" s="37" t="n">
         <f aca="false">IF(OR(G27="",I27=""),"",G27*I27/1000000)</f>
-        <v/>
-      </c>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="38"/>
+        <v>1059.94001718</v>
+      </c>
+      <c r="K27" s="21" t="n">
+        <v>-0.1282</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>-0.1224</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="N27" s="25" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="O27" s="21" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>-0.0257</v>
+      </c>
+      <c r="Q27" s="21" t="n">
+        <v>-0.2072</v>
+      </c>
+      <c r="R27" s="21" t="n">
+        <v>0.5052</v>
+      </c>
+      <c r="S27" s="38" t="n">
+        <v>0.81</v>
+      </c>
       <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="16" t="str">
+      <c r="U27" s="21" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="V27" s="19" t="n">
+        <v>46329</v>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="X27" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y27" s="26" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="Z27" s="26" t="n">
+        <v>185.06</v>
+      </c>
+      <c r="AA27" s="26" t="n">
+        <v>116.42</v>
+      </c>
+      <c r="AB27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(F27="Short",(AND(M27&lt;&gt;"",N(M27)&lt;0))+(AND(L27&lt;&gt;"",N(L27)&lt;0))+(AND(K27&lt;&gt;"",N(K27)&lt;0))+AND(L27&lt;&gt;"",M27&lt;&gt;"",N(M27)&lt;N(L27)),(N(M27)&gt;0)+(N(L27)&gt;0)+(N(K27)&gt;0)+AND(L27&lt;&gt;"",M27&lt;&gt;"",N(M27)&gt;N(L27))))</f>
-        <v/>
-      </c>
-      <c r="AC27" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(F27="Short",IF(N27="",0,IF(AND(N27&gt;=30,N27&lt;=50),2,IF(OR(AND(N27&gt;=25,N27&lt;30),AND(N27&gt;50,N27&lt;=60)),1,0)))+IF(P27="",0,IF(AND(IF(B27="JSE",$L$5,$L$4)&lt;&gt;"",P27&lt;IF(B27="JSE",$L$5,$L$4)),2,IF(P27&lt;0,1,0))),IF(N27="",0,IF(AND(N27&gt;=50,N27&lt;=70),2,IF(OR(AND(N27&gt;=40,N27&lt;50),AND(N27&gt;70,N27&lt;=75)),1,0)))+IF(P27="",0,IF(AND(IF(B27="JSE",$L$5,$L$4)&lt;&gt;"",P27&gt;IF(B27="JSE",$L$5,$L$4)),2,IF(P27&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD27" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AD27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(F27="Short",IF(R27="",0,IF(R27&lt;=0.1,2,IF(R27&lt;=0.25,1,0))),IF(Q27="",0,IF(Q27&gt;=-0.1,2,IF(Q27&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE27" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(J27="",0,IF(J27&gt;=IF(B27="JSE",$L$7,$L$6),2,IF(J27&gt;=IF(B27="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF27" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(F27="Short",AND(T27&lt;&gt;"",N(T27)&lt;0),N(T27)&gt;0)+(N(S27)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG27" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(AL27="",0,IF(AL27&gt;=3,4,IF(AL27&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH27" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(AND(ISNUMBER(V27),ISNUMBER(A27),V27&gt;=A27,V27-A27&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI27" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI27" s="16" t="n">
         <f aca="false">IF(C27="","",IF(AND(F27="Short",N(U27)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ27" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="23" t="n">
         <f aca="false">IF(C27="","",SUM(AB27:AI27))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK27" s="24" t="str">
         <f aca="false">IF(C27="","",IF(AJ27&gt;=14,"A",IF(AJ27&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL27" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL27" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y27="",Z27="",AA27=""),"",IF(F27="Short",IF(Z27&lt;=Y27,"",(Y27-AA27)/(Z27-Y27)),IF(Y27&lt;=Z27,"",(AA27-Y27)/(Y27-Z27)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM27" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="37" t="n">
         <f aca="false">IF(OR(Y27="",Z27="",N(Y27)=N(Z27)),"",IF(OR(AND(F27="Short",Z27&lt;Y27),AND(NOT(F27="Short"),Z27&gt;Y27)),"stop on wrong side",ABS(Y27-Z27)))</f>
-        <v/>
-      </c>
-      <c r="AN27" s="40" t="str">
+        <v>17.16</v>
+      </c>
+      <c r="AN27" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM27)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM27,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO27" s="37" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="AO27" s="37" t="n">
         <f aca="false">IFERROR(IF(AN27="","",AN27*Y27),"")</f>
-        <v/>
-      </c>
-      <c r="AP27" s="35"/>
+        <v>3.358</v>
+      </c>
+      <c r="AP27" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ27" s="19"/>
       <c r="AR27" s="26"/>
       <c r="AS27" s="41" t="str">
@@ -7657,102 +8035,156 @@
       </c>
       <c r="AU27" s="14" t="str">
         <f aca="false">IF(C27="","",IF(AP27="Open position",IF(IF(F27="Short",AND(ISNUMBER(AR27),ISNUMBER(Z27),AR27&gt;=Z27),AND(ISNUMBER(AR27),ISNUMBER(Z27),AR27&lt;=Z27)),IF(F27="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F27="Short",AND(ISNUMBER(AR27),ISNUMBER(AA27),AR27&lt;=AA27),AND(ISNUMBER(AR27),ISNUMBER(AA27),AR27&gt;=AA27)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT27),AT27&gt;182),IF(F27="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT27),AT27&gt;42,ISNUMBER(AS27),AS27&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F27="Short",AND(L27&lt;&gt;"",N(L27)&gt;0),AND(L27&lt;&gt;"",N(L27)&lt;0)),IF(F27="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP27="Closed",AP27="Dropped"),"Closed",IF(AK27="A",IF(F27="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK27="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV27" s="35"/>
-      <c r="AX27" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV27" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="AX27" s="43" t="n">
         <f aca="false">IF(AND(C27&lt;&gt;"",A27=$C$4,ISNUMBER(AJ27)),AJ27+ROW()/100000,"")</f>
-        <v/>
+        <v>10.00027</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="26"/>
+      <c r="A28" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>456.44</v>
+      </c>
       <c r="H28" s="26"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="37" t="str">
+      <c r="I28" s="36" t="n">
+        <v>7702417</v>
+      </c>
+      <c r="J28" s="37" t="n">
         <f aca="false">IF(OR(G28="",I28=""),"",G28*I28/1000000)</f>
-        <v/>
-      </c>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="38"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="26"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="16" t="str">
+        <v>3515.69121548</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <v>-0.1294</v>
+      </c>
+      <c r="L28" s="21" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M28" s="21" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="N28" s="25" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="O28" s="21" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>1.1123</v>
+      </c>
+      <c r="Q28" s="21" t="n">
+        <v>-0.2335</v>
+      </c>
+      <c r="R28" s="21" t="n">
+        <v>3.1412</v>
+      </c>
+      <c r="S28" s="38" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="T28" s="21" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="U28" s="21" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="V28" s="19" t="n">
+        <v>46350</v>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="X28" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y28" s="26" t="n">
+        <v>438.62</v>
+      </c>
+      <c r="Z28" s="26" t="n">
+        <v>500.56</v>
+      </c>
+      <c r="AA28" s="26" t="n">
+        <v>252.8</v>
+      </c>
+      <c r="AB28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(F28="Short",(AND(M28&lt;&gt;"",N(M28)&lt;0))+(AND(L28&lt;&gt;"",N(L28)&lt;0))+(AND(K28&lt;&gt;"",N(K28)&lt;0))+AND(L28&lt;&gt;"",M28&lt;&gt;"",N(M28)&lt;N(L28)),(N(M28)&gt;0)+(N(L28)&gt;0)+(N(K28)&gt;0)+AND(L28&lt;&gt;"",M28&lt;&gt;"",N(M28)&gt;N(L28))))</f>
-        <v/>
-      </c>
-      <c r="AC28" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(F28="Short",IF(N28="",0,IF(AND(N28&gt;=30,N28&lt;=50),2,IF(OR(AND(N28&gt;=25,N28&lt;30),AND(N28&gt;50,N28&lt;=60)),1,0)))+IF(P28="",0,IF(AND(IF(B28="JSE",$L$5,$L$4)&lt;&gt;"",P28&lt;IF(B28="JSE",$L$5,$L$4)),2,IF(P28&lt;0,1,0))),IF(N28="",0,IF(AND(N28&gt;=50,N28&lt;=70),2,IF(OR(AND(N28&gt;=40,N28&lt;50),AND(N28&gt;70,N28&lt;=75)),1,0)))+IF(P28="",0,IF(AND(IF(B28="JSE",$L$5,$L$4)&lt;&gt;"",P28&gt;IF(B28="JSE",$L$5,$L$4)),2,IF(P28&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD28" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AD28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(F28="Short",IF(R28="",0,IF(R28&lt;=0.1,2,IF(R28&lt;=0.25,1,0))),IF(Q28="",0,IF(Q28&gt;=-0.1,2,IF(Q28&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE28" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(J28="",0,IF(J28&gt;=IF(B28="JSE",$L$7,$L$6),2,IF(J28&gt;=IF(B28="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF28" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(F28="Short",AND(T28&lt;&gt;"",N(T28)&lt;0),N(T28)&gt;0)+(N(S28)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG28" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(AL28="",0,IF(AL28&gt;=3,4,IF(AL28&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH28" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(AND(ISNUMBER(V28),ISNUMBER(A28),V28&gt;=A28,V28-A28&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI28" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="16" t="n">
         <f aca="false">IF(C28="","",IF(AND(F28="Short",N(U28)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ28" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="23" t="n">
         <f aca="false">IF(C28="","",SUM(AB28:AI28))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK28" s="24" t="str">
         <f aca="false">IF(C28="","",IF(AJ28&gt;=14,"A",IF(AJ28&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL28" s="39" t="str">
+        <v>B</v>
+      </c>
+      <c r="AL28" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y28="",Z28="",AA28=""),"",IF(F28="Short",IF(Z28&lt;=Y28,"",(Y28-AA28)/(Z28-Y28)),IF(Y28&lt;=Z28,"",(AA28-Y28)/(Y28-Z28)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM28" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="37" t="n">
         <f aca="false">IF(OR(Y28="",Z28="",N(Y28)=N(Z28)),"",IF(OR(AND(F28="Short",Z28&lt;Y28),AND(NOT(F28="Short"),Z28&gt;Y28)),"stop on wrong side",ABS(Y28-Z28)))</f>
-        <v/>
-      </c>
-      <c r="AN28" s="40" t="str">
+        <v>61.94</v>
+      </c>
+      <c r="AN28" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM28)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM28,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO28" s="37" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="37" t="n">
         <f aca="false">IFERROR(IF(AN28="","",AN28*Y28),"")</f>
-        <v/>
-      </c>
-      <c r="AP28" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP28" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ28" s="19"/>
       <c r="AR28" s="26"/>
       <c r="AS28" s="41" t="str">
@@ -7765,102 +8197,156 @@
       </c>
       <c r="AU28" s="14" t="str">
         <f aca="false">IF(C28="","",IF(AP28="Open position",IF(IF(F28="Short",AND(ISNUMBER(AR28),ISNUMBER(Z28),AR28&gt;=Z28),AND(ISNUMBER(AR28),ISNUMBER(Z28),AR28&lt;=Z28)),IF(F28="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F28="Short",AND(ISNUMBER(AR28),ISNUMBER(AA28),AR28&lt;=AA28),AND(ISNUMBER(AR28),ISNUMBER(AA28),AR28&gt;=AA28)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT28),AT28&gt;182),IF(F28="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT28),AT28&gt;42,ISNUMBER(AS28),AS28&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F28="Short",AND(L28&lt;&gt;"",N(L28)&gt;0),AND(L28&lt;&gt;"",N(L28)&lt;0)),IF(F28="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP28="Closed",AP28="Dropped"),"Closed",IF(AK28="A",IF(F28="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK28="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV28" s="35"/>
-      <c r="AX28" s="43" t="str">
+        <v>Watch — wait for setup</v>
+      </c>
+      <c r="AV28" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="AX28" s="43" t="n">
         <f aca="false">IF(AND(C28&lt;&gt;"",A28=$C$4,ISNUMBER(AJ28)),AJ28+ROW()/100000,"")</f>
-        <v/>
+        <v>10.00028</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="26"/>
+      <c r="A29" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="26" t="n">
+        <v>516.79</v>
+      </c>
       <c r="H29" s="26"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="37" t="str">
+      <c r="I29" s="36" t="n">
+        <v>22028486</v>
+      </c>
+      <c r="J29" s="37" t="n">
         <f aca="false">IF(OR(G29="",I29=""),"",G29*I29/1000000)</f>
-        <v/>
-      </c>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="16" t="str">
+        <v>11384.10127994</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <v>-0.1199</v>
+      </c>
+      <c r="L29" s="21" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="N29" s="25" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="O29" s="21" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="P29" s="21" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="Q29" s="21" t="n">
+        <v>-0.2152</v>
+      </c>
+      <c r="R29" s="21" t="n">
+        <v>1.7457</v>
+      </c>
+      <c r="S29" s="38" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="T29" s="21" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="U29" s="21" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="V29" s="19" t="n">
+        <v>46329</v>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="X29" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y29" s="26" t="n">
+        <v>501.59</v>
+      </c>
+      <c r="Z29" s="26" t="n">
+        <v>556.31</v>
+      </c>
+      <c r="AA29" s="26" t="n">
+        <v>337.43</v>
+      </c>
+      <c r="AB29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(F29="Short",(AND(M29&lt;&gt;"",N(M29)&lt;0))+(AND(L29&lt;&gt;"",N(L29)&lt;0))+(AND(K29&lt;&gt;"",N(K29)&lt;0))+AND(L29&lt;&gt;"",M29&lt;&gt;"",N(M29)&lt;N(L29)),(N(M29)&gt;0)+(N(L29)&gt;0)+(N(K29)&gt;0)+AND(L29&lt;&gt;"",M29&lt;&gt;"",N(M29)&gt;N(L29))))</f>
-        <v/>
-      </c>
-      <c r="AC29" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AC29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(F29="Short",IF(N29="",0,IF(AND(N29&gt;=30,N29&lt;=50),2,IF(OR(AND(N29&gt;=25,N29&lt;30),AND(N29&gt;50,N29&lt;=60)),1,0)))+IF(P29="",0,IF(AND(IF(B29="JSE",$L$5,$L$4)&lt;&gt;"",P29&lt;IF(B29="JSE",$L$5,$L$4)),2,IF(P29&lt;0,1,0))),IF(N29="",0,IF(AND(N29&gt;=50,N29&lt;=70),2,IF(OR(AND(N29&gt;=40,N29&lt;50),AND(N29&gt;70,N29&lt;=75)),1,0)))+IF(P29="",0,IF(AND(IF(B29="JSE",$L$5,$L$4)&lt;&gt;"",P29&gt;IF(B29="JSE",$L$5,$L$4)),2,IF(P29&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD29" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AD29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(F29="Short",IF(R29="",0,IF(R29&lt;=0.1,2,IF(R29&lt;=0.25,1,0))),IF(Q29="",0,IF(Q29&gt;=-0.1,2,IF(Q29&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE29" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(J29="",0,IF(J29&gt;=IF(B29="JSE",$L$7,$L$6),2,IF(J29&gt;=IF(B29="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF29" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(F29="Short",AND(T29&lt;&gt;"",N(T29)&lt;0),N(T29)&gt;0)+(N(S29)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG29" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(AL29="",0,IF(AL29&gt;=3,4,IF(AL29&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH29" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(AND(ISNUMBER(V29),ISNUMBER(A29),V29&gt;=A29,V29-A29&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI29" s="16" t="str">
+        <v>-2</v>
+      </c>
+      <c r="AI29" s="16" t="n">
         <f aca="false">IF(C29="","",IF(AND(F29="Short",N(U29)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ29" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="23" t="n">
         <f aca="false">IF(C29="","",SUM(AB29:AI29))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="AK29" s="24" t="str">
         <f aca="false">IF(C29="","",IF(AJ29&gt;=14,"A",IF(AJ29&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL29" s="39" t="str">
+        <v>C</v>
+      </c>
+      <c r="AL29" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y29="",Z29="",AA29=""),"",IF(F29="Short",IF(Z29&lt;=Y29,"",(Y29-AA29)/(Z29-Y29)),IF(Y29&lt;=Z29,"",(AA29-Y29)/(Y29-Z29)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM29" s="37" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="37" t="n">
         <f aca="false">IF(OR(Y29="",Z29="",N(Y29)=N(Z29)),"",IF(OR(AND(F29="Short",Z29&lt;Y29),AND(NOT(F29="Short"),Z29&gt;Y29)),"stop on wrong side",ABS(Y29-Z29)))</f>
-        <v/>
-      </c>
-      <c r="AN29" s="40" t="str">
+        <v>54.72</v>
+      </c>
+      <c r="AN29" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM29)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM29,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO29" s="37" t="str">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="37" t="n">
         <f aca="false">IFERROR(IF(AN29="","",AN29*Y29),"")</f>
-        <v/>
-      </c>
-      <c r="AP29" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="AP29" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ29" s="19"/>
       <c r="AR29" s="26"/>
       <c r="AS29" s="41" t="str">
@@ -7873,102 +8359,154 @@
       </c>
       <c r="AU29" s="14" t="str">
         <f aca="false">IF(C29="","",IF(AP29="Open position",IF(IF(F29="Short",AND(ISNUMBER(AR29),ISNUMBER(Z29),AR29&gt;=Z29),AND(ISNUMBER(AR29),ISNUMBER(Z29),AR29&lt;=Z29)),IF(F29="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F29="Short",AND(ISNUMBER(AR29),ISNUMBER(AA29),AR29&lt;=AA29),AND(ISNUMBER(AR29),ISNUMBER(AA29),AR29&gt;=AA29)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT29),AT29&gt;182),IF(F29="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT29),AT29&gt;42,ISNUMBER(AS29),AS29&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F29="Short",AND(L29&lt;&gt;"",N(L29)&gt;0),AND(L29&lt;&gt;"",N(L29)&lt;0)),IF(F29="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP29="Closed",AP29="Dropped"),"Closed",IF(AK29="A",IF(F29="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK29="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV29" s="35"/>
-      <c r="AX29" s="43" t="str">
+        <v>Drop or re-check next week</v>
+      </c>
+      <c r="AV29" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="AX29" s="43" t="n">
         <f aca="false">IF(AND(C29&lt;&gt;"",A29=$C$4,ISNUMBER(AJ29)),AJ29+ROW()/100000,"")</f>
-        <v/>
+        <v>8.00029</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="26"/>
+      <c r="A30" s="19" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G30" s="26" t="n">
+        <v>51.91</v>
+      </c>
       <c r="H30" s="26"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="37" t="str">
+      <c r="I30" s="36" t="n">
+        <v>7530214</v>
+      </c>
+      <c r="J30" s="37" t="n">
         <f aca="false">IF(OR(G30="",I30=""),"",G30*I30/1000000)</f>
-        <v/>
-      </c>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="38"/>
+        <v>390.89340874</v>
+      </c>
+      <c r="K30" s="21" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="L30" s="21" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="M30" s="21" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="N30" s="25" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="O30" s="21" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="P30" s="21" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="Q30" s="21" t="n">
+        <v>-0.0191</v>
+      </c>
+      <c r="R30" s="21" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="S30" s="38" t="n">
+        <v>0.75</v>
+      </c>
       <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="26"/>
-      <c r="Z30" s="26"/>
-      <c r="AA30" s="26"/>
-      <c r="AB30" s="16" t="str">
+      <c r="U30" s="21" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="V30" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X30" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y30" s="26" t="n">
+        <v>47.21</v>
+      </c>
+      <c r="Z30" s="26" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="AA30" s="26" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="AB30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(F30="Short",(AND(M30&lt;&gt;"",N(M30)&lt;0))+(AND(L30&lt;&gt;"",N(L30)&lt;0))+(AND(K30&lt;&gt;"",N(K30)&lt;0))+AND(L30&lt;&gt;"",M30&lt;&gt;"",N(M30)&lt;N(L30)),(N(M30)&gt;0)+(N(L30)&gt;0)+(N(K30)&gt;0)+AND(L30&lt;&gt;"",M30&lt;&gt;"",N(M30)&gt;N(L30))))</f>
-        <v/>
-      </c>
-      <c r="AC30" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(F30="Short",IF(N30="",0,IF(AND(N30&gt;=30,N30&lt;=50),2,IF(OR(AND(N30&gt;=25,N30&lt;30),AND(N30&gt;50,N30&lt;=60)),1,0)))+IF(P30="",0,IF(AND(IF(B30="JSE",$L$5,$L$4)&lt;&gt;"",P30&lt;IF(B30="JSE",$L$5,$L$4)),2,IF(P30&lt;0,1,0))),IF(N30="",0,IF(AND(N30&gt;=50,N30&lt;=70),2,IF(OR(AND(N30&gt;=40,N30&lt;50),AND(N30&gt;70,N30&lt;=75)),1,0)))+IF(P30="",0,IF(AND(IF(B30="JSE",$L$5,$L$4)&lt;&gt;"",P30&gt;IF(B30="JSE",$L$5,$L$4)),2,IF(P30&gt;0,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AD30" s="16" t="str">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(F30="Short",IF(R30="",0,IF(R30&lt;=0.1,2,IF(R30&lt;=0.25,1,0))),IF(Q30="",0,IF(Q30&gt;=-0.1,2,IF(Q30&gt;=-0.25,1,0)))))</f>
-        <v/>
-      </c>
-      <c r="AE30" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(J30="",0,IF(J30&gt;=IF(B30="JSE",$L$7,$L$6),2,IF(J30&gt;=IF(B30="JSE",$L$7,$L$6)/4,1,0))))</f>
-        <v/>
-      </c>
-      <c r="AF30" s="16" t="str">
+        <v>2</v>
+      </c>
+      <c r="AF30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(F30="Short",AND(T30&lt;&gt;"",N(T30)&lt;0),N(T30)&gt;0)+(N(S30)&gt;=1.5))</f>
-        <v/>
-      </c>
-      <c r="AG30" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(AL30="",0,IF(AL30&gt;=3,4,IF(AL30&gt;=2,2,0))))</f>
-        <v/>
-      </c>
-      <c r="AH30" s="16" t="str">
+        <v>4</v>
+      </c>
+      <c r="AH30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(AND(ISNUMBER(V30),ISNUMBER(A30),V30&gt;=A30,V30-A30&lt;=14),-2,0))</f>
-        <v/>
-      </c>
-      <c r="AI30" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="16" t="n">
         <f aca="false">IF(C30="","",IF(AND(F30="Short",N(U30)&gt;=0.2),-1,0))</f>
-        <v/>
-      </c>
-      <c r="AJ30" s="23" t="str">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="23" t="n">
         <f aca="false">IF(C30="","",SUM(AB30:AI30))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK30" s="24" t="str">
         <f aca="false">IF(C30="","",IF(AJ30&gt;=14,"A",IF(AJ30&gt;=10,"B","C")))</f>
-        <v/>
-      </c>
-      <c r="AL30" s="39" t="str">
+        <v>C</v>
+      </c>
+      <c r="AL30" s="39" t="n">
         <f aca="false">IFERROR(IF(OR(Y30="",Z30="",AA30=""),"",IF(F30="Short",IF(Z30&lt;=Y30,"",(Y30-AA30)/(Z30-Y30)),IF(Y30&lt;=Z30,"",(AA30-Y30)/(Y30-Z30)))),"")</f>
-        <v/>
-      </c>
-      <c r="AM30" s="37" t="str">
+        <v>3.00000000000001</v>
+      </c>
+      <c r="AM30" s="37" t="n">
         <f aca="false">IF(OR(Y30="",Z30="",N(Y30)=N(Z30)),"",IF(OR(AND(F30="Short",Z30&lt;Y30),AND(NOT(F30="Short"),Z30&gt;Y30)),"stop on wrong side",ABS(Y30-Z30)))</f>
-        <v/>
-      </c>
-      <c r="AN30" s="40" t="str">
+        <v>2.66</v>
+      </c>
+      <c r="AN30" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM30)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM30,2)),"")</f>
-        <v/>
-      </c>
-      <c r="AO30" s="37" t="str">
+        <v>0.17</v>
+      </c>
+      <c r="AO30" s="37" t="n">
         <f aca="false">IFERROR(IF(AN30="","",AN30*Y30),"")</f>
-        <v/>
-      </c>
-      <c r="AP30" s="35"/>
+        <v>8.0257</v>
+      </c>
+      <c r="AP30" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="AQ30" s="19"/>
       <c r="AR30" s="26"/>
       <c r="AS30" s="41" t="str">
@@ -7981,12 +8519,14 @@
       </c>
       <c r="AU30" s="14" t="str">
         <f aca="false">IF(C30="","",IF(AP30="Open position",IF(IF(F30="Short",AND(ISNUMBER(AR30),ISNUMBER(Z30),AR30&gt;=Z30),AND(ISNUMBER(AR30),ISNUMBER(Z30),AR30&lt;=Z30)),IF(F30="Short","COVER — stop hit (buy back)","SELL — stop hit"),IF(IF(F30="Short",AND(ISNUMBER(AR30),ISNUMBER(AA30),AR30&lt;=AA30),AND(ISNUMBER(AR30),ISNUMBER(AA30),AR30&gt;=AA30)),"TAKE PROFIT — target hit",IF(AND(ISNUMBER(AT30),AT30&gt;182),IF(F30="Short","COVER — 6-month time limit","SELL — 6-month time limit"),IF(AND(ISNUMBER(AT30),AT30&gt;42,ISNUMBER(AS30),AS30&lt;0.02),"REVIEW — no progress after 6 weeks",IF(IF(F30="Short",AND(L30&lt;&gt;"",N(L30)&gt;0),AND(L30&lt;&gt;"",N(L30)&lt;0)),IF(F30="Short","REVIEW — back above 50-day avg","REVIEW — below 50-day avg"),"HOLD"))))),IF(OR(AP30="Closed",AP30="Dropped"),"Closed",IF(AK30="A",IF(F30="Short","Run Technical Review — SHORT entry","Run Technical Review — LONG entry"),IF(AK30="B","Watch — wait for setup","Drop or re-check next week")))))</f>
-        <v/>
-      </c>
-      <c r="AV30" s="35"/>
-      <c r="AX30" s="43" t="str">
+        <v>Drop or re-check next week</v>
+      </c>
+      <c r="AV30" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="AX30" s="43" t="n">
         <f aca="false">IF(AND(C30&lt;&gt;"",A30=$C$4,ISNUMBER(AJ30)),AJ30+ROW()/100000,"")</f>
-        <v/>
+        <v>7.0003</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27577,7 +28117,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:I68"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="14"/>
@@ -27591,7 +28131,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -27602,7 +28142,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -27615,7 +28155,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -27628,7 +28168,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -27638,12 +28178,12 @@
       <c r="G5" s="44"/>
       <c r="H5" s="44"/>
       <c r="I5" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44"/>
@@ -27653,12 +28193,12 @@
       <c r="G6" s="44"/>
       <c r="H6" s="44"/>
       <c r="I6" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="B7" s="44"/>
       <c r="C7" s="44"/>
@@ -27668,12 +28208,12 @@
       <c r="G7" s="44"/>
       <c r="H7" s="44"/>
       <c r="I7" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="B8" s="44"/>
       <c r="C8" s="44"/>
@@ -27683,12 +28223,12 @@
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
       <c r="I8" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="B9" s="44"/>
       <c r="C9" s="44"/>
@@ -27698,12 +28238,12 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -27713,12 +28253,12 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="B11" s="44"/>
       <c r="C11" s="44"/>
@@ -27728,12 +28268,12 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
@@ -27743,12 +28283,12 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -27758,12 +28298,12 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -27779,39 +28319,39 @@
         <v>33</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>35</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="H16" s="31" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="n">
         <v>46298</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D17" s="15" t="str">
         <f aca="false">IF(OR(B17="",C17=""),"",IF(AND(B17="Y",C17="Y"),"RISK-ON → favour longs",IF(AND(B17="N",C17="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
@@ -27829,21 +28369,21 @@
         <v>0</v>
       </c>
       <c r="H17" s="47" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="I17" s="47" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="n">
         <v>46312</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D18" s="15" t="str">
         <f aca="false">IF(OR(B18="",C18=""),"",IF(AND(B18="Y",C18="Y"),"RISK-ON → favour longs",IF(AND(B18="N",C18="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
@@ -27861,31 +28401,37 @@
         <v>0</v>
       </c>
       <c r="H18" s="47" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="I18" s="47" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19"/>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="n">
+        <v>46318</v>
+      </c>
       <c r="B19" s="46"/>
       <c r="C19" s="46"/>
       <c r="D19" s="15" t="str">
         <f aca="false">IF(OR(B19="",C19=""),"",IF(AND(B19="Y",C19="Y"),"RISK-ON → favour longs",IF(AND(B19="N",C19="N"),"RISK-OFF → favour shorts","MIXED → both, smaller")))</f>
         <v/>
       </c>
-      <c r="E19" s="15" t="str">
+      <c r="E19" s="15" t="n">
         <f aca="false">IF(A19="","",COUNTIFS('Swing Watchlist'!$A$11:$A$210,A19,'Swing Watchlist'!$C$11:$C$210,"?*"))</f>
-        <v/>
-      </c>
-      <c r="F19" s="15" t="str">
+        <v>9</v>
+      </c>
+      <c r="F19" s="15" t="n">
         <f aca="false">IF(A19="","",COUNTIFS('Swing Watchlist'!$A$11:$A$210,A19,'Swing Watchlist'!$AK$11:$AK$210,"A"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="47"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="47" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
+      <c r="I19" s="47" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19"/>
@@ -28927,7 +29473,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="16"/>
@@ -28935,7 +29481,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -28945,7 +29491,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -28957,7 +29503,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -28969,10 +29515,10 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -28983,10 +29529,10 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -28997,10 +29543,10 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -29011,10 +29557,10 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -29025,10 +29571,10 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -29039,10 +29585,10 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -29053,10 +29599,10 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -29067,7 +29613,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -29079,10 +29625,10 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -29093,10 +29639,10 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -29107,10 +29653,10 @@
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -29121,10 +29667,10 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -29135,10 +29681,10 @@
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -29149,10 +29695,10 @@
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -29163,10 +29709,10 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -29180,7 +29726,7 @@
         <v>88</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -29191,7 +29737,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -29203,10 +29749,10 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -29217,10 +29763,10 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -29231,10 +29777,10 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -29287,7 +29833,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AP158"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
@@ -29318,7 +29864,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -29360,7 +29906,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -29404,20 +29950,20 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="19" t="n">
         <v>46296</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
       <c r="J4" s="22" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="K4" s="22"/>
       <c r="L4" s="23" t="n">
@@ -29433,20 +29979,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="25" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="E5" s="20"/>
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
       <c r="J5" s="22" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="K5" s="22"/>
       <c r="L5" s="24" t="str">
@@ -29456,7 +30002,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="B7" s="27"/>
       <c r="C7" s="27"/>
@@ -29481,7 +30027,7 @@
       <c r="V7" s="27"/>
       <c r="W7" s="27"/>
       <c r="X7" s="28" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="Y7" s="28"/>
       <c r="Z7" s="28"/>
@@ -29493,10 +30039,10 @@
       <c r="AF7" s="28"/>
       <c r="AG7" s="28"/>
       <c r="AH7" s="48" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="AI7" s="30" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="AJ7" s="30"/>
       <c r="AK7" s="30"/>
@@ -29527,79 +30073,79 @@
         <v>146</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="L8" s="31" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="M8" s="31" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="N8" s="31" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="O8" s="31" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="P8" s="31" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="Q8" s="31" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="R8" s="31" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="S8" s="31" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="T8" s="31" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="U8" s="31" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="V8" s="31" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="W8" s="31" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="X8" s="32" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="Y8" s="32" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="Z8" s="32" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="AA8" s="32" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="AB8" s="32" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="AC8" s="32" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="AD8" s="32" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="AE8" s="32" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AF8" s="32" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="AG8" s="32" t="s">
         <v>51</v>
@@ -29611,19 +30157,19 @@
         <v>172</v>
       </c>
       <c r="AJ8" s="34" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="AK8" s="34" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="AL8" s="34" t="s">
         <v>174</v>
       </c>
       <c r="AM8" s="34" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="AN8" s="34" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29741,10 +30287,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI9" s="35" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="AJ9" s="35" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="AK9" s="19" t="n">
         <v>46309</v>
@@ -29757,7 +30303,7 @@
         <v>0</v>
       </c>
       <c r="AN9" s="35" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="AP9" s="43" t="n">
         <f aca="false">IF(AND(C9&lt;&gt;"",A9=$C$4,ISNUMBER(AF9)),AF9+ROW()/100000,"")</f>
@@ -29879,10 +30425,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI10" s="35" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="AJ10" s="35" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="AK10" s="19" t="n">
         <v>46309</v>
@@ -29895,7 +30441,7 @@
         <v>0</v>
       </c>
       <c r="AN10" s="35" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AP10" s="43" t="n">
         <f aca="false">IF(AND(C10&lt;&gt;"",A10=$C$4,ISNUMBER(AF10)),AF10+ROW()/100000,"")</f>
@@ -30015,10 +30561,10 @@
         <v>Full LRC Stock Analysis</v>
       </c>
       <c r="AI11" s="35" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="AJ11" s="35" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="AK11" s="19" t="n">
         <v>46309</v>
@@ -30031,7 +30577,7 @@
         <v>0</v>
       </c>
       <c r="AN11" s="35" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="AP11" s="43" t="n">
         <f aca="false">IF(AND(C11&lt;&gt;"",A11=$C$4,ISNUMBER(AF11)),AF11+ROW()/100000,"")</f>
@@ -30154,7 +30700,7 @@
         <v>192</v>
       </c>
       <c r="AJ12" s="35" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="AK12" s="19" t="n">
         <v>46309</v>
@@ -30167,7 +30713,7 @@
         <v>0</v>
       </c>
       <c r="AN12" s="35" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AP12" s="43" t="n">
         <f aca="false">IF(AND(C12&lt;&gt;"",A12=$C$4,ISNUMBER(AF12)),AF12+ROW()/100000,"")</f>
@@ -30182,13 +30728,13 @@
         <v>179</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>762.5</v>
@@ -30292,7 +30838,7 @@
         <v>192</v>
       </c>
       <c r="AJ13" s="35" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="AK13" s="19" t="n">
         <v>46309</v>
@@ -30305,7 +30851,7 @@
         <v>0</v>
       </c>
       <c r="AN13" s="35" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="AP13" s="43" t="n">
         <f aca="false">IF(AND(C13&lt;&gt;"",A13=$C$4,ISNUMBER(AF13)),AF13+ROW()/100000,"")</f>
@@ -30423,10 +30969,10 @@
         <v>Closed</v>
       </c>
       <c r="AI14" s="35" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AJ14" s="35" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="AK14" s="19" t="n">
         <v>46309</v>
@@ -30439,7 +30985,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="35" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="AP14" s="43" t="n">
         <f aca="false">IF(AND(C14&lt;&gt;"",A14=$C$4,ISNUMBER(AF14)),AF14+ROW()/100000,"")</f>
@@ -30555,10 +31101,10 @@
         <v>Closed</v>
       </c>
       <c r="AI15" s="35" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AJ15" s="35" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="AK15" s="19" t="n">
         <v>46309</v>
@@ -30571,7 +31117,7 @@
         <v>0</v>
       </c>
       <c r="AN15" s="35" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="AP15" s="43" t="n">
         <f aca="false">IF(AND(C15&lt;&gt;"",A15=$C$4,ISNUMBER(AF15)),AF15+ROW()/100000,"")</f>
@@ -30687,10 +31233,10 @@
         <v>Closed</v>
       </c>
       <c r="AI16" s="35" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AJ16" s="35" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="AK16" s="19" t="n">
         <v>46309</v>
@@ -30703,7 +31249,7 @@
         <v>0</v>
       </c>
       <c r="AN16" s="35" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="AP16" s="43" t="n">
         <f aca="false">IF(AND(C16&lt;&gt;"",A16=$C$4,ISNUMBER(AF16)),AF16+ROW()/100000,"")</f>
@@ -30823,10 +31369,10 @@
         <v>Closed</v>
       </c>
       <c r="AI17" s="35" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AJ17" s="35" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="AK17" s="19" t="n">
         <v>46309</v>
@@ -30839,7 +31385,7 @@
         <v>0</v>
       </c>
       <c r="AN17" s="35" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="AP17" s="43" t="n">
         <f aca="false">IF(AND(C17&lt;&gt;"",A17=$C$4,ISNUMBER(AF17)),AF17+ROW()/100000,"")</f>
@@ -30959,10 +31505,10 @@
         <v>Closed</v>
       </c>
       <c r="AI18" s="35" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AJ18" s="35" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="AK18" s="19" t="n">
         <v>46309</v>
@@ -30975,7 +31521,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="35" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="AP18" s="43" t="n">
         <f aca="false">IF(AND(C18&lt;&gt;"",A18=$C$4,ISNUMBER(AF18)),AF18+ROW()/100000,"")</f>
@@ -42552,7 +43098,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
@@ -42564,7 +43110,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -42573,7 +43119,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -42584,7 +43130,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -42595,7 +43141,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="44" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
@@ -42603,12 +43149,12 @@
       <c r="E5" s="44"/>
       <c r="F5" s="44"/>
       <c r="G5" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="44"/>
@@ -42616,12 +43162,12 @@
       <c r="E6" s="44"/>
       <c r="F6" s="44"/>
       <c r="G6" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="B7" s="44"/>
       <c r="C7" s="44"/>
@@ -42629,12 +43175,12 @@
       <c r="E7" s="44"/>
       <c r="F7" s="44"/>
       <c r="G7" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="B8" s="44"/>
       <c r="C8" s="44"/>
@@ -42642,12 +43188,12 @@
       <c r="E8" s="44"/>
       <c r="F8" s="44"/>
       <c r="G8" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="B9" s="44"/>
       <c r="C9" s="44"/>
@@ -42655,12 +43201,12 @@
       <c r="E9" s="44"/>
       <c r="F9" s="44"/>
       <c r="G9" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
@@ -42668,12 +43214,12 @@
       <c r="E10" s="44"/>
       <c r="F10" s="44"/>
       <c r="G10" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="B11" s="44"/>
       <c r="C11" s="44"/>
@@ -42681,12 +43227,12 @@
       <c r="E11" s="44"/>
       <c r="F11" s="44"/>
       <c r="G11" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
@@ -42694,12 +43240,12 @@
       <c r="E12" s="44"/>
       <c r="F12" s="44"/>
       <c r="G12" s="45" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -42707,12 +43253,12 @@
       <c r="E13" s="44"/>
       <c r="F13" s="44"/>
       <c r="G13" s="45" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -42729,22 +43275,22 @@
         <v>35</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>43</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="51" t="n">
         <v>46296</v>
       </c>
@@ -42757,16 +43303,16 @@
         <v>5</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="G17" s="47" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43159,7 +43705,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -43168,7 +43714,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C1" s="2" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -43176,7 +43722,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -43186,7 +43732,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -43196,587 +43742,587 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="52" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="52" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="52" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="52" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E9" s="52" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="52" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="E11" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F11" s="52" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="E13" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F13" s="52" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="D15" s="52" t="s">
+        <v>436</v>
+      </c>
+      <c r="E15" s="52" t="s">
         <v>416</v>
       </c>
-      <c r="E15" s="52" t="s">
-        <v>396</v>
-      </c>
       <c r="F15" s="52" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="52" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E17" s="52" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="F17" s="52" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E18" s="52" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="F18" s="52" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E19" s="52" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="F19" s="52" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="D21" s="52" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="F21" s="52" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="E22" s="52" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="F22" s="52" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="F23" s="52" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D24" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E24" s="52" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="F24" s="52" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="52" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E25" s="52" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="52" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="E26" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="52" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="C27" s="52" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="D27" s="52" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="E27" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F27" s="52" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="52" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="E28" s="52" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="F28" s="52" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="52" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="52" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="C30" s="52" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="E30" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F30" s="52" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="52" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>152</v>
       </c>
       <c r="C31" s="52" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="D31" s="52" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="E31" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F31" s="52" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="52" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="C32" s="52" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="D32" s="52" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="E32" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F32" s="52" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="52" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="D33" s="52" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="53" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="B34" s="53"/>
       <c r="C34" s="53"/>
@@ -43786,7 +44332,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -43796,10 +44342,10 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="54" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -43808,10 +44354,10 @@
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="54" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -43820,7 +44366,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -43830,92 +44376,92 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="55" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="B42" s="55"/>
       <c r="C42" s="52" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
       <c r="D42" s="52" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="E42" s="52" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="F42" s="52" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="55" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="B43" s="55"/>
       <c r="C43" s="52" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="D43" s="52" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="E43" s="52" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="F43" s="52" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="55" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="B44" s="55"/>
       <c r="C44" s="52" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="D44" s="52" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="E44" s="52" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="F44" s="52" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="55" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="B45" s="55"/>
       <c r="C45" s="52" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="D45" s="52" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="E45" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F45" s="52" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -43924,139 +44470,139 @@
       </c>
       <c r="B46" s="55"/>
       <c r="C46" s="52" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="D46" s="52" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="E46" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F46" s="52" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="55" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="B47" s="55"/>
       <c r="C47" s="52" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="D47" s="52" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="E47" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="55" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="B48" s="55"/>
       <c r="C48" s="52" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="D48" s="52" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="E48" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="F48" s="52" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="55" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="B49" s="55"/>
       <c r="C49" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D49" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E49" s="52" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="F49" s="52" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="55" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="B50" s="55"/>
       <c r="C50" s="52" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="D50" s="52" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="E50" s="52" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="F50" s="52" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="55" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="B51" s="55"/>
       <c r="C51" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D51" s="52" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E51" s="52" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="F51" s="52" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="55" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="B52" s="55"/>
       <c r="C52" s="52" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="D52" s="52" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="E52" s="52" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="F52" s="52" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="55" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="B53" s="55"/>
       <c r="C53" s="52" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="D53" s="52" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="E53" s="52" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="F53" s="52"/>
     </row>

--- a/templates/LRC_Watchlist_master.xlsx
+++ b/templates/LRC_Watchlist_master.xlsx
@@ -707,61 +707,61 @@
     <t xml:space="preserve">Trigger: Sell stop below the 15-day low (49.11) — only AFTER the 14 Oct results are digested. Short entry 49.00, stop 50.96 (2×ATR 0.98), target 43.12 (3R). LRC Work-sheet 14 Oct: SELL (6-m target ~$38.37, -25%; score 3.5/5; technical: CLEARED — STAGED ENTRY). SELL (−25%) + technical clearance. Results 14 Oct (today) — wait for the reaction. 5th short: house limit is 4 open shorts, so only if one of the others has not triggered. Data 13 Oct close: stockanalysis statistics + daily history to 13 Oct (SMA20/ATR14 computed); Perf Half vs ~13 Apr close; EPS growth this yr = consensus current FY (adjusted). Perf Quarter n/f (history page holds 50 sessions). Finviz itself blocked for us — same filters applied manually. — P. Nkuna</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONG: Trend continuation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating BUY (6-m value 262.56); NOT CLEARED. Entry 219.32, stop 207.2 (2×ATR), target 255.68 (3R).  — LRC Watchlist</t>
+  </si>
+  <si>
     <t xml:space="preserve">Intuit</t>
   </si>
   <si>
-    <t xml:space="preserve">LONG: Trend continuation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating BUY (6-m value 426.0); NOT CLEARED. Entry 358.75, stop 332.97 (2×ATR), target 436.09 (3R).  — LRC Watchlist Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating BUY (6-m value 262.56); NOT CLEARED. Entry 219.32, stop 207.2 (2×ATR), target 255.68 (3R).  — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating BUY (6-m value 426.0); NOT CLEARED. Entry 358.75, stop 332.97 (2×ATR), target 436.09 (3R).  — LRC Watchlist</t>
   </si>
   <si>
     <t xml:space="preserve">Deckers Outdoor</t>
   </si>
   <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating BUY (6-m value 103.0); NOT CLEARED. Entry 88.1, stop 82.28 (2×ATR), target 105.56 (3R).  — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating BUY (6-m value 103.0); NOT CLEARED. Entry 88.1, stop 82.28 (2×ATR), target 105.56 (3R).  — LRC Watchlist</t>
   </si>
   <si>
     <t xml:space="preserve">Wabtec</t>
   </si>
   <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 248.07); CLEARED. Entry 270.6, stop 285.66 (2×ATR), target 225.42 (3R).  — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating SELL (6-m value 248.07); CLEARED. Entry 270.6, stop 285.66 (2×ATR), target 225.42 (3R).  — LRC Watchlist</t>
   </si>
   <si>
     <t xml:space="preserve">Nike</t>
   </si>
   <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 29.75); CLEARED. Entry 32.69, stop 34.87 (2×ATR), target 26.15 (3R).  — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating SELL (6-m value 29.75); CLEARED. Entry 32.69, stop 34.87 (2×ATR), target 26.15 (3R).  — LRC Watchlist</t>
   </si>
   <si>
     <t xml:space="preserve">Arista Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 144.61); CLEARED — results within 14 days. Entry 167.9, stop 185.06 (2×ATR), target 116.42 (3R). Results 2026-11-03 — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating SELL (6-m value 144.61); CLEARED — results within 14 days. Entry 167.9, stop 185.06 (2×ATR), target 116.42 (3R). Results 2026-11-03 — LRC Watchlist</t>
   </si>
   <si>
     <t xml:space="preserve">Dell Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 404.7); CLEARED. Entry 438.62, stop 500.56 (2×ATR), target 252.8 (3R).  — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating SELL (6-m value 404.7); CLEARED. Entry 438.62, stop 500.56 (2×ATR), target 252.8 (3R).  — LRC Watchlist</t>
   </si>
   <si>
     <t xml:space="preserve">Advanced Micro Devices</t>
   </si>
   <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 402.73); CLEARED — results within 14 days. Entry 501.59, stop 556.31 (2×ATR), target 337.43 (3R). Results 2026-11-03; house limit: max 4 shorts — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating SELL (6-m value 402.73); CLEARED — results within 14 days. Entry 501.59, stop 556.31 (2×ATR), target 337.43 (3R). Results 2026-11-03; house limit: max 4 shorts — LRC Watchlist</t>
   </si>
   <si>
     <t xml:space="preserve">Fastenal</t>
   </si>
   <si>
-    <t xml:space="preserve">Agent 2026-10-24T06:26+02:00: LRC rating SELL (6-m value 38.37); CLEARED. Entry 47.21, stop 49.87 (2×ATR), target 39.23 (3R). house limit: max 4 shorts — LRC Watchlist Agent</t>
+    <t xml:space="preserve">Agent 2026-10-25T15:09+02:00: LRC rating SELL (6-m value 38.37); CLEARED. Entry 47.21, stop 49.87 (2×ATR), target 39.23 (3R). house limit: max 4 shorts — LRC Watchlist</t>
   </si>
   <si>
     <t xml:space="preserve">Weekly Review — swing (every weekend)</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">Finviz is blocked for our tools, so the Swing Long / Swing Short presets were applied manually on stockanalysis.com data (13 Oct closes). LRC RULE: only BUY/SELL-rated names with technical clearance are tradeable. LONGS: only NVDA qualifies; INTU and DECK are BUY-rated but in downtrends (watch only). 2 long slots unfilled — the momentum names the long preset finds (DELL, HPE, KEYS, APH, AMD) all rate SELL on valuation. SHORTS: NKE, ANET, AMD, DELL, FAST (max 4 open; FAST only after its 14 Oct results). Event risk inside 14 days: WAB 21 Oct, DECK 22 Oct, META 21 Oct, APH/GOOGL 28 Oct. S&amp;P 500 above its 200-day; JSE All Share below (−7.4% in 6 months). Lesson: an un-entered trigger cost us the PCTY move (+9%) — set conditional orders when a setup is approved. — P. Nkuna</t>
   </si>
   <si>
-    <t xml:space="preserve">Built by the LRC Watchlist Agent 2026-10-24T06:26+02:00: 3 long / 6 short candidates under house rules. Analyst to review before any trade.</t>
+    <t xml:space="preserve">Built by the LRC Watchlist 2026-10-25T15:09+02:00: 3 long / 6 short candidates under house rules. Analyst to review before any trade.</t>
   </si>
   <si>
     <t xml:space="preserve">How to pick long-term investments (hold 5 to 10+ years) — every month</t>
@@ -2597,9 +2597,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2613,7 +2613,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2640,9 +2640,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>420840</xdr:colOff>
+      <xdr:colOff>420480</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2656,7 +2656,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2683,9 +2683,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2699,7 +2699,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2726,9 +2726,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2742,7 +2742,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2769,9 +2769,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2785,7 +2785,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2812,9 +2812,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2828,7 +2828,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2855,9 +2855,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2871,7 +2871,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2898,9 +2898,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2914,7 +2914,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2941,9 +2941,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>865440</xdr:colOff>
+      <xdr:colOff>865080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>570240</xdr:rowOff>
+      <xdr:rowOff>569880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2957,7 +2957,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="865440" cy="570240"/>
+          <a:ext cx="865080" cy="569880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4021,15 +4021,15 @@
       </c>
       <c r="B18" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>DELL</v>
+        <v>NVDA</v>
       </c>
       <c r="C18" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
-        <v>Short</v>
+        <v>Long</v>
       </c>
       <c r="D18" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="15" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AK$11:$AK$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,3),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B19" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>ANET</v>
+        <v>DELL</v>
       </c>
       <c r="C19" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,4),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
@@ -4119,11 +4119,11 @@
       </c>
       <c r="B20" s="14" t="str">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$C$11:$C$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
-        <v>NVDA</v>
+        <v>ANET</v>
       </c>
       <c r="C20" s="15" t="str">
         <f aca="false">IFERROR(IF(INDEX('Swing Watchlist'!$F$11:$F$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0))="Short","Short","Long"),"")</f>
-        <v>Long</v>
+        <v>Short</v>
       </c>
       <c r="D20" s="16" t="n">
         <f aca="false">IFERROR(INDEX('Swing Watchlist'!$AJ$11:$AJ$210,MATCH(LARGE('Swing Watchlist'!$AX$11:$AX$210,5),'Swing Watchlist'!$AX$11:$AX$210,0)),"")</f>
@@ -7091,7 +7091,7 @@
         <v>179</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D22" s="35" t="s">
         <v>224</v>
@@ -7103,66 +7103,68 @@
         <v>183</v>
       </c>
       <c r="G22" s="26" t="n">
-        <v>343.39</v>
-      </c>
-      <c r="H22" s="26"/>
+        <v>210.96</v>
+      </c>
+      <c r="H22" s="26" t="n">
+        <v>5090</v>
+      </c>
       <c r="I22" s="36" t="n">
-        <v>3794424</v>
+        <v>116520944</v>
       </c>
       <c r="J22" s="37" t="n">
         <f aca="false">IF(OR(G22="",I22=""),"",G22*I22/1000000)</f>
-        <v>1302.96725736</v>
+        <v>24581.25834624</v>
       </c>
       <c r="K22" s="21" t="n">
-        <v>0.1216</v>
+        <v>-0.0646</v>
       </c>
       <c r="L22" s="21" t="n">
-        <v>0.0694</v>
+        <v>-0.0518</v>
       </c>
       <c r="M22" s="21" t="n">
-        <v>-0.0662</v>
+        <v>0.0358</v>
       </c>
       <c r="N22" s="25" t="n">
-        <v>64.05</v>
+        <v>38.09</v>
       </c>
       <c r="O22" s="21" t="n">
-        <v>0.1299</v>
+        <v>0.0735</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>-0.1327</v>
+        <v>0.0129</v>
       </c>
       <c r="Q22" s="21" t="n">
-        <v>-0.5017</v>
+        <v>-0.1332</v>
       </c>
       <c r="R22" s="21" t="n">
-        <v>0.3581</v>
+        <v>0.2842</v>
       </c>
       <c r="S22" s="38" t="n">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="T22" s="21" t="n">
-        <v>-0.0133</v>
+        <v>0.9523</v>
       </c>
       <c r="U22" s="21" t="n">
-        <v>0.0279</v>
+        <v>0.0134</v>
       </c>
       <c r="V22" s="19" t="n">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="W22" s="26" t="n">
-        <v>12.89</v>
+        <v>6.06</v>
       </c>
       <c r="X22" s="35" t="s">
         <v>225</v>
       </c>
       <c r="Y22" s="26" t="n">
-        <v>358.75</v>
+        <v>219.32</v>
       </c>
       <c r="Z22" s="26" t="n">
-        <v>332.97</v>
+        <v>207.2</v>
       </c>
       <c r="AA22" s="26" t="n">
-        <v>436.09</v>
+        <v>255.68</v>
       </c>
       <c r="AB22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",(AND(M22&lt;&gt;"",N(M22)&lt;0))+(AND(L22&lt;&gt;"",N(L22)&lt;0))+(AND(K22&lt;&gt;"",N(K22)&lt;0))+AND(L22&lt;&gt;"",M22&lt;&gt;"",N(M22)&lt;N(L22)),(N(M22)&gt;0)+(N(L22)&gt;0)+(N(K22)&gt;0)+AND(L22&lt;&gt;"",M22&lt;&gt;"",N(M22)&gt;N(L22))))</f>
@@ -7170,11 +7172,11 @@
       </c>
       <c r="AC22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",IF(N22="",0,IF(AND(N22&gt;=30,N22&lt;=50),2,IF(OR(AND(N22&gt;=25,N22&lt;30),AND(N22&gt;50,N22&lt;=60)),1,0)))+IF(P22="",0,IF(AND(IF(B22="JSE",$L$5,$L$4)&lt;&gt;"",P22&lt;IF(B22="JSE",$L$5,$L$4)),2,IF(P22&lt;0,1,0))),IF(N22="",0,IF(AND(N22&gt;=50,N22&lt;=70),2,IF(OR(AND(N22&gt;=40,N22&lt;50),AND(N22&gt;70,N22&lt;=75)),1,0)))+IF(P22="",0,IF(AND(IF(B22="JSE",$L$5,$L$4)&lt;&gt;"",P22&gt;IF(B22="JSE",$L$5,$L$4)),2,IF(P22&gt;0,1,0)))))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",IF(R22="",0,IF(R22&lt;=0.1,2,IF(R22&lt;=0.25,1,0))),IF(Q22="",0,IF(Q22&gt;=-0.1,2,IF(Q22&gt;=-0.25,1,0)))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(J22="",0,IF(J22&gt;=IF(B22="JSE",$L$7,$L$6),2,IF(J22&gt;=IF(B22="JSE",$L$7,$L$6)/4,1,0))))</f>
@@ -7182,7 +7184,7 @@
       </c>
       <c r="AF22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(F22="Short",AND(T22&lt;&gt;"",N(T22)&lt;0),N(T22)&gt;0)+(N(S22)&gt;=1.5))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" s="16" t="n">
         <f aca="false">IF(C22="","",IF(AL22="",0,IF(AL22&gt;=3,4,IF(AL22&gt;=2,2,0))))</f>
@@ -7198,7 +7200,7 @@
       </c>
       <c r="AJ22" s="23" t="n">
         <f aca="false">IF(C22="","",SUM(AB22:AI22))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK22" s="24" t="str">
         <f aca="false">IF(C22="","",IF(AJ22&gt;=14,"A",IF(AJ22&gt;=10,"B","C")))</f>
@@ -7210,15 +7212,15 @@
       </c>
       <c r="AM22" s="37" t="n">
         <f aca="false">IF(OR(Y22="",Z22="",N(Y22)=N(Z22)),"",IF(OR(AND(F22="Short",Z22&lt;Y22),AND(NOT(F22="Short"),Z22&gt;Y22)),"stop on wrong side",ABS(Y22-Z22)))</f>
-        <v>25.78</v>
+        <v>12.12</v>
       </c>
       <c r="AN22" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM22)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM22,2)),"")</f>
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AO22" s="37" t="n">
         <f aca="false">IFERROR(IF(AN22="","",AN22*Y22),"")</f>
-        <v>3.5875</v>
+        <v>6.5796</v>
       </c>
       <c r="AP22" s="35" t="s">
         <v>192</v>
@@ -7242,7 +7244,7 @@
       </c>
       <c r="AX22" s="43" t="n">
         <f aca="false">IF(AND(C22&lt;&gt;"",A22=$C$4,ISNUMBER(AJ22)),AJ22+ROW()/100000,"")</f>
-        <v>10.00022</v>
+        <v>11.00022</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7253,7 +7255,7 @@
         <v>179</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D23" s="35" t="s">
         <v>227</v>
@@ -7265,64 +7267,68 @@
         <v>183</v>
       </c>
       <c r="G23" s="26" t="n">
-        <v>210.96</v>
-      </c>
-      <c r="H23" s="26"/>
+        <v>343.39</v>
+      </c>
+      <c r="H23" s="26" t="n">
+        <v>91.77</v>
+      </c>
       <c r="I23" s="36" t="n">
-        <v>116520944</v>
+        <v>3794424</v>
       </c>
       <c r="J23" s="37" t="n">
         <f aca="false">IF(OR(G23="",I23=""),"",G23*I23/1000000)</f>
-        <v>24581.25834624</v>
+        <v>1302.96725736</v>
       </c>
       <c r="K23" s="21" t="n">
-        <v>-0.0646</v>
+        <v>0.1216</v>
       </c>
       <c r="L23" s="21" t="n">
-        <v>-0.0518</v>
+        <v>0.0694</v>
       </c>
       <c r="M23" s="21" t="n">
-        <v>0.0358</v>
+        <v>-0.0662</v>
       </c>
       <c r="N23" s="25" t="n">
-        <v>38.09</v>
+        <v>64.05</v>
       </c>
       <c r="O23" s="21" t="n">
-        <v>0.0735</v>
+        <v>0.1299</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>0.0129</v>
+        <v>-0.1327</v>
       </c>
       <c r="Q23" s="21" t="n">
-        <v>-0.1332</v>
+        <v>-0.5017</v>
       </c>
       <c r="R23" s="21" t="n">
-        <v>0.2842</v>
+        <v>0.3581</v>
       </c>
       <c r="S23" s="38" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="T23" s="21"/>
+        <v>0.67</v>
+      </c>
+      <c r="T23" s="21" t="n">
+        <v>-0.0189</v>
+      </c>
       <c r="U23" s="21" t="n">
-        <v>0.0134</v>
+        <v>0.0279</v>
       </c>
       <c r="V23" s="19" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="W23" s="26" t="n">
-        <v>6.06</v>
+        <v>12.89</v>
       </c>
       <c r="X23" s="35" t="s">
         <v>225</v>
       </c>
       <c r="Y23" s="26" t="n">
-        <v>219.32</v>
+        <v>358.75</v>
       </c>
       <c r="Z23" s="26" t="n">
-        <v>207.2</v>
+        <v>332.97</v>
       </c>
       <c r="AA23" s="26" t="n">
-        <v>255.68</v>
+        <v>436.09</v>
       </c>
       <c r="AB23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",(AND(M23&lt;&gt;"",N(M23)&lt;0))+(AND(L23&lt;&gt;"",N(L23)&lt;0))+(AND(K23&lt;&gt;"",N(K23)&lt;0))+AND(L23&lt;&gt;"",M23&lt;&gt;"",N(M23)&lt;N(L23)),(N(M23)&gt;0)+(N(L23)&gt;0)+(N(K23)&gt;0)+AND(L23&lt;&gt;"",M23&lt;&gt;"",N(M23)&gt;N(L23))))</f>
@@ -7330,11 +7336,11 @@
       </c>
       <c r="AC23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",IF(N23="",0,IF(AND(N23&gt;=30,N23&lt;=50),2,IF(OR(AND(N23&gt;=25,N23&lt;30),AND(N23&gt;50,N23&lt;=60)),1,0)))+IF(P23="",0,IF(AND(IF(B23="JSE",$L$5,$L$4)&lt;&gt;"",P23&lt;IF(B23="JSE",$L$5,$L$4)),2,IF(P23&lt;0,1,0))),IF(N23="",0,IF(AND(N23&gt;=50,N23&lt;=70),2,IF(OR(AND(N23&gt;=40,N23&lt;50),AND(N23&gt;70,N23&lt;=75)),1,0)))+IF(P23="",0,IF(AND(IF(B23="JSE",$L$5,$L$4)&lt;&gt;"",P23&gt;IF(B23="JSE",$L$5,$L$4)),2,IF(P23&gt;0,1,0)))))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(F23="Short",IF(R23="",0,IF(R23&lt;=0.1,2,IF(R23&lt;=0.25,1,0))),IF(Q23="",0,IF(Q23&gt;=-0.1,2,IF(Q23&gt;=-0.25,1,0)))))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE23" s="16" t="n">
         <f aca="false">IF(C23="","",IF(J23="",0,IF(J23&gt;=IF(B23="JSE",$L$7,$L$6),2,IF(J23&gt;=IF(B23="JSE",$L$7,$L$6)/4,1,0))))</f>
@@ -7370,15 +7376,15 @@
       </c>
       <c r="AM23" s="37" t="n">
         <f aca="false">IF(OR(Y23="",Z23="",N(Y23)=N(Z23)),"",IF(OR(AND(F23="Short",Z23&lt;Y23),AND(NOT(F23="Short"),Z23&gt;Y23)),"stop on wrong side",ABS(Y23-Z23)))</f>
-        <v>12.12</v>
+        <v>25.78</v>
       </c>
       <c r="AN23" s="40" t="n">
         <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(AM23)),$C$6=""),"",ROUNDDOWN($C$6*$C$7/AM23,2)),"")</f>
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AO23" s="37" t="n">
         <f aca="false">IFERROR(IF(AN23="","",AN23*Y23),"")</f>
-        <v>6.5796</v>
+        <v>3.5875</v>
       </c>
       <c r="AP23" s="35" t="s">
         <v>192</v>
@@ -7419,7 +7425,7 @@
         <v>229</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="F24" s="35" t="s">
         <v>183</v>
@@ -7427,7 +7433,9 @@
       <c r="G24" s="26" t="n">
         <v>81.09</v>
       </c>
-      <c r="H24" s="26"/>
+      <c r="H24" s="26" t="n">
+        <v>11.04</v>
+      </c>
       <c r="I24" s="36" t="n">
         <v>3058068</v>
       </c>
@@ -7462,13 +7470,13 @@
       <c r="S24" s="38" t="n">
         <v>3.04</v>
       </c>
-      <c r="T24" s="21"/>
+      <c r="T24" s="21" t="n">
+        <v>0.0733</v>
+      </c>
       <c r="U24" s="21" t="n">
         <v>0.0877</v>
       </c>
-      <c r="V24" s="19" t="n">
-        <v>46317</v>
-      </c>
+      <c r="V24" s="19"/>
       <c r="W24" s="26" t="n">
         <v>2.91</v>
       </c>
@@ -7502,7 +7510,7 @@
       </c>
       <c r="AF24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(F24="Short",AND(T24&lt;&gt;"",N(T24)&lt;0),N(T24)&gt;0)+(N(S24)&gt;=1.5))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG24" s="16" t="n">
         <f aca="false">IF(C24="","",IF(AL24="",0,IF(AL24&gt;=3,4,IF(AL24&gt;=2,2,0))))</f>
@@ -7518,7 +7526,7 @@
       </c>
       <c r="AJ24" s="23" t="n">
         <f aca="false">IF(C24="","",SUM(AB24:AI24))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK24" s="24" t="str">
         <f aca="false">IF(C24="","",IF(AJ24&gt;=14,"A",IF(AJ24&gt;=10,"B","C")))</f>
@@ -7562,7 +7570,7 @@
       </c>
       <c r="AX24" s="43" t="n">
         <f aca="false">IF(AND(C24&lt;&gt;"",A24=$C$4,ISNUMBER(AJ24)),AJ24+ROW()/100000,"")</f>
-        <v>8.00024</v>
+        <v>9.00024</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7579,7 +7587,7 @@
         <v>231</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F25" s="35" t="s">
         <v>190</v>
@@ -7587,7 +7595,9 @@
       <c r="G25" s="26" t="n">
         <v>272.35</v>
       </c>
-      <c r="H25" s="26"/>
+      <c r="H25" s="26" t="n">
+        <v>45.7</v>
+      </c>
       <c r="I25" s="36" t="n">
         <v>906852</v>
       </c>
@@ -7622,13 +7632,13 @@
       <c r="S25" s="38" t="n">
         <v>1.71</v>
       </c>
-      <c r="T25" s="21"/>
+      <c r="T25" s="21" t="n">
+        <v>0.2118</v>
+      </c>
       <c r="U25" s="21" t="n">
         <v>0.0212</v>
       </c>
-      <c r="V25" s="19" t="n">
-        <v>46316</v>
-      </c>
+      <c r="V25" s="19"/>
       <c r="W25" s="26" t="n">
         <v>7.53</v>
       </c>
@@ -7739,7 +7749,7 @@
         <v>233</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="F26" s="35" t="s">
         <v>190</v>
@@ -7747,7 +7757,9 @@
       <c r="G26" s="26" t="n">
         <v>37.3</v>
       </c>
-      <c r="H26" s="26"/>
+      <c r="H26" s="26" t="n">
+        <v>55.4</v>
+      </c>
       <c r="I26" s="36" t="n">
         <v>33320533</v>
       </c>
@@ -7783,7 +7795,7 @@
         <v>0.78</v>
       </c>
       <c r="T26" s="21" t="n">
-        <v>-0.1642</v>
+        <v>-0.173</v>
       </c>
       <c r="U26" s="21" t="n">
         <v>0.0842</v>
@@ -7907,7 +7919,9 @@
       <c r="G27" s="26" t="n">
         <v>172.37</v>
       </c>
-      <c r="H27" s="26"/>
+      <c r="H27" s="26" t="n">
+        <v>217.4</v>
+      </c>
       <c r="I27" s="36" t="n">
         <v>6149214</v>
       </c>
@@ -7942,7 +7956,9 @@
       <c r="S27" s="38" t="n">
         <v>0.81</v>
       </c>
-      <c r="T27" s="21"/>
+      <c r="T27" s="21" t="n">
+        <v>0.3815</v>
+      </c>
       <c r="U27" s="21" t="n">
         <v>0.0114</v>
       </c>
@@ -8067,7 +8083,9 @@
       <c r="G28" s="26" t="n">
         <v>456.44</v>
       </c>
-      <c r="H28" s="26"/>
+      <c r="H28" s="26" t="n">
+        <v>290.21</v>
+      </c>
       <c r="I28" s="36" t="n">
         <v>7702417</v>
       </c>
@@ -8103,10 +8121,10 @@
         <v>0.56</v>
       </c>
       <c r="T28" s="21" t="n">
-        <v>1.514</v>
+        <v>1.5142</v>
       </c>
       <c r="U28" s="21" t="n">
-        <v>0.0469</v>
+        <v>0.0421</v>
       </c>
       <c r="V28" s="19" t="n">
         <v>46350</v>
@@ -8229,7 +8247,9 @@
       <c r="G29" s="26" t="n">
         <v>516.79</v>
       </c>
-      <c r="H29" s="26"/>
+      <c r="H29" s="26" t="n">
+        <v>843.65</v>
+      </c>
       <c r="I29" s="36" t="n">
         <v>22028486</v>
       </c>
@@ -8265,7 +8285,7 @@
         <v>0.69</v>
       </c>
       <c r="T29" s="21" t="n">
-        <v>0.819</v>
+        <v>0.8194</v>
       </c>
       <c r="U29" s="21" t="n">
         <v>0.0242</v>
@@ -8383,7 +8403,7 @@
         <v>241</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F30" s="35" t="s">
         <v>190</v>
@@ -8391,7 +8411,9 @@
       <c r="G30" s="26" t="n">
         <v>51.91</v>
       </c>
-      <c r="H30" s="26"/>
+      <c r="H30" s="26" t="n">
+        <v>59.56</v>
+      </c>
       <c r="I30" s="36" t="n">
         <v>7530214</v>
       </c>
@@ -8426,13 +8448,13 @@
       <c r="S30" s="38" t="n">
         <v>0.75</v>
       </c>
-      <c r="T30" s="21"/>
+      <c r="T30" s="21" t="n">
+        <v>0.1666</v>
+      </c>
       <c r="U30" s="21" t="n">
         <v>0.0302</v>
       </c>
-      <c r="V30" s="19" t="n">
-        <v>46309</v>
-      </c>
+      <c r="V30" s="19"/>
       <c r="W30" s="26" t="n">
         <v>1.33</v>
       </c>
